--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G15">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G35">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G61">

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G11">

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G32">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G35">

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G15">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G26">

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G35">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G62">

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU67"/>
+  <dimension ref="A1:AU68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G19">
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G20">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-09-07 13:30:00</t>
+          <t>2026-09-07 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3690,22 +3690,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G21">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N21">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-07 13:45:00</t>
+          <t>2026-09-07 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:00</t>
+          <t>2026-09-07 13:45:00</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G30">
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G38">
@@ -6619,27 +6619,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-07 14:05:00</t>
+          <t>2026-09-07 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,27 +6782,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-07 14:15:00</t>
+          <t>2026-09-07 14:05:00</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-07 14:30:00</t>
+          <t>2026-09-07 14:15:00</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G43">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G45">
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-07 15:00:00</t>
+          <t>2026-09-07 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G49">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G50">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-09-07 15:30:00</t>
+          <t>2026-09-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G53">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-09-07 15:45:00</t>
+          <t>2026-09-07 15:30:00</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G55">
@@ -9390,27 +9390,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G56">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-09-07 16:00:00</t>
+          <t>2026-09-07 15:45:00</t>
         </is>
       </c>
     </row>
@@ -9558,22 +9558,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G62">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-09-07 16:15:00</t>
+          <t>2026-09-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-09-07 16:30:00</t>
+          <t>2026-09-07 16:15:00</t>
         </is>
       </c>
     </row>
@@ -10857,27 +10857,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O65">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P65">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-09-07 19:30:00</t>
+          <t>2026-09-07 16:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-07 20:00:00</t>
+          <t>2026-09-07 19:30:00</t>
         </is>
       </c>
     </row>
@@ -11188,151 +11188,314 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
+      <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>-1</v>
+      </c>
+      <c r="AN67">
+        <v>-1</v>
+      </c>
+      <c r="AO67">
+        <v>-1</v>
+      </c>
+      <c r="AP67">
+        <v>-1</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>2026-09-07 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Deportes Limache</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Cobresal</t>
         </is>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr">
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>0</v>
-      </c>
-      <c r="Y67">
-        <v>0</v>
-      </c>
-      <c r="Z67">
-        <v>0</v>
-      </c>
-      <c r="AA67">
-        <v>0</v>
-      </c>
-      <c r="AB67">
-        <v>0</v>
-      </c>
-      <c r="AC67">
-        <v>0</v>
-      </c>
-      <c r="AD67">
-        <v>0</v>
-      </c>
-      <c r="AE67">
-        <v>0</v>
-      </c>
-      <c r="AF67">
-        <v>0</v>
-      </c>
-      <c r="AG67">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>0</v>
-      </c>
-      <c r="AK67">
-        <v>0</v>
-      </c>
-      <c r="AL67">
-        <v>0</v>
-      </c>
-      <c r="AM67">
-        <v>-1</v>
-      </c>
-      <c r="AN67">
-        <v>-1</v>
-      </c>
-      <c r="AO67">
-        <v>-1</v>
-      </c>
-      <c r="AP67">
-        <v>-1</v>
-      </c>
-      <c r="AQ67">
-        <v>0</v>
-      </c>
-      <c r="AR67">
-        <v>0</v>
-      </c>
-      <c r="AS67">
-        <v>0</v>
-      </c>
-      <c r="AT67">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>0</v>
+      </c>
+      <c r="AB68">
+        <v>0</v>
+      </c>
+      <c r="AC68">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>0</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
+      <c r="AG68">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>0</v>
+      </c>
+      <c r="AK68">
+        <v>0</v>
+      </c>
+      <c r="AL68">
+        <v>0</v>
+      </c>
+      <c r="AM68">
+        <v>-1</v>
+      </c>
+      <c r="AN68">
+        <v>-1</v>
+      </c>
+      <c r="AO68">
+        <v>-1</v>
+      </c>
+      <c r="AP68">
+        <v>-1</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>0</v>
+      </c>
+      <c r="AS68">
+        <v>0</v>
+      </c>
+      <c r="AT68">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
         <is>
           <t>2026-09-07 20:00:00</t>
         </is>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU68"/>
+  <dimension ref="A1:AU69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O66">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-07 19:30:00</t>
+          <t>2026-09-07 18:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-09-07 20:00:00</t>
+          <t>2026-09-07 19:30:00</t>
         </is>
       </c>
     </row>
@@ -11351,151 +11351,314 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>0</v>
+      </c>
+      <c r="AB68">
+        <v>0</v>
+      </c>
+      <c r="AC68">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>0</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
+      <c r="AG68">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>0</v>
+      </c>
+      <c r="AK68">
+        <v>0</v>
+      </c>
+      <c r="AL68">
+        <v>0</v>
+      </c>
+      <c r="AM68">
+        <v>-1</v>
+      </c>
+      <c r="AN68">
+        <v>-1</v>
+      </c>
+      <c r="AO68">
+        <v>-1</v>
+      </c>
+      <c r="AP68">
+        <v>-1</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>0</v>
+      </c>
+      <c r="AS68">
+        <v>0</v>
+      </c>
+      <c r="AT68">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>2026-09-07 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Deportes Limache</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Cobresal</t>
         </is>
       </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68" t="inlineStr">
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>0</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
-        <v>0</v>
-      </c>
-      <c r="T68">
-        <v>0</v>
-      </c>
-      <c r="U68">
-        <v>0</v>
-      </c>
-      <c r="V68">
-        <v>0</v>
-      </c>
-      <c r="W68">
-        <v>0</v>
-      </c>
-      <c r="X68">
-        <v>0</v>
-      </c>
-      <c r="Y68">
-        <v>0</v>
-      </c>
-      <c r="Z68">
-        <v>0</v>
-      </c>
-      <c r="AA68">
-        <v>0</v>
-      </c>
-      <c r="AB68">
-        <v>0</v>
-      </c>
-      <c r="AC68">
-        <v>0</v>
-      </c>
-      <c r="AD68">
-        <v>0</v>
-      </c>
-      <c r="AE68">
-        <v>0</v>
-      </c>
-      <c r="AF68">
-        <v>0</v>
-      </c>
-      <c r="AG68">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>0</v>
-      </c>
-      <c r="AK68">
-        <v>0</v>
-      </c>
-      <c r="AL68">
-        <v>0</v>
-      </c>
-      <c r="AM68">
-        <v>-1</v>
-      </c>
-      <c r="AN68">
-        <v>-1</v>
-      </c>
-      <c r="AO68">
-        <v>-1</v>
-      </c>
-      <c r="AP68">
-        <v>-1</v>
-      </c>
-      <c r="AQ68">
-        <v>0</v>
-      </c>
-      <c r="AR68">
-        <v>0</v>
-      </c>
-      <c r="AS68">
-        <v>0</v>
-      </c>
-      <c r="AT68">
-        <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <v>0</v>
+      </c>
+      <c r="AB69">
+        <v>0</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69">
+        <v>0</v>
+      </c>
+      <c r="AE69">
+        <v>0</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
+      <c r="AG69">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>0</v>
+      </c>
+      <c r="AK69">
+        <v>0</v>
+      </c>
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>-1</v>
+      </c>
+      <c r="AN69">
+        <v>-1</v>
+      </c>
+      <c r="AO69">
+        <v>-1</v>
+      </c>
+      <c r="AP69">
+        <v>-1</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>0</v>
+      </c>
+      <c r="AS69">
+        <v>0</v>
+      </c>
+      <c r="AT69">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
         <is>
           <t>2026-09-07 20:00:00</t>
         </is>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,34 +4067,34 @@
         <v>3.68</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA23">
         <v>2.62</v>
@@ -4103,19 +4103,19 @@
         <v>1.5</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>0</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>7.21</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G50">

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>12.3</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL40">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1133,55 +1133,55 @@
         <v>2.6</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>2.3</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9120,55 +9120,55 @@
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9772,55 +9772,55 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL63">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU69"/>
+  <dimension ref="A1:AU70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2274,55 +2274,55 @@
         <v>2.59</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3089,34 +3089,34 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA17">
         <v>1.44</v>
@@ -3125,19 +3125,19 @@
         <v>2.62</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,34 +3252,34 @@
         <v>12.3</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA18">
         <v>1.36</v>
@@ -3288,19 +3288,19 @@
         <v>3</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.7</v>
+        <v>3.83</v>
       </c>
       <c r="O28">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="P28">
-        <v>5.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q28">
-        <v>2.38</v>
+        <v>5.03</v>
       </c>
       <c r="R28">
         <v>2</v>
       </c>
       <c r="S28">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="T28">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="U28">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="V28">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X28">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y28">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z28">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="AA28">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="AB28">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AC28">
-        <v>5.25</v>
+        <v>3.92</v>
       </c>
       <c r="AD28">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AE28">
         <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="AG28">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK28">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.83</v>
+        <v>1.7</v>
       </c>
       <c r="O29">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="P29">
-        <v>2.14</v>
+        <v>5.25</v>
       </c>
       <c r="Q29">
-        <v>5.03</v>
+        <v>2.38</v>
       </c>
       <c r="R29">
         <v>2</v>
       </c>
       <c r="S29">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="T29">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="U29">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="V29">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="W29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X29">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z29">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="AA29">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="AB29">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AC29">
-        <v>3.92</v>
+        <v>5.25</v>
       </c>
       <c r="AD29">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AE29">
         <v>1.02</v>
       </c>
       <c r="AF29">
+        <v>2.34</v>
+      </c>
+      <c r="AG29">
+        <v>1.57</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.27</v>
+      </c>
+      <c r="AK29">
         <v>1.95</v>
-      </c>
-      <c r="AG29">
-        <v>1.76</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.4</v>
-      </c>
-      <c r="AK29">
-        <v>1.22</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,65 +5525,65 @@
         </is>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="O32">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="P32">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="Q32">
-        <v>4.68</v>
+        <v>3.3</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="S32">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="T32">
-        <v>3.15</v>
+        <v>2.19</v>
       </c>
       <c r="U32">
-        <v>2.41</v>
+        <v>4.33</v>
       </c>
       <c r="V32">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="W32">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="Z32">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="AA32">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="AB32">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="AC32">
-        <v>2.51</v>
+        <v>6</v>
       </c>
       <c r="AD32">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AE32">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
+        <v>2.21</v>
+      </c>
+      <c r="AG32">
         <v>1.61</v>
       </c>
-      <c r="AG32">
-        <v>2.18</v>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AK32">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q33">
-        <v>2.5</v>
+        <v>4.68</v>
       </c>
       <c r="R33">
         <v>2.25</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T33">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="U33">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="V33">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB33">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AC33">
-        <v>2.72</v>
+        <v>2.51</v>
       </c>
       <c r="AD33">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE33">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF33">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG33">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.74</v>
+        <v>1.21</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q35">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="R35">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="V35">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="W35">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y35">
+        <v>1.2</v>
+      </c>
+      <c r="Z35">
+        <v>3.9</v>
+      </c>
+      <c r="AA35">
+        <v>1.8</v>
+      </c>
+      <c r="AB35">
+        <v>2</v>
+      </c>
+      <c r="AC35">
+        <v>2.72</v>
+      </c>
+      <c r="AD35">
+        <v>1.4</v>
+      </c>
+      <c r="AE35">
+        <v>1.11</v>
+      </c>
+      <c r="AF35">
+        <v>1.62</v>
+      </c>
+      <c r="AG35">
+        <v>2.16</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.27</v>
       </c>
-      <c r="Z35">
-        <v>3.14</v>
-      </c>
-      <c r="AA35">
-        <v>1.95</v>
-      </c>
-      <c r="AB35">
-        <v>1.76</v>
-      </c>
-      <c r="AC35">
-        <v>3.42</v>
-      </c>
-      <c r="AD35">
-        <v>1.23</v>
-      </c>
-      <c r="AE35">
-        <v>1.04</v>
-      </c>
-      <c r="AF35">
+      <c r="AK35">
         <v>1.74</v>
-      </c>
-      <c r="AG35">
-        <v>1.96</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.26</v>
-      </c>
-      <c r="AK35">
-        <v>1.49</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G36">
@@ -6186,55 +6186,55 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>5.11</v>
+        <v>2.98</v>
       </c>
       <c r="R36">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S36">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T36">
-        <v>2.91</v>
+        <v>2.74</v>
       </c>
       <c r="U36">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>3.68</v>
+        <v>3.14</v>
       </c>
       <c r="AA36">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AB36">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="AC36">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="AD36">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF36">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG36">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK36">
-        <v>1.13</v>
+        <v>1.49</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G37">
@@ -6349,55 +6349,55 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>1.94</v>
+        <v>5.11</v>
       </c>
       <c r="R37">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
         <v>1.33</v>
       </c>
       <c r="T37">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="U37">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V37">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.88</v>
+        <v>3.68</v>
       </c>
       <c r="AA37">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AB37">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AC37">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AD37">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AG37">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK37">
-        <v>2.71</v>
+        <v>1.13</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.52</v>
+        <v>1.94</v>
       </c>
       <c r="R38">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="U38">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="V38">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>4.9</v>
+        <v>3.88</v>
       </c>
       <c r="AA38">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="AB38">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AC38">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="AD38">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AE38">
+        <v>1.12</v>
+      </c>
+      <c r="AF38">
+        <v>1.87</v>
+      </c>
+      <c r="AG38">
+        <v>1.83</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.18</v>
       </c>
-      <c r="AF38">
-        <v>1.5</v>
-      </c>
-      <c r="AG38">
-        <v>2.53</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.26</v>
-      </c>
       <c r="AK38">
-        <v>1.76</v>
+        <v>2.71</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.41</v>
+        <v>2.05</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P39">
-        <v>1.97</v>
+        <v>3.34</v>
       </c>
       <c r="Q39">
-        <v>3.75</v>
+        <v>2.52</v>
       </c>
       <c r="R39">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="U39">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="V39">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="W39">
         <v>1.11</v>
@@ -6699,31 +6699,31 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
+        <v>1.11</v>
+      </c>
+      <c r="Z39">
+        <v>4.9</v>
+      </c>
+      <c r="AA39">
+        <v>1.54</v>
+      </c>
+      <c r="AB39">
+        <v>2.32</v>
+      </c>
+      <c r="AC39">
+        <v>2.33</v>
+      </c>
+      <c r="AD39">
+        <v>1.58</v>
+      </c>
+      <c r="AE39">
         <v>1.18</v>
       </c>
-      <c r="Z39">
-        <v>3.92</v>
-      </c>
-      <c r="AA39">
-        <v>1.72</v>
-      </c>
-      <c r="AB39">
-        <v>2.06</v>
-      </c>
-      <c r="AC39">
-        <v>2.7</v>
-      </c>
-      <c r="AD39">
-        <v>1.36</v>
-      </c>
-      <c r="AE39">
-        <v>1.1</v>
-      </c>
       <c r="AF39">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG39">
-        <v>2.18</v>
+        <v>2.53</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.81</v>
+        <v>1.26</v>
       </c>
       <c r="AK39">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6782,27 +6782,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.7</v>
+        <v>3.41</v>
       </c>
       <c r="O40">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="Q40">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="R40">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S40">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="U40">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="AA40">
+        <v>1.72</v>
+      </c>
+      <c r="AB40">
+        <v>2.06</v>
+      </c>
+      <c r="AC40">
+        <v>2.7</v>
+      </c>
+      <c r="AD40">
+        <v>1.36</v>
+      </c>
+      <c r="AE40">
+        <v>1.1</v>
+      </c>
+      <c r="AF40">
+        <v>1.61</v>
+      </c>
+      <c r="AG40">
+        <v>2.18</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.81</v>
       </c>
-      <c r="AB40">
-        <v>1.95</v>
-      </c>
-      <c r="AC40">
-        <v>2.98</v>
-      </c>
-      <c r="AD40">
-        <v>1.33</v>
-      </c>
-      <c r="AE40">
-        <v>1.09</v>
-      </c>
-      <c r="AF40">
-        <v>1.65</v>
-      </c>
-      <c r="AG40">
-        <v>2.15</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.27</v>
-      </c>
       <c r="AK40">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-07 14:05:00</t>
+          <t>2026-09-07 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,65 +6992,65 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q41">
-        <v>7.21</v>
+        <v>3.28</v>
       </c>
       <c r="R41">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="S41">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T41">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U41">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="V41">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="Z41">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AB41">
+        <v>1.95</v>
+      </c>
+      <c r="AC41">
+        <v>2.98</v>
+      </c>
+      <c r="AD41">
+        <v>1.33</v>
+      </c>
+      <c r="AE41">
+        <v>1.09</v>
+      </c>
+      <c r="AF41">
+        <v>1.65</v>
+      </c>
+      <c r="AG41">
         <v>2.15</v>
       </c>
-      <c r="AC41">
-        <v>2.52</v>
-      </c>
-      <c r="AD41">
-        <v>1.41</v>
-      </c>
-      <c r="AE41">
-        <v>1.14</v>
-      </c>
-      <c r="AF41">
-        <v>1.93</v>
-      </c>
-      <c r="AG41">
-        <v>1.78</v>
-      </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AK41">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-07 14:15:00</t>
+          <t>2026-09-07 14:05:00</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G42">
@@ -7164,55 +7164,55 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>7.21</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-09-07 14:30:00</t>
+          <t>2026-09-07 14:15:00</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G43">
@@ -7327,55 +7327,55 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,25 +7481,25 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="R44">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S44">
         <v>1.29</v>
       </c>
       <c r="T44">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U44">
         <v>2.44</v>
@@ -7508,37 +7508,37 @@
         <v>1.48</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z44">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="AA44">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB44">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC44">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AD44">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE44">
         <v>1.12</v>
       </c>
       <c r="AF44">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AG44">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK44">
-        <v>2.14</v>
+        <v>1.56</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.2</v>
+        <v>2.13</v>
       </c>
       <c r="O45">
+        <v>3.65</v>
+      </c>
+      <c r="P45">
+        <v>3.33</v>
+      </c>
+      <c r="Q45">
+        <v>2.2</v>
+      </c>
+      <c r="R45">
+        <v>2.3</v>
+      </c>
+      <c r="S45">
+        <v>1.29</v>
+      </c>
+      <c r="T45">
+        <v>3.3</v>
+      </c>
+      <c r="U45">
+        <v>2.44</v>
+      </c>
+      <c r="V45">
+        <v>1.48</v>
+      </c>
+      <c r="W45">
+        <v>1.07</v>
+      </c>
+      <c r="X45">
+        <v>1.01</v>
+      </c>
+      <c r="Y45">
+        <v>1.17</v>
+      </c>
+      <c r="Z45">
+        <v>3.98</v>
+      </c>
+      <c r="AA45">
+        <v>1.69</v>
+      </c>
+      <c r="AB45">
         <v>2.1</v>
       </c>
-      <c r="P45">
-        <v>3</v>
-      </c>
-      <c r="Q45">
-        <v>3.36</v>
-      </c>
-      <c r="R45">
-        <v>2.05</v>
-      </c>
-      <c r="S45">
-        <v>1.4</v>
-      </c>
-      <c r="T45">
-        <v>2.69</v>
-      </c>
-      <c r="U45">
-        <v>2.85</v>
-      </c>
-      <c r="V45">
-        <v>1.36</v>
-      </c>
-      <c r="W45">
-        <v>1.05</v>
-      </c>
-      <c r="X45">
-        <v>1.02</v>
-      </c>
-      <c r="Y45">
-        <v>1.3</v>
-      </c>
-      <c r="Z45">
-        <v>2.97</v>
-      </c>
-      <c r="AA45">
-        <v>2.02</v>
-      </c>
-      <c r="AB45">
-        <v>1.75</v>
-      </c>
       <c r="AC45">
-        <v>3.34</v>
+        <v>2.59</v>
       </c>
       <c r="AD45">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AE45">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF45">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AG45">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>1.41</v>
+        <v>2.14</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.43</v>
+        <v>3.2</v>
       </c>
       <c r="O46">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="P46">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-07 15:00:00</t>
+          <t>2026-09-07 14:30:00</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,65 +8296,65 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="R49">
-        <v>2.47</v>
+        <v>2.07</v>
       </c>
       <c r="S49">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>4.33</v>
+        <v>2.77</v>
       </c>
       <c r="U49">
-        <v>1.84</v>
+        <v>2.88</v>
       </c>
       <c r="V49">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="W49">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="Z49">
-        <v>6.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA49">
-        <v>1.29</v>
+        <v>1.92</v>
       </c>
       <c r="AB49">
-        <v>3.28</v>
+        <v>1.88</v>
       </c>
       <c r="AC49">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="AD49">
+        <v>1.28</v>
+      </c>
+      <c r="AE49">
+        <v>1.07</v>
+      </c>
+      <c r="AF49">
+        <v>1.68</v>
+      </c>
+      <c r="AG49">
         <v>2</v>
       </c>
-      <c r="AE49">
-        <v>1.4</v>
-      </c>
-      <c r="AF49">
-        <v>1.28</v>
-      </c>
-      <c r="AG49">
-        <v>3.1</v>
-      </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="O50">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P50">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="Q50">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S50">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="U50">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="V50">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z50">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA50">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AB50">
-        <v>2.55</v>
+        <v>3.28</v>
       </c>
       <c r="AC50">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AD50">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AE50">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF50">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AG50">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AK50">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="O51">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="P51">
-        <v>4.28</v>
+        <v>2.62</v>
       </c>
       <c r="Q51">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="R51">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="T51">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="U51">
-        <v>2.81</v>
+        <v>2.21</v>
       </c>
       <c r="V51">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X51">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="Z51">
-        <v>3.18</v>
+        <v>5.5</v>
       </c>
       <c r="AA51">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AB51">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC51">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD51">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="AG51">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-09-07 15:30:00</t>
+          <t>2026-09-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="O52">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P52">
-        <v>3.3</v>
+        <v>4.28</v>
       </c>
       <c r="Q52">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="R52">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="S52">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T52">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U52">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="V52">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W52">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y52">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z52">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AA52">
         <v>2.05</v>
       </c>
       <c r="AB52">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC52">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD52">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE52">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG52">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q54">
-        <v>2.03</v>
+        <v>2.46</v>
       </c>
       <c r="R54">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="S54">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
-        <v>2.44</v>
+        <v>2.86</v>
       </c>
       <c r="U54">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="V54">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="W54">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
         <v>1.02</v>
       </c>
       <c r="Y54">
+        <v>1.19</v>
+      </c>
+      <c r="Z54">
+        <v>3.93</v>
+      </c>
+      <c r="AA54">
+        <v>1.8</v>
+      </c>
+      <c r="AB54">
+        <v>2</v>
+      </c>
+      <c r="AC54">
+        <v>2.8</v>
+      </c>
+      <c r="AD54">
         <v>1.33</v>
       </c>
-      <c r="Z54">
-        <v>2.83</v>
-      </c>
-      <c r="AA54">
-        <v>2.12</v>
-      </c>
-      <c r="AB54">
-        <v>1.63</v>
-      </c>
-      <c r="AC54">
-        <v>3.82</v>
-      </c>
-      <c r="AD54">
-        <v>1.19</v>
-      </c>
       <c r="AE54">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AF54">
-        <v>2.31</v>
+        <v>1.65</v>
       </c>
       <c r="AG54">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>2.49</v>
+        <v>1.82</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G55">
@@ -9283,55 +9283,55 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-09-07 15:45:00</t>
+          <t>2026-09-07 15:30:00</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.85</v>
+        <v>1.91</v>
       </c>
       <c r="O56">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P56">
-        <v>2.44</v>
+        <v>3.13</v>
       </c>
       <c r="Q56">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="R56">
+        <v>2.12</v>
+      </c>
+      <c r="S56">
+        <v>1.36</v>
+      </c>
+      <c r="T56">
+        <v>3</v>
+      </c>
+      <c r="U56">
+        <v>2.75</v>
+      </c>
+      <c r="V56">
+        <v>1.42</v>
+      </c>
+      <c r="W56">
+        <v>1.08</v>
+      </c>
+      <c r="X56">
+        <v>1</v>
+      </c>
+      <c r="Y56">
+        <v>1.28</v>
+      </c>
+      <c r="Z56">
+        <v>3.62</v>
+      </c>
+      <c r="AA56">
+        <v>1.92</v>
+      </c>
+      <c r="AB56">
         <v>1.95</v>
       </c>
-      <c r="S56">
-        <v>1.52</v>
-      </c>
-      <c r="T56">
-        <v>2.5</v>
-      </c>
-      <c r="U56">
-        <v>3.4</v>
-      </c>
-      <c r="V56">
-        <v>1.32</v>
-      </c>
-      <c r="W56">
-        <v>1.03</v>
-      </c>
-      <c r="X56">
-        <v>1.04</v>
-      </c>
-      <c r="Y56">
-        <v>1.39</v>
-      </c>
-      <c r="Z56">
-        <v>2.8</v>
-      </c>
-      <c r="AA56">
-        <v>2.25</v>
-      </c>
-      <c r="AB56">
-        <v>1.68</v>
-      </c>
       <c r="AC56">
-        <v>4.6</v>
+        <v>2.89</v>
       </c>
       <c r="AD56">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AE56">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF56">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG56">
+        <v>2</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>1.27</v>
+      </c>
+      <c r="AK56">
         <v>1.88</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.4</v>
-      </c>
-      <c r="AK56">
-        <v>1.43</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9553,27 +9553,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-09-07 16:00:00</t>
+          <t>2026-09-07 15:45:00</t>
         </is>
       </c>
     </row>
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G58">
@@ -9772,55 +9772,55 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S58">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T58">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U58">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V58">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W58">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z58">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AA58">
+        <v>1.7</v>
+      </c>
+      <c r="AB58">
         <v>2.1</v>
       </c>
-      <c r="AB58">
-        <v>1.64</v>
-      </c>
       <c r="AC58">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AD58">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE58">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF58">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG58">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK58">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G59">
@@ -9935,55 +9935,55 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q60">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="R60">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S60">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="T60">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="U60">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="V60">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="W60">
+        <v>1.06</v>
+      </c>
+      <c r="X60">
         <v>1.02</v>
       </c>
-      <c r="X60">
-        <v>1.05</v>
-      </c>
       <c r="Y60">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z60">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="AA60">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="AB60">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AC60">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD60">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AE60">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF60">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="AG60">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G61">
@@ -10261,55 +10261,55 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="R61">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S61">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T61">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="U61">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V61">
         <v>1.27</v>
       </c>
       <c r="W61">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z61">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AA61">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AB61">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AC61">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD61">
         <v>1.16</v>
       </c>
       <c r="AE61">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF61">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AG61">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G62">
@@ -10424,55 +10424,55 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="R62">
+        <v>1.9</v>
+      </c>
+      <c r="S62">
+        <v>1.45</v>
+      </c>
+      <c r="T62">
+        <v>2.44</v>
+      </c>
+      <c r="U62">
+        <v>3.2</v>
+      </c>
+      <c r="V62">
+        <v>1.27</v>
+      </c>
+      <c r="W62">
+        <v>1</v>
+      </c>
+      <c r="X62">
+        <v>1.02</v>
+      </c>
+      <c r="Y62">
+        <v>1.36</v>
+      </c>
+      <c r="Z62">
+        <v>2.7</v>
+      </c>
+      <c r="AA62">
+        <v>2.3</v>
+      </c>
+      <c r="AB62">
+        <v>1.6</v>
+      </c>
+      <c r="AC62">
+        <v>4.1</v>
+      </c>
+      <c r="AD62">
+        <v>1.16</v>
+      </c>
+      <c r="AE62">
+        <v>1.01</v>
+      </c>
+      <c r="AF62">
         <v>1.88</v>
       </c>
-      <c r="S62">
-        <v>1.5</v>
-      </c>
-      <c r="T62">
-        <v>2.5</v>
-      </c>
-      <c r="U62">
-        <v>3.5</v>
-      </c>
-      <c r="V62">
-        <v>1.25</v>
-      </c>
-      <c r="W62">
-        <v>1.04</v>
-      </c>
-      <c r="X62">
-        <v>1.05</v>
-      </c>
-      <c r="Y62">
-        <v>1.5</v>
-      </c>
-      <c r="Z62">
-        <v>2.38</v>
-      </c>
-      <c r="AA62">
-        <v>2.49</v>
-      </c>
-      <c r="AB62">
-        <v>1.42</v>
-      </c>
-      <c r="AC62">
-        <v>5</v>
-      </c>
-      <c r="AD62">
-        <v>1.1</v>
-      </c>
-      <c r="AE62">
-        <v>1.04</v>
-      </c>
-      <c r="AF62">
-        <v>2.08</v>
-      </c>
       <c r="AG62">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK62">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G63">
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
+        <v>3.08</v>
+      </c>
+      <c r="R63">
+        <v>1.88</v>
+      </c>
+      <c r="S63">
+        <v>1.5</v>
+      </c>
+      <c r="T63">
         <v>2.5</v>
       </c>
-      <c r="R63">
-        <v>2</v>
-      </c>
-      <c r="S63">
-        <v>1.46</v>
-      </c>
-      <c r="T63">
-        <v>2.41</v>
-      </c>
       <c r="U63">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="V63">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W63">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X63">
+        <v>1.05</v>
+      </c>
+      <c r="Y63">
+        <v>1.5</v>
+      </c>
+      <c r="Z63">
+        <v>2.38</v>
+      </c>
+      <c r="AA63">
+        <v>2.49</v>
+      </c>
+      <c r="AB63">
+        <v>1.42</v>
+      </c>
+      <c r="AC63">
+        <v>5</v>
+      </c>
+      <c r="AD63">
+        <v>1.1</v>
+      </c>
+      <c r="AE63">
         <v>1.04</v>
       </c>
-      <c r="Y63">
-        <v>1.36</v>
-      </c>
-      <c r="Z63">
-        <v>2.7</v>
-      </c>
-      <c r="AA63">
-        <v>2.35</v>
-      </c>
-      <c r="AB63">
-        <v>1.6</v>
-      </c>
-      <c r="AC63">
-        <v>3.84</v>
-      </c>
-      <c r="AD63">
-        <v>1.18</v>
-      </c>
-      <c r="AE63">
-        <v>1.03</v>
-      </c>
       <c r="AF63">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AG63">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK63">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G64">
@@ -10750,55 +10750,55 @@
         <v>0</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-09-07 16:15:00</t>
+          <t>2026-09-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-09-07 16:30:00</t>
+          <t>2026-09-07 16:15:00</t>
         </is>
       </c>
     </row>
@@ -11020,27 +11020,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:00</t>
+          <t>2026-09-07 16:30:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-09-07 19:30:00</t>
+          <t>2026-09-07 18:00:00</t>
         </is>
       </c>
     </row>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-09-07 20:00:00</t>
+          <t>2026-09-07 19:30:00</t>
         </is>
       </c>
     </row>
@@ -11514,151 +11514,314 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N69">
+        <v>2.05</v>
+      </c>
+      <c r="O69">
+        <v>3.4</v>
+      </c>
+      <c r="P69">
+        <v>3.6</v>
+      </c>
+      <c r="Q69">
+        <v>2.46</v>
+      </c>
+      <c r="R69">
+        <v>2.18</v>
+      </c>
+      <c r="S69">
+        <v>1.43</v>
+      </c>
+      <c r="T69">
+        <v>2.62</v>
+      </c>
+      <c r="U69">
+        <v>2.95</v>
+      </c>
+      <c r="V69">
+        <v>1.35</v>
+      </c>
+      <c r="W69">
+        <v>1.03</v>
+      </c>
+      <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
+        <v>1.36</v>
+      </c>
+      <c r="Z69">
+        <v>3.16</v>
+      </c>
+      <c r="AA69">
+        <v>2.1</v>
+      </c>
+      <c r="AB69">
+        <v>1.68</v>
+      </c>
+      <c r="AC69">
+        <v>3.85</v>
+      </c>
+      <c r="AD69">
+        <v>1.22</v>
+      </c>
+      <c r="AE69">
+        <v>1.04</v>
+      </c>
+      <c r="AF69">
+        <v>1.85</v>
+      </c>
+      <c r="AG69">
+        <v>1.85</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>1.25</v>
+      </c>
+      <c r="AK69">
+        <v>1.74</v>
+      </c>
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>-1</v>
+      </c>
+      <c r="AN69">
+        <v>-1</v>
+      </c>
+      <c r="AO69">
+        <v>-1</v>
+      </c>
+      <c r="AP69">
+        <v>-1</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>0</v>
+      </c>
+      <c r="AS69">
+        <v>0</v>
+      </c>
+      <c r="AT69">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>2026-09-07 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Deportes Limache</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Cobresal</t>
         </is>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69" t="inlineStr">
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>0</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="W69">
-        <v>0</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
-      </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
-      <c r="AA69">
-        <v>0</v>
-      </c>
-      <c r="AB69">
-        <v>0</v>
-      </c>
-      <c r="AC69">
-        <v>0</v>
-      </c>
-      <c r="AD69">
-        <v>0</v>
-      </c>
-      <c r="AE69">
-        <v>0</v>
-      </c>
-      <c r="AF69">
-        <v>0</v>
-      </c>
-      <c r="AG69">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>0</v>
-      </c>
-      <c r="AK69">
-        <v>0</v>
-      </c>
-      <c r="AL69">
-        <v>0</v>
-      </c>
-      <c r="AM69">
-        <v>-1</v>
-      </c>
-      <c r="AN69">
-        <v>-1</v>
-      </c>
-      <c r="AO69">
-        <v>-1</v>
-      </c>
-      <c r="AP69">
-        <v>-1</v>
-      </c>
-      <c r="AQ69">
-        <v>0</v>
-      </c>
-      <c r="AR69">
-        <v>0</v>
-      </c>
-      <c r="AS69">
-        <v>0</v>
-      </c>
-      <c r="AT69">
-        <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
+      <c r="N70">
+        <v>1.7</v>
+      </c>
+      <c r="O70">
+        <v>3.6</v>
+      </c>
+      <c r="P70">
+        <v>3.9</v>
+      </c>
+      <c r="Q70">
+        <v>2.15</v>
+      </c>
+      <c r="R70">
+        <v>2.4</v>
+      </c>
+      <c r="S70">
+        <v>1.25</v>
+      </c>
+      <c r="T70">
+        <v>3.5</v>
+      </c>
+      <c r="U70">
+        <v>2.27</v>
+      </c>
+      <c r="V70">
+        <v>1.58</v>
+      </c>
+      <c r="W70">
+        <v>1.14</v>
+      </c>
+      <c r="X70">
+        <v>1.02</v>
+      </c>
+      <c r="Y70">
+        <v>1.17</v>
+      </c>
+      <c r="Z70">
+        <v>4.2</v>
+      </c>
+      <c r="AA70">
+        <v>1.53</v>
+      </c>
+      <c r="AB70">
+        <v>2.3</v>
+      </c>
+      <c r="AC70">
+        <v>2.25</v>
+      </c>
+      <c r="AD70">
+        <v>1.55</v>
+      </c>
+      <c r="AE70">
+        <v>1.22</v>
+      </c>
+      <c r="AF70">
+        <v>1.55</v>
+      </c>
+      <c r="AG70">
+        <v>2.33</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
+        <v>1.17</v>
+      </c>
+      <c r="AK70">
+        <v>2</v>
+      </c>
+      <c r="AL70">
+        <v>0</v>
+      </c>
+      <c r="AM70">
+        <v>-1</v>
+      </c>
+      <c r="AN70">
+        <v>-1</v>
+      </c>
+      <c r="AO70">
+        <v>-1</v>
+      </c>
+      <c r="AP70">
+        <v>-1</v>
+      </c>
+      <c r="AQ70">
+        <v>0</v>
+      </c>
+      <c r="AR70">
+        <v>0</v>
+      </c>
+      <c r="AS70">
+        <v>0</v>
+      </c>
+      <c r="AT70">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
         <is>
           <t>2026-09-07 20:00:00</t>
         </is>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU70"/>
+  <dimension ref="A1:AU73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="O17">
-        <v>5.1</v>
+        <v>5.65</v>
       </c>
       <c r="P17">
-        <v>8</v>
+        <v>12.3</v>
       </c>
       <c r="Q17">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="R17">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="S17">
+        <v>1.22</v>
+      </c>
+      <c r="T17">
+        <v>3.5</v>
+      </c>
+      <c r="U17">
+        <v>2</v>
+      </c>
+      <c r="V17">
+        <v>1.68</v>
+      </c>
+      <c r="W17">
         <v>1.17</v>
-      </c>
-      <c r="T17">
-        <v>4.5</v>
-      </c>
-      <c r="U17">
-        <v>2.06</v>
-      </c>
-      <c r="V17">
-        <v>1.66</v>
-      </c>
-      <c r="W17">
-        <v>1.14</v>
       </c>
       <c r="X17">
         <v>1</v>
       </c>
       <c r="Y17">
+        <v>1.08</v>
+      </c>
+      <c r="Z17">
+        <v>5.6</v>
+      </c>
+      <c r="AA17">
+        <v>1.36</v>
+      </c>
+      <c r="AB17">
+        <v>3</v>
+      </c>
+      <c r="AC17">
+        <v>1.94</v>
+      </c>
+      <c r="AD17">
+        <v>1.75</v>
+      </c>
+      <c r="AE17">
+        <v>1.29</v>
+      </c>
+      <c r="AF17">
+        <v>1.83</v>
+      </c>
+      <c r="AG17">
+        <v>1.84</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.07</v>
       </c>
-      <c r="Z17">
-        <v>5.75</v>
-      </c>
-      <c r="AA17">
-        <v>1.44</v>
-      </c>
-      <c r="AB17">
-        <v>2.62</v>
-      </c>
-      <c r="AC17">
-        <v>2.02</v>
-      </c>
-      <c r="AD17">
-        <v>1.69</v>
-      </c>
-      <c r="AE17">
-        <v>1.25</v>
-      </c>
-      <c r="AF17">
-        <v>1.63</v>
-      </c>
-      <c r="AG17">
-        <v>2.1</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.1</v>
-      </c>
       <c r="AK17">
-        <v>3.4</v>
+        <v>3.86</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="O18">
-        <v>5.65</v>
+        <v>5.1</v>
       </c>
       <c r="P18">
-        <v>12.3</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="R18">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V18">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z18">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA18">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB18">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AC18">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AD18">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AE18">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AG18">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK18">
-        <v>3.86</v>
+        <v>3.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="O34">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>4.16</v>
+        <v>3.2</v>
       </c>
       <c r="Q34">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>3.66</v>
+        <v>3.04</v>
       </c>
       <c r="U34">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>5.05</v>
+        <v>3.9</v>
       </c>
       <c r="AA34">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AB34">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC34">
-        <v>2.25</v>
+        <v>2.72</v>
       </c>
       <c r="AD34">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK34">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="P35">
-        <v>3.2</v>
+        <v>4.16</v>
       </c>
       <c r="Q35">
+        <v>2.18</v>
+      </c>
+      <c r="R35">
         <v>2.5</v>
       </c>
-      <c r="R35">
+      <c r="S35">
+        <v>1.22</v>
+      </c>
+      <c r="T35">
+        <v>3.66</v>
+      </c>
+      <c r="U35">
+        <v>2.11</v>
+      </c>
+      <c r="V35">
+        <v>1.63</v>
+      </c>
+      <c r="W35">
+        <v>1.13</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.1</v>
+      </c>
+      <c r="Z35">
+        <v>5.05</v>
+      </c>
+      <c r="AA35">
+        <v>1.44</v>
+      </c>
+      <c r="AB35">
+        <v>2.5</v>
+      </c>
+      <c r="AC35">
         <v>2.25</v>
       </c>
-      <c r="S35">
-        <v>1.33</v>
-      </c>
-      <c r="T35">
-        <v>3.04</v>
-      </c>
-      <c r="U35">
-        <v>2.45</v>
-      </c>
-      <c r="V35">
-        <v>1.48</v>
-      </c>
-      <c r="W35">
-        <v>1.08</v>
-      </c>
-      <c r="X35">
-        <v>1.05</v>
-      </c>
-      <c r="Y35">
-        <v>1.2</v>
-      </c>
-      <c r="Z35">
-        <v>3.9</v>
-      </c>
-      <c r="AA35">
-        <v>1.8</v>
-      </c>
-      <c r="AB35">
-        <v>2</v>
-      </c>
-      <c r="AC35">
-        <v>2.72</v>
-      </c>
       <c r="AD35">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="AE35">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AG35">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK35">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="O50">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="P50">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="Q50">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="R50">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="T50">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>1.84</v>
+        <v>2.21</v>
       </c>
       <c r="V50">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="W50">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z50">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA50">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AB50">
-        <v>3.28</v>
+        <v>2.55</v>
       </c>
       <c r="AC50">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD50">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AE50">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AF50">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AG50">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AK50">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="O51">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P51">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="Q51">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S51">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="T51">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="U51">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="V51">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="W51">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z51">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA51">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AB51">
-        <v>2.55</v>
+        <v>3.28</v>
       </c>
       <c r="AC51">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AD51">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AE51">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF51">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AG51">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AK51">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -11824,6 +11824,495 @@
       <c r="AU70" t="inlineStr">
         <is>
           <t>2026-09-07 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+      <c r="AA71">
+        <v>0</v>
+      </c>
+      <c r="AB71">
+        <v>0</v>
+      </c>
+      <c r="AC71">
+        <v>0</v>
+      </c>
+      <c r="AD71">
+        <v>0</v>
+      </c>
+      <c r="AE71">
+        <v>0</v>
+      </c>
+      <c r="AF71">
+        <v>0</v>
+      </c>
+      <c r="AG71">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>0</v>
+      </c>
+      <c r="AK71">
+        <v>0</v>
+      </c>
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>-1</v>
+      </c>
+      <c r="AN71">
+        <v>-1</v>
+      </c>
+      <c r="AO71">
+        <v>-1</v>
+      </c>
+      <c r="AP71">
+        <v>-1</v>
+      </c>
+      <c r="AQ71">
+        <v>0</v>
+      </c>
+      <c r="AR71">
+        <v>0</v>
+      </c>
+      <c r="AS71">
+        <v>0</v>
+      </c>
+      <c r="AT71">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+      <c r="AA72">
+        <v>0</v>
+      </c>
+      <c r="AB72">
+        <v>0</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72">
+        <v>0</v>
+      </c>
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>0</v>
+      </c>
+      <c r="AG72">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
+        <v>0</v>
+      </c>
+      <c r="AK72">
+        <v>0</v>
+      </c>
+      <c r="AL72">
+        <v>0</v>
+      </c>
+      <c r="AM72">
+        <v>-1</v>
+      </c>
+      <c r="AN72">
+        <v>-1</v>
+      </c>
+      <c r="AO72">
+        <v>-1</v>
+      </c>
+      <c r="AP72">
+        <v>-1</v>
+      </c>
+      <c r="AQ72">
+        <v>0</v>
+      </c>
+      <c r="AR72">
+        <v>0</v>
+      </c>
+      <c r="AS72">
+        <v>0</v>
+      </c>
+      <c r="AT72">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Mushuc Runa SC</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Leones del Norte</t>
+        </is>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+      <c r="AA73">
+        <v>0</v>
+      </c>
+      <c r="AB73">
+        <v>0</v>
+      </c>
+      <c r="AC73">
+        <v>0</v>
+      </c>
+      <c r="AD73">
+        <v>0</v>
+      </c>
+      <c r="AE73">
+        <v>0</v>
+      </c>
+      <c r="AF73">
+        <v>0</v>
+      </c>
+      <c r="AG73">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
+        <v>0</v>
+      </c>
+      <c r="AK73">
+        <v>0</v>
+      </c>
+      <c r="AL73">
+        <v>0</v>
+      </c>
+      <c r="AM73">
+        <v>-1</v>
+      </c>
+      <c r="AN73">
+        <v>-1</v>
+      </c>
+      <c r="AO73">
+        <v>-1</v>
+      </c>
+      <c r="AP73">
+        <v>-1</v>
+      </c>
+      <c r="AQ73">
+        <v>0</v>
+      </c>
+      <c r="AR73">
+        <v>0</v>
+      </c>
+      <c r="AS73">
+        <v>0</v>
+      </c>
+      <c r="AT73">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="O17">
-        <v>5.65</v>
+        <v>5.1</v>
       </c>
       <c r="P17">
-        <v>12.3</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T17">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="U17">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V17">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W17">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z17">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA17">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB17">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AC17">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AD17">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AE17">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF17">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AG17">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK17">
-        <v>3.86</v>
+        <v>3.4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="O18">
-        <v>5.1</v>
+        <v>5.65</v>
       </c>
       <c r="P18">
-        <v>8</v>
+        <v>12.3</v>
       </c>
       <c r="Q18">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="R18">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="S18">
+        <v>1.22</v>
+      </c>
+      <c r="T18">
+        <v>3.5</v>
+      </c>
+      <c r="U18">
+        <v>2</v>
+      </c>
+      <c r="V18">
+        <v>1.68</v>
+      </c>
+      <c r="W18">
         <v>1.17</v>
-      </c>
-      <c r="T18">
-        <v>4.5</v>
-      </c>
-      <c r="U18">
-        <v>2.06</v>
-      </c>
-      <c r="V18">
-        <v>1.66</v>
-      </c>
-      <c r="W18">
-        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
       <c r="Y18">
+        <v>1.08</v>
+      </c>
+      <c r="Z18">
+        <v>5.6</v>
+      </c>
+      <c r="AA18">
+        <v>1.36</v>
+      </c>
+      <c r="AB18">
+        <v>3</v>
+      </c>
+      <c r="AC18">
+        <v>1.94</v>
+      </c>
+      <c r="AD18">
+        <v>1.75</v>
+      </c>
+      <c r="AE18">
+        <v>1.29</v>
+      </c>
+      <c r="AF18">
+        <v>1.83</v>
+      </c>
+      <c r="AG18">
+        <v>1.84</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.07</v>
       </c>
-      <c r="Z18">
-        <v>5.75</v>
-      </c>
-      <c r="AA18">
-        <v>1.44</v>
-      </c>
-      <c r="AB18">
-        <v>2.62</v>
-      </c>
-      <c r="AC18">
-        <v>2.02</v>
-      </c>
-      <c r="AD18">
-        <v>1.69</v>
-      </c>
-      <c r="AE18">
-        <v>1.25</v>
-      </c>
-      <c r="AF18">
-        <v>1.63</v>
-      </c>
-      <c r="AG18">
-        <v>2.1</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.1</v>
-      </c>
       <c r="AK18">
-        <v>3.4</v>
+        <v>3.86</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="R5">
         <v>2.12</v>
@@ -1166,7 +1166,7 @@
         <v>1.83</v>
       </c>
       <c r="AB5">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC5">
         <v>2.97</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
         <v>2.3</v>
@@ -1320,7 +1320,7 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z6">
         <v>3.34</v>
@@ -1329,7 +1329,7 @@
         <v>1.86</v>
       </c>
       <c r="AB6">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AC6">
         <v>3.08</v>
@@ -1450,37 +1450,37 @@
         </is>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O7">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="P7">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q7">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="R7">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S7">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T7">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="U7">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V7">
         <v>1.27</v>
       </c>
       <c r="W7">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
         <v>1.38</v>
@@ -1495,7 +1495,7 @@
         <v>1.57</v>
       </c>
       <c r="AC7">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="AD7">
         <v>1.19</v>
@@ -1504,10 +1504,10 @@
         <v>1</v>
       </c>
       <c r="AF7">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG7">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.32</v>
       </c>
       <c r="AK7">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="O8">
         <v>3.5</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Q55">
         <v>2.03</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q59">
         <v>2.73</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q61">
         <v>2.77</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q62">
         <v>3</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q64">
         <v>2.5</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
         <v>4</v>
       </c>
       <c r="Q26">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="R26">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U26">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z26">
-        <v>3.74</v>
+        <v>3.18</v>
       </c>
       <c r="AA26">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AB26">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AC26">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AD26">
+        <v>1.26</v>
+      </c>
+      <c r="AE26">
+        <v>1.06</v>
+      </c>
+      <c r="AF26">
+        <v>1.83</v>
+      </c>
+      <c r="AG26">
+        <v>1.9</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
         <v>1.33</v>
       </c>
-      <c r="AE26">
-        <v>1.09</v>
-      </c>
-      <c r="AF26">
-        <v>1.67</v>
-      </c>
-      <c r="AG26">
-        <v>2.05</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.3</v>
-      </c>
       <c r="AK26">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
         <v>4</v>
       </c>
       <c r="Q27">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="R27">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="S27">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>3.18</v>
+        <v>3.74</v>
       </c>
       <c r="AA27">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AB27">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AC27">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AD27">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF27">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q42">
         <v>7.21</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -2929,52 +2929,52 @@
         <v>2.4</v>
       </c>
       <c r="R16">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="S16">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z16">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AA16">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AB16">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AC16">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="AD16">
         <v>1.34</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF16">
         <v>1.65</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O32">
         <v>2.85</v>
       </c>
       <c r="P32">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q32">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R32">
         <v>1.85</v>
       </c>
       <c r="S32">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="T32">
         <v>2.19</v>
       </c>
       <c r="U32">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="V32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y32">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z32">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AA32">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AB32">
         <v>1.4</v>
       </c>
       <c r="AC32">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AD32">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE32">
         <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AG32">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AK32">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -9111,49 +9111,49 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="O54">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q54">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R54">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S54">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T54">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="U54">
         <v>2.59</v>
       </c>
       <c r="V54">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W54">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z54">
-        <v>3.93</v>
+        <v>3.85</v>
       </c>
       <c r="AA54">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB54">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC54">
         <v>2.8</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
         <v>4</v>
       </c>
       <c r="Q26">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="R26">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="S26">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>3.18</v>
+        <v>3.74</v>
       </c>
       <c r="AA26">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AB26">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AD26">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF26">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O27">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
         <v>4</v>
       </c>
       <c r="Q27">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="R27">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U27">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V27">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z27">
-        <v>3.74</v>
+        <v>3.18</v>
       </c>
       <c r="AA27">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AB27">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AC27">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AD27">
+        <v>1.26</v>
+      </c>
+      <c r="AE27">
+        <v>1.06</v>
+      </c>
+      <c r="AF27">
+        <v>1.83</v>
+      </c>
+      <c r="AG27">
+        <v>1.9</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.33</v>
       </c>
-      <c r="AE27">
-        <v>1.09</v>
-      </c>
-      <c r="AF27">
-        <v>1.67</v>
-      </c>
-      <c r="AG27">
-        <v>2.05</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.3</v>
-      </c>
       <c r="AK27">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O5">
         <v>3.3</v>
       </c>
       <c r="P5">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="Q5">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="R5">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S5">
+        <v>1.33</v>
+      </c>
+      <c r="T5">
+        <v>2.91</v>
+      </c>
+      <c r="U5">
+        <v>2.63</v>
+      </c>
+      <c r="V5">
+        <v>1.43</v>
+      </c>
+      <c r="W5">
+        <v>1.07</v>
+      </c>
+      <c r="X5">
+        <v>1.01</v>
+      </c>
+      <c r="Y5">
+        <v>1.21</v>
+      </c>
+      <c r="Z5">
+        <v>3.58</v>
+      </c>
+      <c r="AA5">
+        <v>1.74</v>
+      </c>
+      <c r="AB5">
+        <v>1.98</v>
+      </c>
+      <c r="AC5">
+        <v>2.74</v>
+      </c>
+      <c r="AD5">
         <v>1.35</v>
       </c>
-      <c r="T5">
-        <v>2.82</v>
-      </c>
-      <c r="U5">
-        <v>2.62</v>
-      </c>
-      <c r="V5">
-        <v>1.4</v>
-      </c>
-      <c r="W5">
-        <v>1.06</v>
-      </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
-      <c r="Y5">
-        <v>1.24</v>
-      </c>
-      <c r="Z5">
-        <v>3.34</v>
-      </c>
-      <c r="AA5">
-        <v>1.83</v>
-      </c>
-      <c r="AB5">
-        <v>1.8</v>
-      </c>
-      <c r="AC5">
-        <v>2.97</v>
-      </c>
-      <c r="AD5">
-        <v>1.3</v>
-      </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG5">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
         <v>3.2</v>
       </c>
       <c r="P6">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R6">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z6">
-        <v>3.34</v>
+        <v>3.76</v>
       </c>
       <c r="AA6">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AB6">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AC6">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD6">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG6">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="O7">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="P7">
         <v>2.25</v>
       </c>
       <c r="Q7">
-        <v>3.26</v>
+        <v>3.88</v>
       </c>
       <c r="R7">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="S7">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T7">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="U7">
         <v>3.3</v>
       </c>
       <c r="V7">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W7">
         <v>1.03</v>
@@ -1483,31 +1483,31 @@
         <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="Z7">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AA7">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AB7">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC7">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AD7">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE7">
         <v>1</v>
       </c>
       <c r="AF7">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AG7">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.32</v>
       </c>
       <c r="AK7">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         <v>1.24</v>
       </c>
       <c r="Z16">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="AA16">
         <v>1.76</v>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3575,25 +3575,25 @@
         <v>4.9</v>
       </c>
       <c r="P20">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="Q20">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="R20">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T20">
         <v>3.16</v>
       </c>
       <c r="U20">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W20">
         <v>1.12</v>
@@ -3602,25 +3602,25 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="AA20">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB20">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AD20">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE20">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
         <v>1.85</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="O22">
         <v>3.05</v>
       </c>
       <c r="P22">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="Q22">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="R22">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S22">
         <v>1.53</v>
@@ -3934,10 +3934,10 @@
         <v>2.69</v>
       </c>
       <c r="AA22">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="AB22">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC22">
         <v>4.2</v>
@@ -3949,7 +3949,7 @@
         <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG22">
         <v>1.8</v>
@@ -3968,7 +3968,7 @@
         <v>1.41</v>
       </c>
       <c r="AK22">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="O23">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="P23">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="Q23">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S23">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="T23">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U23">
         <v>3.6</v>
@@ -4091,31 +4091,31 @@
         <v>1.06</v>
       </c>
       <c r="Y23">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z23">
         <v>2.74</v>
       </c>
       <c r="AA23">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AB23">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC23">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AD23">
         <v>1.16</v>
       </c>
       <c r="AE23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
         <v>2.14</v>
       </c>
       <c r="AG23">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AK23">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q24">
         <v>2.38</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S24">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W24">
         <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
         <v>1.19</v>
       </c>
       <c r="Z24">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="AA24">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB24">
         <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AD24">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE24">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK24">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,31 +4387,31 @@
         <v>1.74</v>
       </c>
       <c r="O25">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="Q25">
+        <v>2.23</v>
+      </c>
+      <c r="R25">
         <v>2.26</v>
       </c>
-      <c r="R25">
-        <v>2.24</v>
-      </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="U25">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="V25">
         <v>1.46</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4420,28 +4420,28 @@
         <v>1.23</v>
       </c>
       <c r="Z25">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="AA25">
         <v>1.72</v>
       </c>
       <c r="AB25">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC25">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="AD25">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG25">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK25">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="Q26">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R26">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U26">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V26">
         <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AA26">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB26">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC26">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE26">
         <v>1.09</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG26">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK26">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="Q27">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="R27">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
         <v>1.42</v>
@@ -4731,10 +4731,10 @@
         <v>2.65</v>
       </c>
       <c r="U27">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W27">
         <v>1.04</v>
@@ -4743,22 +4743,22 @@
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>3.18</v>
+        <v>3.47</v>
       </c>
       <c r="AA27">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AC27">
         <v>3.4</v>
       </c>
       <c r="AD27">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
@@ -4767,7 +4767,7 @@
         <v>1.83</v>
       </c>
       <c r="AG27">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,25 +4873,25 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.83</v>
+        <v>3.97</v>
       </c>
       <c r="O28">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="P28">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q28">
-        <v>5.03</v>
+        <v>4.2</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S28">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T28">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U28">
         <v>3.6</v>
@@ -4903,34 +4903,34 @@
         <v>1.01</v>
       </c>
       <c r="X28">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y28">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z28">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AA28">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB28">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC28">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="AD28">
         <v>1.18</v>
       </c>
       <c r="AE28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG28">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK28">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,13 +5039,13 @@
         <v>1.7</v>
       </c>
       <c r="O29">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="Q29">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R29">
         <v>2</v>
@@ -5054,7 +5054,7 @@
         <v>1.5</v>
       </c>
       <c r="T29">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="U29">
         <v>3.8</v>
@@ -5066,16 +5066,16 @@
         <v>1.02</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y29">
         <v>1.5</v>
       </c>
       <c r="Z29">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="AA29">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="AB29">
         <v>1.41</v>
@@ -5084,13 +5084,13 @@
         <v>5.25</v>
       </c>
       <c r="AD29">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE29">
         <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AG29">
         <v>1.57</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="AK29">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O30">
         <v>3.1</v>
       </c>
       <c r="P30">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q30">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R30">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="S30">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T30">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="U30">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="V30">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z30">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA30">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AB30">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC30">
-        <v>3.98</v>
+        <v>3.85</v>
       </c>
       <c r="AD30">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE30">
         <v>1.02</v>
       </c>
       <c r="AF30">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG30">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.31</v>
       </c>
       <c r="AK30">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5528,25 +5528,25 @@
         <v>2.4</v>
       </c>
       <c r="O32">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P32">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q32">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="R32">
         <v>1.85</v>
       </c>
       <c r="S32">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="T32">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="U32">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="V32">
         <v>1.22</v>
@@ -5558,10 +5558,10 @@
         <v>1.11</v>
       </c>
       <c r="Y32">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Z32">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AA32">
         <v>3</v>
@@ -5582,7 +5582,7 @@
         <v>2.23</v>
       </c>
       <c r="AG32">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.36</v>
       </c>
       <c r="AK32">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>2.98</v>
+        <v>2.48</v>
       </c>
       <c r="R36">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="S36">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T36">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V36">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W36">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z36">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AA36">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB36">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AC36">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD36">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE36">
         <v>1.04</v>
       </c>
       <c r="AF36">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AG36">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,25 +6340,25 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q37">
-        <v>5.11</v>
+        <v>4.85</v>
       </c>
       <c r="R37">
         <v>2.15</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U37">
         <v>2.59</v>
@@ -6376,16 +6376,16 @@
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="AA37">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB37">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AC37">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AD37">
         <v>1.32</v>
@@ -6394,10 +6394,10 @@
         <v>1.08</v>
       </c>
       <c r="AF37">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG37">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.21</v>
       </c>
       <c r="AK37">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q38">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R38">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S38">
         <v>1.33</v>
@@ -6524,10 +6524,10 @@
         <v>2.99</v>
       </c>
       <c r="U38">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
         <v>1.07</v>
@@ -6536,31 +6536,31 @@
         <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="AA38">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB38">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AC38">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD38">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG38">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,49 +6666,49 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O39">
         <v>3.75</v>
       </c>
       <c r="P39">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="Q39">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="R39">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T39">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="U39">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V39">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
         <v>1.11</v>
       </c>
       <c r="Z39">
-        <v>4.9</v>
+        <v>5.12</v>
       </c>
       <c r="AA39">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AB39">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="AC39">
         <v>2.33</v>
@@ -6720,10 +6720,10 @@
         <v>1.18</v>
       </c>
       <c r="AF39">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG39">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,61 +6832,61 @@
         <v>3.41</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P40">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q40">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="R40">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T40">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="U40">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V40">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z40">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="AA40">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AB40">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AC40">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AD40">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF40">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AK40">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="O42">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P42">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Q42">
-        <v>7.21</v>
+        <v>7</v>
       </c>
       <c r="R42">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="S42">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U42">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W42">
         <v>1.09</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
         <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AA42">
         <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC42">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD42">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE42">
         <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AG42">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.16</v>
+        <v>2.71</v>
       </c>
       <c r="AK42">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q44">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="R44">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="S44">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T44">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U44">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="V44">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.05</v>
+        <v>4.98</v>
       </c>
       <c r="AA44">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB44">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AC44">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AD44">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE44">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,25 +7644,25 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.13</v>
+        <v>1.56</v>
       </c>
       <c r="O45">
-        <v>3.65</v>
+        <v>3.32</v>
       </c>
       <c r="P45">
         <v>3.33</v>
       </c>
       <c r="Q45">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="R45">
         <v>2.3</v>
       </c>
       <c r="S45">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T45">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U45">
         <v>2.44</v>
@@ -7671,37 +7671,37 @@
         <v>1.48</v>
       </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z45">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="AA45">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AB45">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC45">
         <v>2.59</v>
       </c>
       <c r="AD45">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE45">
         <v>1.12</v>
       </c>
       <c r="AF45">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK45">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="O46">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="P46">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q46">
         <v>3.36</v>
@@ -7825,43 +7825,43 @@
         <v>1.4</v>
       </c>
       <c r="T46">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="U46">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V46">
         <v>1.36</v>
       </c>
       <c r="W46">
+        <v>1.04</v>
+      </c>
+      <c r="X46">
         <v>1.05</v>
-      </c>
-      <c r="X46">
-        <v>1.02</v>
       </c>
       <c r="Y46">
         <v>1.3</v>
       </c>
       <c r="Z46">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AA46">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AB46">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC46">
         <v>3.34</v>
       </c>
       <c r="AD46">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE46">
         <v>1.06</v>
       </c>
       <c r="AF46">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG46">
         <v>1.95</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK46">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8305,52 +8305,52 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="R49">
+        <v>1.96</v>
+      </c>
+      <c r="S49">
+        <v>1.43</v>
+      </c>
+      <c r="T49">
+        <v>2.75</v>
+      </c>
+      <c r="U49">
+        <v>3.06</v>
+      </c>
+      <c r="V49">
+        <v>1.33</v>
+      </c>
+      <c r="W49">
+        <v>1.04</v>
+      </c>
+      <c r="X49">
+        <v>1.03</v>
+      </c>
+      <c r="Y49">
+        <v>1.33</v>
+      </c>
+      <c r="Z49">
+        <v>2.97</v>
+      </c>
+      <c r="AA49">
         <v>2.07</v>
       </c>
-      <c r="S49">
-        <v>1.36</v>
-      </c>
-      <c r="T49">
-        <v>2.77</v>
-      </c>
-      <c r="U49">
-        <v>2.88</v>
-      </c>
-      <c r="V49">
-        <v>1.36</v>
-      </c>
-      <c r="W49">
-        <v>1.06</v>
-      </c>
-      <c r="X49">
-        <v>1.01</v>
-      </c>
-      <c r="Y49">
-        <v>1.28</v>
-      </c>
-      <c r="Z49">
-        <v>3.25</v>
-      </c>
-      <c r="AA49">
-        <v>1.92</v>
-      </c>
       <c r="AB49">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AC49">
         <v>3.05</v>
       </c>
       <c r="AD49">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE49">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF49">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG49">
         <v>2</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK49">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="O50">
-        <v>3.68</v>
+        <v>3.81</v>
       </c>
       <c r="P50">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="Q50">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S50">
         <v>1.24</v>
@@ -8480,7 +8480,7 @@
         <v>3.6</v>
       </c>
       <c r="U50">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="V50">
         <v>1.62</v>
@@ -8498,25 +8498,25 @@
         <v>5.5</v>
       </c>
       <c r="AA50">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB50">
         <v>2.55</v>
       </c>
       <c r="AC50">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD50">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE50">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF50">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG50">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="O51">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P51">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="Q51">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R51">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="S51">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T51">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="U51">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V51">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="W51">
         <v>1.22</v>
@@ -8655,10 +8655,10 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z51">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA51">
         <v>1.29</v>
@@ -8670,32 +8670,32 @@
         <v>1.8</v>
       </c>
       <c r="AD51">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AE51">
         <v>1.4</v>
       </c>
       <c r="AF51">
+        <v>1.25</v>
+      </c>
+      <c r="AG51">
+        <v>3.25</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.28</v>
       </c>
-      <c r="AG51">
-        <v>3.1</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.35</v>
-      </c>
       <c r="AK51">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="O52">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P52">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="Q52">
         <v>2.2</v>
       </c>
       <c r="R52">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="S52">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T52">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="U52">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="V52">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W52">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
         <v>1.06</v>
       </c>
       <c r="Y52">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AA52">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB52">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC52">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="AD52">
+        <v>1.32</v>
+      </c>
+      <c r="AE52">
+        <v>1.08</v>
+      </c>
+      <c r="AF52">
+        <v>1.77</v>
+      </c>
+      <c r="AG52">
+        <v>1.94</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.28</v>
       </c>
-      <c r="AE52">
-        <v>1.07</v>
-      </c>
-      <c r="AF52">
-        <v>1.8</v>
-      </c>
-      <c r="AG52">
-        <v>1.9</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.3</v>
-      </c>
       <c r="AK52">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="O53">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="P53">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="Q53">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="R53">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="S53">
         <v>1.42</v>
@@ -8969,43 +8969,43 @@
         <v>2.65</v>
       </c>
       <c r="U53">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V53">
         <v>1.36</v>
       </c>
       <c r="W53">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z53">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AA53">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB53">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AC53">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AD53">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE53">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF53">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG53">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK53">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P54">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="Q54">
         <v>2.4</v>
@@ -9162,7 +9162,7 @@
         <v>1.33</v>
       </c>
       <c r="AE54">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
         <v>1.65</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK54">
         <v>1.82</v>
@@ -9283,55 +9283,55 @@
         <v>5.45</v>
       </c>
       <c r="Q55">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="R55">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S55">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T55">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="U55">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="V55">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="W55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X55">
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z55">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA55">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AB55">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AC55">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AD55">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE55">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF55">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="AG55">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9443,28 +9443,28 @@
         <v>3.3</v>
       </c>
       <c r="P56">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
       <c r="Q56">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R56">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S56">
         <v>1.36</v>
       </c>
       <c r="T56">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="U56">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="V56">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X56">
         <v>1</v>
@@ -9473,19 +9473,19 @@
         <v>1.28</v>
       </c>
       <c r="Z56">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="AA56">
         <v>1.92</v>
       </c>
       <c r="AB56">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC56">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="AD56">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE56">
         <v>1.07</v>
@@ -9510,7 +9510,7 @@
         <v>1.27</v>
       </c>
       <c r="AK56">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O57">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P57">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="Q57">
         <v>3.6</v>
@@ -9615,13 +9615,13 @@
         <v>1.95</v>
       </c>
       <c r="S57">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T57">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="U57">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V57">
         <v>1.32</v>
@@ -9630,25 +9630,25 @@
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y57">
         <v>1.39</v>
       </c>
       <c r="Z57">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AA57">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AB57">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC57">
         <v>4.6</v>
       </c>
       <c r="AD57">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE57">
         <v>1.02</v>
@@ -9657,7 +9657,7 @@
         <v>1.9</v>
       </c>
       <c r="AG57">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AK57">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9935,55 +9935,55 @@
         <v>3</v>
       </c>
       <c r="Q59">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="S59">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T59">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="U59">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="V59">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W59">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X59">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y59">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z59">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AA59">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="AB59">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC59">
-        <v>3.68</v>
+        <v>3.96</v>
       </c>
       <c r="AD59">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE59">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF59">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AG59">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK59">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,16 +10089,16 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
       <c r="O60">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P60">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q60">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R60">
         <v>2.12</v>
@@ -10107,43 +10107,43 @@
         <v>1.36</v>
       </c>
       <c r="T60">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="U60">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="V60">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W60">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z60">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AA60">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB60">
         <v>1.81</v>
       </c>
       <c r="AC60">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AD60">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE60">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF60">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG60">
         <v>1.97</v>
@@ -10162,7 +10162,7 @@
         <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>3.3</v>
       </c>
       <c r="Q61">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="R61">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S61">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T61">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U61">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V61">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W61">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X61">
         <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z61">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="AA61">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="AB61">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC61">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="AD61">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AE61">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF61">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AG61">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10421,46 +10421,46 @@
         <v>2.85</v>
       </c>
       <c r="P62">
+        <v>3.1</v>
+      </c>
+      <c r="Q62">
         <v>3.05</v>
       </c>
-      <c r="Q62">
-        <v>3</v>
-      </c>
       <c r="R62">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S62">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T62">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U62">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V62">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W62">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
         <v>1.36</v>
       </c>
       <c r="Z62">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA62">
         <v>2.3</v>
       </c>
       <c r="AB62">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC62">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AD62">
         <v>1.16</v>
@@ -10469,10 +10469,10 @@
         <v>1.01</v>
       </c>
       <c r="AF62">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG62">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK62">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,16 +10587,16 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="R63">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="S63">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T63">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="U63">
         <v>3.5</v>
@@ -10605,22 +10605,22 @@
         <v>1.25</v>
       </c>
       <c r="W63">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X63">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z63">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AA63">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AB63">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AC63">
         <v>5</v>
@@ -10629,13 +10629,13 @@
         <v>1.1</v>
       </c>
       <c r="AE63">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF63">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AG63">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK63">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,16 +10750,16 @@
         <v>3.85</v>
       </c>
       <c r="Q64">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R64">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S64">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T64">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="U64">
         <v>3.2</v>
@@ -10771,22 +10771,22 @@
         <v>1.02</v>
       </c>
       <c r="X64">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y64">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z64">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA64">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AB64">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC64">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="AD64">
         <v>1.18</v>
@@ -10795,7 +10795,7 @@
         <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG64">
         <v>1.75</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK64">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,22 +10904,22 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
         <v>3.4</v>
       </c>
       <c r="P65">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q65">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="R65">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S65">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T65">
         <v>3</v>
@@ -10931,37 +10931,37 @@
         <v>1.41</v>
       </c>
       <c r="W65">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X65">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="AA65">
+        <v>1.9</v>
+      </c>
+      <c r="AB65">
         <v>1.88</v>
-      </c>
-      <c r="AB65">
-        <v>1.84</v>
       </c>
       <c r="AC65">
         <v>3.15</v>
       </c>
       <c r="AD65">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE65">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF65">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG65">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK65">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="O66">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P66">
         <v>2.35</v>
@@ -11082,49 +11082,49 @@
         <v>2.08</v>
       </c>
       <c r="S66">
+        <v>1.39</v>
+      </c>
+      <c r="T66">
+        <v>3</v>
+      </c>
+      <c r="U66">
+        <v>2.6</v>
+      </c>
+      <c r="V66">
+        <v>1.43</v>
+      </c>
+      <c r="W66">
+        <v>1.08</v>
+      </c>
+      <c r="X66">
+        <v>1</v>
+      </c>
+      <c r="Y66">
+        <v>1.27</v>
+      </c>
+      <c r="Z66">
+        <v>3.3</v>
+      </c>
+      <c r="AA66">
+        <v>1.89</v>
+      </c>
+      <c r="AB66">
+        <v>2</v>
+      </c>
+      <c r="AC66">
+        <v>3</v>
+      </c>
+      <c r="AD66">
         <v>1.35</v>
       </c>
-      <c r="T66">
-        <v>2.95</v>
-      </c>
-      <c r="U66">
-        <v>2.75</v>
-      </c>
-      <c r="V66">
-        <v>1.4</v>
-      </c>
-      <c r="W66">
-        <v>1.06</v>
-      </c>
-      <c r="X66">
-        <v>1.01</v>
-      </c>
-      <c r="Y66">
-        <v>1.26</v>
-      </c>
-      <c r="Z66">
-        <v>3.4</v>
-      </c>
-      <c r="AA66">
-        <v>1.97</v>
-      </c>
-      <c r="AB66">
-        <v>1.95</v>
-      </c>
-      <c r="AC66">
-        <v>3.04</v>
-      </c>
-      <c r="AD66">
-        <v>1.32</v>
-      </c>
       <c r="AE66">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF66">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG66">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK66">
         <v>1.36</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL67">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU73"/>
+  <dimension ref="A1:AU75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-07 12:30:00</t>
+          <t>2026-09-07 12:15:00</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G11">
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-07 12:45:00</t>
+          <t>2026-09-07 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-07 13:00:00</t>
+          <t>2026-09-07 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G15">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G16">
@@ -2926,55 +2926,55 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3038,22 +3038,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="R17">
-        <v>2.59</v>
+        <v>2.17</v>
       </c>
       <c r="S17">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Z17">
-        <v>5.75</v>
+        <v>3.97</v>
       </c>
       <c r="AA17">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AB17">
-        <v>2.62</v>
+        <v>2.01</v>
       </c>
       <c r="AC17">
-        <v>2.02</v>
+        <v>2.78</v>
       </c>
       <c r="AD17">
-        <v>1.69</v>
+        <v>1.34</v>
       </c>
       <c r="AE17">
+        <v>1.15</v>
+      </c>
+      <c r="AF17">
+        <v>1.65</v>
+      </c>
+      <c r="AG17">
+        <v>2.11</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.25</v>
       </c>
-      <c r="AF17">
-        <v>1.63</v>
-      </c>
-      <c r="AG17">
-        <v>2.1</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.1</v>
-      </c>
       <c r="AK17">
-        <v>3.4</v>
+        <v>1.82</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="O18">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>12.3</v>
+        <v>5.75</v>
       </c>
       <c r="Q18">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="R18">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="V18">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z18">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA18">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB18">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AC18">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AD18">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE18">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AK18">
-        <v>3.86</v>
+        <v>3.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3364,22 +3364,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK20">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G21">
@@ -3728,68 +3728,68 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-09-07 13:30:00</t>
+          <t>2026-09-07 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G22">
@@ -3891,68 +3891,68 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N22">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="O23">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="P23">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="Q23">
-        <v>2.5</v>
+        <v>3.38</v>
       </c>
       <c r="R23">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S23">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="T23">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="U23">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="V23">
         <v>1.3</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X23">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="Z23">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AA23">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AB23">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC23">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD23">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF23">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AG23">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AK23">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-07 13:45:00</t>
+          <t>2026-09-07 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="O25">
+        <v>3.07</v>
+      </c>
+      <c r="P25">
+        <v>3.65</v>
+      </c>
+      <c r="Q25">
+        <v>2.5</v>
+      </c>
+      <c r="R25">
+        <v>1.95</v>
+      </c>
+      <c r="S25">
+        <v>1.58</v>
+      </c>
+      <c r="T25">
+        <v>2.4</v>
+      </c>
+      <c r="U25">
         <v>3.6</v>
       </c>
-      <c r="P25">
-        <v>3.75</v>
-      </c>
-      <c r="Q25">
-        <v>2.23</v>
-      </c>
-      <c r="R25">
-        <v>2.26</v>
-      </c>
-      <c r="S25">
-        <v>1.31</v>
-      </c>
-      <c r="T25">
-        <v>3.26</v>
-      </c>
-      <c r="U25">
-        <v>2.63</v>
-      </c>
       <c r="V25">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
+        <v>1.06</v>
+      </c>
+      <c r="Y25">
+        <v>1.47</v>
+      </c>
+      <c r="Z25">
+        <v>2.74</v>
+      </c>
+      <c r="AA25">
+        <v>2.3</v>
+      </c>
+      <c r="AB25">
+        <v>1.57</v>
+      </c>
+      <c r="AC25">
+        <v>4.5</v>
+      </c>
+      <c r="AD25">
+        <v>1.16</v>
+      </c>
+      <c r="AE25">
         <v>1.03</v>
       </c>
-      <c r="Y25">
-        <v>1.23</v>
-      </c>
-      <c r="Z25">
-        <v>3.84</v>
-      </c>
-      <c r="AA25">
-        <v>1.72</v>
-      </c>
-      <c r="AB25">
-        <v>2.03</v>
-      </c>
-      <c r="AC25">
-        <v>2.79</v>
-      </c>
-      <c r="AD25">
-        <v>1.36</v>
-      </c>
-      <c r="AE25">
-        <v>1.11</v>
-      </c>
       <c r="AF25">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="AG25">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="AK25">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:00</t>
+          <t>2026-09-07 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>4.02</v>
+        <v>3.2</v>
       </c>
       <c r="Q26">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z26">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="AA26">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="AD26">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE26">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AK26">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:00</t>
+          <t>2026-09-07 13:45:00</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>4.12</v>
+        <v>3.75</v>
       </c>
       <c r="Q27">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="R27">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="S27">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="T27">
-        <v>2.65</v>
+        <v>3.26</v>
       </c>
       <c r="U27">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="V27">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z27">
-        <v>3.47</v>
+        <v>3.84</v>
       </c>
       <c r="AA27">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB27">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="AC27">
-        <v>3.4</v>
+        <v>2.79</v>
       </c>
       <c r="AD27">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.97</v>
+        <v>1.88</v>
       </c>
       <c r="O28">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>2.08</v>
+        <v>4.02</v>
       </c>
       <c r="Q28">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="R28">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S28">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
-        <v>2.24</v>
+        <v>2.94</v>
       </c>
       <c r="U28">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="V28">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>2.66</v>
+        <v>3.9</v>
       </c>
       <c r="AA28">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AB28">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>3.85</v>
+        <v>2.83</v>
       </c>
       <c r="AD28">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AG28">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AK28">
-        <v>1.17</v>
+        <v>1.89</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="O29">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>5.3</v>
+        <v>4.12</v>
       </c>
       <c r="Q29">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R29">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="T29">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="U29">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="V29">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="Z29">
-        <v>2.32</v>
+        <v>3.47</v>
       </c>
       <c r="AA29">
-        <v>2.47</v>
+        <v>1.9</v>
       </c>
       <c r="AB29">
-        <v>1.41</v>
+        <v>1.86</v>
       </c>
       <c r="AC29">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD29">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AE29">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AG29">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,49 +5199,49 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.1</v>
+        <v>3.97</v>
       </c>
       <c r="O30">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="P30">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q30">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="R30">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="S30">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="T30">
-        <v>2.47</v>
+        <v>2.24</v>
       </c>
       <c r="U30">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="V30">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W30">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y30">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z30">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AA30">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AB30">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC30">
         <v>3.85</v>
@@ -5250,13 +5250,13 @@
         <v>1.18</v>
       </c>
       <c r="AE30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG30">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK30">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O32">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P32">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q32">
-        <v>3.24</v>
+        <v>2.8</v>
       </c>
       <c r="R32">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="S32">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="T32">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="U32">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="V32">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="W32">
         <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="Z32">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AA32">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="AB32">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AC32">
-        <v>5.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD32">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AE32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AG32">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="P34">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
-        <v>2.5</v>
+        <v>3.24</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="T34">
-        <v>3.04</v>
+        <v>2.31</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="V34">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="Z34">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
       <c r="AA34">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AC34">
-        <v>2.72</v>
+        <v>5.75</v>
       </c>
       <c r="AD34">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="AG34">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK34">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.71</v>
+        <v>3.75</v>
       </c>
       <c r="O35">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="P35">
-        <v>4.16</v>
+        <v>1.8</v>
       </c>
       <c r="Q35">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
+        <v>1.29</v>
+      </c>
+      <c r="T35">
+        <v>3.3</v>
+      </c>
+      <c r="U35">
+        <v>2.33</v>
+      </c>
+      <c r="V35">
+        <v>1.51</v>
+      </c>
+      <c r="W35">
+        <v>1.1</v>
+      </c>
+      <c r="X35">
+        <v>1.04</v>
+      </c>
+      <c r="Y35">
+        <v>1.17</v>
+      </c>
+      <c r="Z35">
+        <v>4.32</v>
+      </c>
+      <c r="AA35">
+        <v>1.67</v>
+      </c>
+      <c r="AB35">
+        <v>2.17</v>
+      </c>
+      <c r="AC35">
+        <v>2.48</v>
+      </c>
+      <c r="AD35">
+        <v>1.44</v>
+      </c>
+      <c r="AE35">
+        <v>1.14</v>
+      </c>
+      <c r="AF35">
+        <v>1.61</v>
+      </c>
+      <c r="AG35">
+        <v>2.2</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.25</v>
+      </c>
+      <c r="AK35">
         <v>1.22</v>
-      </c>
-      <c r="T35">
-        <v>3.66</v>
-      </c>
-      <c r="U35">
-        <v>2.11</v>
-      </c>
-      <c r="V35">
-        <v>1.63</v>
-      </c>
-      <c r="W35">
-        <v>1.13</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.1</v>
-      </c>
-      <c r="Z35">
-        <v>5.05</v>
-      </c>
-      <c r="AA35">
-        <v>1.44</v>
-      </c>
-      <c r="AB35">
-        <v>2.5</v>
-      </c>
-      <c r="AC35">
-        <v>2.25</v>
-      </c>
-      <c r="AD35">
-        <v>1.63</v>
-      </c>
-      <c r="AE35">
-        <v>1.19</v>
-      </c>
-      <c r="AF35">
-        <v>1.49</v>
-      </c>
-      <c r="AG35">
-        <v>2.44</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.21</v>
-      </c>
-      <c r="AK35">
-        <v>2.1</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q36">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="R36">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="T36">
-        <v>2.59</v>
+        <v>3.15</v>
       </c>
       <c r="U36">
-        <v>2.96</v>
+        <v>2.44</v>
       </c>
       <c r="V36">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="W36">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X36">
         <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>3.1</v>
+        <v>3.96</v>
       </c>
       <c r="AA36">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB36">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AC36">
-        <v>3.5</v>
+        <v>2.54</v>
       </c>
       <c r="AD36">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AE36">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF36">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AG36">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK36">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6298,22 +6298,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>1.67</v>
+        <v>4.1</v>
       </c>
       <c r="Q37">
-        <v>4.85</v>
+        <v>2.12</v>
       </c>
       <c r="R37">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T37">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="V37">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA37">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AB37">
-        <v>1.87</v>
+        <v>2.44</v>
       </c>
       <c r="AC37">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="AD37">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AF37">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.21</v>
       </c>
       <c r="AK37">
-        <v>1.14</v>
+        <v>2.09</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="R38">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T38">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
       <c r="U38">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
+        <v>1.28</v>
+      </c>
+      <c r="Z38">
+        <v>3.1</v>
+      </c>
+      <c r="AA38">
+        <v>2.02</v>
+      </c>
+      <c r="AB38">
+        <v>1.71</v>
+      </c>
+      <c r="AC38">
+        <v>3.5</v>
+      </c>
+      <c r="AD38">
+        <v>1.26</v>
+      </c>
+      <c r="AE38">
+        <v>1.04</v>
+      </c>
+      <c r="AF38">
+        <v>1.84</v>
+      </c>
+      <c r="AG38">
+        <v>1.85</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.24</v>
       </c>
-      <c r="Z38">
-        <v>3.83</v>
-      </c>
-      <c r="AA38">
-        <v>1.73</v>
-      </c>
-      <c r="AB38">
-        <v>2.04</v>
-      </c>
-      <c r="AC38">
-        <v>2.7</v>
-      </c>
-      <c r="AD38">
-        <v>1.36</v>
-      </c>
-      <c r="AE38">
-        <v>1.1</v>
-      </c>
-      <c r="AF38">
-        <v>1.85</v>
-      </c>
-      <c r="AG38">
-        <v>1.77</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.18</v>
-      </c>
       <c r="AK38">
-        <v>2.64</v>
+        <v>1.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="O39">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
+        <v>1.67</v>
+      </c>
+      <c r="Q39">
+        <v>4.85</v>
+      </c>
+      <c r="R39">
+        <v>2.15</v>
+      </c>
+      <c r="S39">
+        <v>1.3</v>
+      </c>
+      <c r="T39">
         <v>3.2</v>
       </c>
-      <c r="Q39">
-        <v>2.33</v>
-      </c>
-      <c r="R39">
-        <v>2.5</v>
-      </c>
-      <c r="S39">
-        <v>1.23</v>
-      </c>
-      <c r="T39">
-        <v>3.7</v>
-      </c>
       <c r="U39">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="V39">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="W39">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>5.12</v>
+        <v>3.4</v>
       </c>
       <c r="AA39">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AB39">
-        <v>2.48</v>
+        <v>1.87</v>
       </c>
       <c r="AC39">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="AD39">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="AE39">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="AG39">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK39">
-        <v>1.87</v>
+        <v>1.14</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.41</v>
+        <v>1.42</v>
       </c>
       <c r="O40">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="P40">
-        <v>1.98</v>
+        <v>6.25</v>
       </c>
       <c r="Q40">
-        <v>3.61</v>
+        <v>1.95</v>
       </c>
       <c r="R40">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="S40">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="T40">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="U40">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="V40">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z40">
-        <v>4.3</v>
+        <v>3.83</v>
       </c>
       <c r="AA40">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AB40">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="AC40">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD40">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AE40">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.78</v>
+        <v>1.18</v>
       </c>
       <c r="AK40">
-        <v>1.26</v>
+        <v>2.64</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="O41">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="P41">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q41">
-        <v>3.28</v>
+        <v>2.33</v>
       </c>
       <c r="R41">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="S41">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="T41">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="U41">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>3.5</v>
+        <v>5.12</v>
       </c>
       <c r="AA41">
-        <v>1.81</v>
+        <v>1.47</v>
       </c>
       <c r="AB41">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="AC41">
-        <v>2.98</v>
+        <v>2.33</v>
       </c>
       <c r="AD41">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AE41">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AG41">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK41">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-07 14:05:00</t>
+          <t>2026-09-07 14:00:00</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>6.25</v>
+        <v>3.41</v>
       </c>
       <c r="O42">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="P42">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="Q42">
-        <v>7</v>
+        <v>3.61</v>
       </c>
       <c r="R42">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T42">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V42">
         <v>1.51</v>
       </c>
       <c r="W42">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB42">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AC42">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AD42">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AG42">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>2.71</v>
+        <v>1.78</v>
       </c>
       <c r="AK42">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-09-07 14:15:00</t>
+          <t>2026-09-07 14:00:00</t>
         </is>
       </c>
     </row>
@@ -7271,27 +7271,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-09-07 14:30:00</t>
+          <t>2026-09-07 14:05:00</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.4</v>
+        <v>6.25</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="P44">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="Q44">
-        <v>3.08</v>
+        <v>7</v>
       </c>
       <c r="R44">
         <v>2.45</v>
       </c>
       <c r="S44">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T44">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U44">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="V44">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W44">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>4.98</v>
+        <v>4</v>
       </c>
       <c r="AA44">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AB44">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AC44">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AD44">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AE44">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AG44">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.3</v>
+        <v>2.71</v>
       </c>
       <c r="AK44">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-07 14:30:00</t>
+          <t>2026-09-07 14:15:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S45">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T45">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U45">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V45">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W45">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y45">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z45">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA45">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC45">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD45">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE45">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF45">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG45">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK45">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="O46">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q46">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
       <c r="R46">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="S46">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T46">
-        <v>2.61</v>
+        <v>3.1</v>
       </c>
       <c r="U46">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="V46">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W46">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>3.25</v>
+        <v>4.98</v>
       </c>
       <c r="AA46">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AB46">
+        <v>2.21</v>
+      </c>
+      <c r="AC46">
+        <v>2.35</v>
+      </c>
+      <c r="AD46">
         <v>1.57</v>
       </c>
-      <c r="AC46">
-        <v>3.34</v>
-      </c>
-      <c r="AD46">
-        <v>1.18</v>
-      </c>
       <c r="AE46">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF46">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AG46">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.3</v>
       </c>
       <c r="AK46">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.43</v>
+        <v>1.56</v>
       </c>
       <c r="O47">
+        <v>3.32</v>
+      </c>
+      <c r="P47">
+        <v>3.33</v>
+      </c>
+      <c r="Q47">
+        <v>2.06</v>
+      </c>
+      <c r="R47">
+        <v>2.3</v>
+      </c>
+      <c r="S47">
+        <v>1.3</v>
+      </c>
+      <c r="T47">
         <v>3.25</v>
       </c>
-      <c r="P47">
-        <v>2.6</v>
-      </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-07 15:00:00</t>
+          <t>2026-09-07 14:30:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK49">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-07 15:00:00</t>
+          <t>2026-09-07 14:30:00</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB50">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC50">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.3</v>
+        <v>2.97</v>
       </c>
       <c r="R51">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="S51">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="T51">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="U51">
-        <v>1.8</v>
+        <v>3.06</v>
       </c>
       <c r="V51">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="W51">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="Z51">
-        <v>7.5</v>
+        <v>2.97</v>
       </c>
       <c r="AA51">
+        <v>2.07</v>
+      </c>
+      <c r="AB51">
+        <v>1.75</v>
+      </c>
+      <c r="AC51">
+        <v>3.05</v>
+      </c>
+      <c r="AD51">
         <v>1.29</v>
       </c>
-      <c r="AB51">
-        <v>3.28</v>
-      </c>
-      <c r="AC51">
-        <v>1.8</v>
-      </c>
-      <c r="AD51">
-        <v>1.97</v>
-      </c>
       <c r="AE51">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="AF51">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AG51">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK51">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.79</v>
+        <v>2.23</v>
       </c>
       <c r="O52">
-        <v>3.1</v>
+        <v>3.81</v>
       </c>
       <c r="P52">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="Q52">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
       <c r="R52">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="S52">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="T52">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U52">
-        <v>2.91</v>
+        <v>2.15</v>
       </c>
       <c r="V52">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X52">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="Z52">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA52">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AB52">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="AC52">
-        <v>2.99</v>
+        <v>2.3</v>
       </c>
       <c r="AD52">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AF52">
-        <v>1.77</v>
+        <v>1.43</v>
       </c>
       <c r="AG52">
-        <v>1.94</v>
+        <v>2.63</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK52">
-        <v>1.94</v>
+        <v>1.45</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-09-07 15:30:00</t>
+          <t>2026-09-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="O53">
+        <v>4.1</v>
+      </c>
+      <c r="P53">
+        <v>2.67</v>
+      </c>
+      <c r="Q53">
+        <v>2.3</v>
+      </c>
+      <c r="R53">
+        <v>2.6</v>
+      </c>
+      <c r="S53">
+        <v>1.17</v>
+      </c>
+      <c r="T53">
+        <v>4.6</v>
+      </c>
+      <c r="U53">
+        <v>1.8</v>
+      </c>
+      <c r="V53">
+        <v>1.87</v>
+      </c>
+      <c r="W53">
+        <v>1.22</v>
+      </c>
+      <c r="X53">
+        <v>1.01</v>
+      </c>
+      <c r="Y53">
+        <v>1.05</v>
+      </c>
+      <c r="Z53">
+        <v>7.5</v>
+      </c>
+      <c r="AA53">
+        <v>1.29</v>
+      </c>
+      <c r="AB53">
         <v>3.28</v>
       </c>
-      <c r="P53">
-        <v>2.95</v>
-      </c>
-      <c r="Q53">
-        <v>2.85</v>
-      </c>
-      <c r="R53">
-        <v>2.08</v>
-      </c>
-      <c r="S53">
-        <v>1.42</v>
-      </c>
-      <c r="T53">
-        <v>2.65</v>
-      </c>
-      <c r="U53">
-        <v>2.88</v>
-      </c>
-      <c r="V53">
-        <v>1.36</v>
-      </c>
-      <c r="W53">
-        <v>1.07</v>
-      </c>
-      <c r="X53">
-        <v>1.04</v>
-      </c>
-      <c r="Y53">
-        <v>1.33</v>
-      </c>
-      <c r="Z53">
-        <v>3.18</v>
-      </c>
-      <c r="AA53">
-        <v>2.02</v>
-      </c>
-      <c r="AB53">
-        <v>1.68</v>
-      </c>
       <c r="AC53">
-        <v>3.65</v>
+        <v>1.8</v>
       </c>
       <c r="AD53">
-        <v>1.23</v>
+        <v>1.97</v>
       </c>
       <c r="AE53">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="AF53">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="AG53">
-        <v>1.89</v>
+        <v>3.25</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK53">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-09-07 15:30:00</t>
+          <t>2026-09-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="O54">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="P54">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="Q54">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="R54">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S54">
+        <v>1.38</v>
+      </c>
+      <c r="T54">
+        <v>3</v>
+      </c>
+      <c r="U54">
+        <v>2.91</v>
+      </c>
+      <c r="V54">
+        <v>1.39</v>
+      </c>
+      <c r="W54">
+        <v>1.06</v>
+      </c>
+      <c r="X54">
+        <v>1.06</v>
+      </c>
+      <c r="Y54">
+        <v>1.25</v>
+      </c>
+      <c r="Z54">
+        <v>3.3</v>
+      </c>
+      <c r="AA54">
+        <v>1.89</v>
+      </c>
+      <c r="AB54">
+        <v>1.88</v>
+      </c>
+      <c r="AC54">
+        <v>2.99</v>
+      </c>
+      <c r="AD54">
         <v>1.32</v>
-      </c>
-      <c r="T54">
-        <v>3.2</v>
-      </c>
-      <c r="U54">
-        <v>2.59</v>
-      </c>
-      <c r="V54">
-        <v>1.45</v>
-      </c>
-      <c r="W54">
-        <v>1.08</v>
-      </c>
-      <c r="X54">
-        <v>1.04</v>
-      </c>
-      <c r="Y54">
-        <v>1.21</v>
-      </c>
-      <c r="Z54">
-        <v>3.85</v>
-      </c>
-      <c r="AA54">
-        <v>1.78</v>
-      </c>
-      <c r="AB54">
-        <v>1.98</v>
-      </c>
-      <c r="AC54">
-        <v>2.8</v>
-      </c>
-      <c r="AD54">
-        <v>1.33</v>
       </c>
       <c r="AE54">
         <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG54">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK54">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.57</v>
+        <v>2.08</v>
       </c>
       <c r="O55">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P55">
-        <v>5.45</v>
+        <v>2.95</v>
       </c>
       <c r="Q55">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="R55">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="S55">
         <v>1.42</v>
       </c>
       <c r="T55">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U55">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="V55">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W55">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z55">
-        <v>2.92</v>
+        <v>3.18</v>
       </c>
       <c r="AA55">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB55">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC55">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="AD55">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE55">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="AG55">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AK55">
-        <v>2.23</v>
+        <v>1.66</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G56">
@@ -9440,61 +9440,61 @@
         <v>1.91</v>
       </c>
       <c r="O56">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P56">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="Q56">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R56">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S56">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T56">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="U56">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="V56">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W56">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z56">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="AA56">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AB56">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AC56">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD56">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE56">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF56">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG56">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK56">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-09-07 15:45:00</t>
+          <t>2026-09-07 15:30:00</t>
         </is>
       </c>
     </row>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="O57">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.55</v>
+        <v>5.45</v>
       </c>
       <c r="Q57">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="R57">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="S57">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T57">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="U57">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="V57">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W57">
+        <v>1.02</v>
+      </c>
+      <c r="X57">
+        <v>1.02</v>
+      </c>
+      <c r="Y57">
+        <v>1.31</v>
+      </c>
+      <c r="Z57">
+        <v>2.92</v>
+      </c>
+      <c r="AA57">
+        <v>2.05</v>
+      </c>
+      <c r="AB57">
+        <v>1.67</v>
+      </c>
+      <c r="AC57">
+        <v>3.58</v>
+      </c>
+      <c r="AD57">
+        <v>1.21</v>
+      </c>
+      <c r="AE57">
         <v>1.03</v>
       </c>
-      <c r="X57">
-        <v>1.08</v>
-      </c>
-      <c r="Y57">
-        <v>1.39</v>
-      </c>
-      <c r="Z57">
-        <v>2.73</v>
-      </c>
-      <c r="AA57">
-        <v>2.39</v>
-      </c>
-      <c r="AB57">
-        <v>1.63</v>
-      </c>
-      <c r="AC57">
-        <v>4.6</v>
-      </c>
-      <c r="AD57">
-        <v>1.18</v>
-      </c>
-      <c r="AE57">
-        <v>1.02</v>
-      </c>
       <c r="AF57">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AG57">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>1.36</v>
+        <v>2.23</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-09-07 15:45:00</t>
+          <t>2026-09-07 15:30:00</t>
         </is>
       </c>
     </row>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA58">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AB58">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-09-07 16:00:00</t>
+          <t>2026-09-07 15:45:00</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,55 +9926,55 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="O59">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="P59">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Q59">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="R59">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="S59">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T59">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="U59">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="V59">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W59">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X59">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y59">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z59">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="AA59">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="AB59">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC59">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="AD59">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE59">
         <v>1.02</v>
@@ -9983,7 +9983,7 @@
         <v>1.9</v>
       </c>
       <c r="AG59">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AK59">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-09-07 16:00:00</t>
+          <t>2026-09-07 15:45:00</t>
         </is>
       </c>
     </row>
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q60">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T60">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U60">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V60">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W60">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X60">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z60">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB60">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC60">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE60">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF60">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG60">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK60">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="O61">
+        <v>2.85</v>
+      </c>
+      <c r="P61">
         <v>3</v>
       </c>
-      <c r="P61">
-        <v>3.3</v>
-      </c>
       <c r="Q61">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="R61">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="S61">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T61">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="U61">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="V61">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W61">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X61">
         <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="Z61">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="AA61">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AB61">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC61">
-        <v>4.65</v>
+        <v>3.96</v>
       </c>
       <c r="AD61">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE61">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF61">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AG61">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK61">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="O62">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="P62">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q62">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="R62">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S62">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="T62">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="U62">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="V62">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W62">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z62">
-        <v>2.69</v>
+        <v>3.35</v>
       </c>
       <c r="AA62">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AB62">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="AC62">
-        <v>4.15</v>
+        <v>3.24</v>
       </c>
       <c r="AD62">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AE62">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF62">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG62">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK62">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q63">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="R63">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="S63">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="T63">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="U63">
         <v>3.5</v>
       </c>
       <c r="V63">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W63">
         <v>1.01</v>
       </c>
       <c r="X63">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y63">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="Z63">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="AA63">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AB63">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AC63">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AD63">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AE63">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF63">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AG63">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK63">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="O64">
+        <v>2.85</v>
+      </c>
+      <c r="P64">
+        <v>3.1</v>
+      </c>
+      <c r="Q64">
         <v>3.05</v>
       </c>
-      <c r="P64">
-        <v>3.85</v>
-      </c>
-      <c r="Q64">
-        <v>2.62</v>
-      </c>
       <c r="R64">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S64">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T64">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U64">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V64">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W64">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z64">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AA64">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AB64">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC64">
-        <v>3.88</v>
+        <v>4.15</v>
       </c>
       <c r="AD64">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE64">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF64">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG64">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK64">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O65">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P65">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q65">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R65">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="S65">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="T65">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="U65">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="V65">
+        <v>1.25</v>
+      </c>
+      <c r="W65">
+        <v>1.01</v>
+      </c>
+      <c r="X65">
+        <v>1.06</v>
+      </c>
+      <c r="Y65">
+        <v>1.51</v>
+      </c>
+      <c r="Z65">
+        <v>2.36</v>
+      </c>
+      <c r="AA65">
+        <v>2.52</v>
+      </c>
+      <c r="AB65">
         <v>1.41</v>
       </c>
-      <c r="W65">
-        <v>1.07</v>
-      </c>
-      <c r="X65">
+      <c r="AC65">
+        <v>5</v>
+      </c>
+      <c r="AD65">
+        <v>1.1</v>
+      </c>
+      <c r="AE65">
         <v>1.03</v>
       </c>
-      <c r="Y65">
-        <v>1.22</v>
-      </c>
-      <c r="Z65">
-        <v>3.54</v>
-      </c>
-      <c r="AA65">
-        <v>1.9</v>
-      </c>
-      <c r="AB65">
-        <v>1.88</v>
-      </c>
-      <c r="AC65">
-        <v>3.15</v>
-      </c>
-      <c r="AD65">
-        <v>1.31</v>
-      </c>
-      <c r="AE65">
-        <v>1.14</v>
-      </c>
       <c r="AF65">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AG65">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK65">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-09-07 16:15:00</t>
+          <t>2026-09-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.76</v>
+        <v>1.94</v>
       </c>
       <c r="O66">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="P66">
-        <v>2.35</v>
+        <v>3.85</v>
       </c>
       <c r="Q66">
-        <v>3.24</v>
+        <v>2.62</v>
       </c>
       <c r="R66">
         <v>2.08</v>
       </c>
       <c r="S66">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="U66">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="V66">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X66">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y66">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="Z66">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="AA66">
-        <v>1.89</v>
+        <v>2.19</v>
       </c>
       <c r="AB66">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AC66">
-        <v>3</v>
+        <v>3.88</v>
       </c>
       <c r="AD66">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AE66">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF66">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AG66">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-07 16:30:00</t>
+          <t>2026-09-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,27 +11183,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="O67">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>4.25</v>
+        <v>2.95</v>
       </c>
       <c r="Q67">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="R67">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S67">
+        <v>1.33</v>
+      </c>
+      <c r="T67">
+        <v>3</v>
+      </c>
+      <c r="U67">
+        <v>2.69</v>
+      </c>
+      <c r="V67">
+        <v>1.41</v>
+      </c>
+      <c r="W67">
+        <v>1.07</v>
+      </c>
+      <c r="X67">
+        <v>1.03</v>
+      </c>
+      <c r="Y67">
+        <v>1.22</v>
+      </c>
+      <c r="Z67">
+        <v>3.54</v>
+      </c>
+      <c r="AA67">
+        <v>1.9</v>
+      </c>
+      <c r="AB67">
+        <v>1.88</v>
+      </c>
+      <c r="AC67">
+        <v>3.15</v>
+      </c>
+      <c r="AD67">
         <v>1.31</v>
       </c>
-      <c r="T67">
-        <v>2.99</v>
-      </c>
-      <c r="U67">
-        <v>2.6</v>
-      </c>
-      <c r="V67">
-        <v>1.4</v>
-      </c>
-      <c r="W67">
-        <v>1.08</v>
-      </c>
-      <c r="X67">
-        <v>1</v>
-      </c>
-      <c r="Y67">
-        <v>1.24</v>
-      </c>
-      <c r="Z67">
-        <v>3.34</v>
-      </c>
-      <c r="AA67">
-        <v>1.85</v>
-      </c>
-      <c r="AB67">
-        <v>1.84</v>
-      </c>
-      <c r="AC67">
-        <v>3.14</v>
-      </c>
-      <c r="AD67">
-        <v>1.27</v>
-      </c>
       <c r="AE67">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF67">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AK67">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-09-07 18:00:00</t>
+          <t>2026-09-07 16:15:00</t>
         </is>
       </c>
     </row>
@@ -11346,27 +11346,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="O68">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="P68">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-09-07 19:30:00</t>
+          <t>2026-09-07 16:30:00</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="O69">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="P69">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q69">
-        <v>2.46</v>
+        <v>3.42</v>
       </c>
       <c r="R69">
+        <v>1.91</v>
+      </c>
+      <c r="S69">
+        <v>1.6</v>
+      </c>
+      <c r="T69">
         <v>2.18</v>
       </c>
-      <c r="S69">
-        <v>1.43</v>
-      </c>
-      <c r="T69">
-        <v>2.62</v>
-      </c>
       <c r="U69">
-        <v>2.95</v>
+        <v>3.72</v>
       </c>
       <c r="V69">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="W69">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="Y69">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="Z69">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="AA69">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB69">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AC69">
-        <v>3.85</v>
+        <v>5.43</v>
       </c>
       <c r="AD69">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE69">
         <v>1.04</v>
       </c>
       <c r="AF69">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG69">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK69">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-09-07 20:00:00</t>
+          <t>2026-09-07 17:00:00</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,80 +11719,80 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O70">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P70">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="Q70">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="R70">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="S70">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T70">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="U70">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="V70">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="W70">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y70">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z70">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA70">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AB70">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AC70">
-        <v>2.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD70">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AE70">
+        <v>1.06</v>
+      </c>
+      <c r="AF70">
+        <v>1.8</v>
+      </c>
+      <c r="AG70">
+        <v>1.87</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
         <v>1.22</v>
       </c>
-      <c r="AF70">
-        <v>1.55</v>
-      </c>
-      <c r="AG70">
-        <v>2.33</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>1.17</v>
-      </c>
       <c r="AK70">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-09-07 20:00:00</t>
+          <t>2026-09-07 18:00:00</t>
         </is>
       </c>
     </row>
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:00</t>
+          <t>2026-09-07 20:00:00</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:00</t>
+          <t>2026-09-07 20:00:00</t>
         </is>
       </c>
     </row>
@@ -12176,141 +12176,467 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+      <c r="AA73">
+        <v>0</v>
+      </c>
+      <c r="AB73">
+        <v>0</v>
+      </c>
+      <c r="AC73">
+        <v>0</v>
+      </c>
+      <c r="AD73">
+        <v>0</v>
+      </c>
+      <c r="AE73">
+        <v>0</v>
+      </c>
+      <c r="AF73">
+        <v>0</v>
+      </c>
+      <c r="AG73">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
+        <v>0</v>
+      </c>
+      <c r="AK73">
+        <v>0</v>
+      </c>
+      <c r="AL73">
+        <v>0</v>
+      </c>
+      <c r="AM73">
+        <v>-1</v>
+      </c>
+      <c r="AN73">
+        <v>-1</v>
+      </c>
+      <c r="AO73">
+        <v>-1</v>
+      </c>
+      <c r="AP73">
+        <v>-1</v>
+      </c>
+      <c r="AQ73">
+        <v>0</v>
+      </c>
+      <c r="AR73">
+        <v>0</v>
+      </c>
+      <c r="AS73">
+        <v>0</v>
+      </c>
+      <c r="AT73">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+      <c r="AC74">
+        <v>0</v>
+      </c>
+      <c r="AD74">
+        <v>0</v>
+      </c>
+      <c r="AE74">
+        <v>0</v>
+      </c>
+      <c r="AF74">
+        <v>0</v>
+      </c>
+      <c r="AG74">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ74">
+        <v>0</v>
+      </c>
+      <c r="AK74">
+        <v>0</v>
+      </c>
+      <c r="AL74">
+        <v>0</v>
+      </c>
+      <c r="AM74">
+        <v>-1</v>
+      </c>
+      <c r="AN74">
+        <v>-1</v>
+      </c>
+      <c r="AO74">
+        <v>-1</v>
+      </c>
+      <c r="AP74">
+        <v>-1</v>
+      </c>
+      <c r="AQ74">
+        <v>0</v>
+      </c>
+      <c r="AR74">
+        <v>0</v>
+      </c>
+      <c r="AS74">
+        <v>0</v>
+      </c>
+      <c r="AT74">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>Mushuc Runa SC</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Leones del Norte</t>
         </is>
       </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73" t="inlineStr">
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
-      </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>0</v>
-      </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
-        <v>0</v>
-      </c>
-      <c r="T73">
-        <v>0</v>
-      </c>
-      <c r="U73">
-        <v>0</v>
-      </c>
-      <c r="V73">
-        <v>0</v>
-      </c>
-      <c r="W73">
-        <v>0</v>
-      </c>
-      <c r="X73">
-        <v>0</v>
-      </c>
-      <c r="Y73">
-        <v>0</v>
-      </c>
-      <c r="Z73">
-        <v>0</v>
-      </c>
-      <c r="AA73">
-        <v>0</v>
-      </c>
-      <c r="AB73">
-        <v>0</v>
-      </c>
-      <c r="AC73">
-        <v>0</v>
-      </c>
-      <c r="AD73">
-        <v>0</v>
-      </c>
-      <c r="AE73">
-        <v>0</v>
-      </c>
-      <c r="AF73">
-        <v>0</v>
-      </c>
-      <c r="AG73">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>0</v>
-      </c>
-      <c r="AK73">
-        <v>0</v>
-      </c>
-      <c r="AL73">
-        <v>0</v>
-      </c>
-      <c r="AM73">
-        <v>-1</v>
-      </c>
-      <c r="AN73">
-        <v>-1</v>
-      </c>
-      <c r="AO73">
-        <v>-1</v>
-      </c>
-      <c r="AP73">
-        <v>-1</v>
-      </c>
-      <c r="AQ73">
-        <v>0</v>
-      </c>
-      <c r="AR73">
-        <v>0</v>
-      </c>
-      <c r="AS73">
-        <v>0</v>
-      </c>
-      <c r="AT73">
-        <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
+      <c r="N75">
+        <v>1.67</v>
+      </c>
+      <c r="O75">
+        <v>3.4</v>
+      </c>
+      <c r="P75">
+        <v>4.5</v>
+      </c>
+      <c r="Q75">
+        <v>2.22</v>
+      </c>
+      <c r="R75">
+        <v>2.16</v>
+      </c>
+      <c r="S75">
+        <v>1.42</v>
+      </c>
+      <c r="T75">
+        <v>2.65</v>
+      </c>
+      <c r="U75">
+        <v>3</v>
+      </c>
+      <c r="V75">
+        <v>1.33</v>
+      </c>
+      <c r="W75">
+        <v>1.07</v>
+      </c>
+      <c r="X75">
+        <v>1.03</v>
+      </c>
+      <c r="Y75">
+        <v>1.35</v>
+      </c>
+      <c r="Z75">
+        <v>3.03</v>
+      </c>
+      <c r="AA75">
+        <v>2.09</v>
+      </c>
+      <c r="AB75">
+        <v>1.69</v>
+      </c>
+      <c r="AC75">
+        <v>3.7</v>
+      </c>
+      <c r="AD75">
+        <v>1.23</v>
+      </c>
+      <c r="AE75">
+        <v>1.05</v>
+      </c>
+      <c r="AF75">
+        <v>2.04</v>
+      </c>
+      <c r="AG75">
+        <v>1.71</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
+        <v>1.25</v>
+      </c>
+      <c r="AK75">
+        <v>2.1</v>
+      </c>
+      <c r="AL75">
+        <v>0</v>
+      </c>
+      <c r="AM75">
+        <v>-1</v>
+      </c>
+      <c r="AN75">
+        <v>-1</v>
+      </c>
+      <c r="AO75">
+        <v>-1</v>
+      </c>
+      <c r="AP75">
+        <v>-1</v>
+      </c>
+      <c r="AQ75">
+        <v>0</v>
+      </c>
+      <c r="AR75">
+        <v>0</v>
+      </c>
+      <c r="AS75">
+        <v>0</v>
+      </c>
+      <c r="AT75">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
         <is>
           <t>2026-09-07 21:00:00</t>
         </is>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="P5">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="Q5">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="R5">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>2.91</v>
+        <v>3.21</v>
       </c>
       <c r="U5">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V5">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z5">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA5">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AB5">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AD5">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,28 +1287,28 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
-        <v>3.28</v>
+        <v>3.63</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S6">
         <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>3.19</v>
       </c>
       <c r="U6">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
         <v>1.44</v>
@@ -1320,31 +1320,31 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z6">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="AA6">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB6">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="O7">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="P7">
         <v>2.25</v>
       </c>
       <c r="Q7">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
       <c r="R7">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="S7">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="U7">
         <v>3.3</v>
@@ -1486,22 +1486,22 @@
         <v>1.49</v>
       </c>
       <c r="Z7">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AA7">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB7">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC7">
-        <v>4.35</v>
+        <v>4.61</v>
       </c>
       <c r="AD7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE7">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
         <v>1.97</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="O8">
         <v>3.5</v>
       </c>
       <c r="P8">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2428,61 +2428,61 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O13">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q13">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="S13">
         <v>1.37</v>
       </c>
       <c r="T13">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="U13">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="V13">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.26</v>
       </c>
       <c r="Z13">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA13">
         <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC13">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AD13">
         <v>1.28</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG13">
         <v>2</v>
@@ -3095,49 +3095,49 @@
         <v>2.17</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="AA17">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AB17">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC17">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AD17">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE17">
         <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="O18">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P18">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q18">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R18">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S18">
         <v>1.17</v>
@@ -3264,16 +3264,16 @@
         <v>4.5</v>
       </c>
       <c r="U18">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="V18">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
         <v>1.07</v>
@@ -3282,25 +3282,25 @@
         <v>5.75</v>
       </c>
       <c r="AA18">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AB18">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AC18">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AD18">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AE18">
         <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG18">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O19">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q19">
         <v>1.6</v>
@@ -3424,43 +3424,43 @@
         <v>1.22</v>
       </c>
       <c r="T19">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="AA19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB19">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AC19">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AD19">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AE19">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG19">
         <v>1.84</v>
@@ -3479,7 +3479,7 @@
         <v>1.03</v>
       </c>
       <c r="AK19">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3738,25 +3738,25 @@
         <v>4.9</v>
       </c>
       <c r="P21">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="R21">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S21">
         <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="U21">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V21">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W21">
         <v>1.12</v>
@@ -3768,28 +3768,28 @@
         <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA21">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AB21">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AC21">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AD21">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AE21">
         <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG21">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK21">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.58</v>
+        <v>2.73</v>
       </c>
       <c r="O23">
         <v>3.05</v>
       </c>
       <c r="P23">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="Q23">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="R23">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S23">
         <v>1.53</v>
       </c>
       <c r="T23">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="U23">
         <v>3.38</v>
@@ -4097,7 +4097,7 @@
         <v>2.69</v>
       </c>
       <c r="AA23">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AB23">
         <v>1.61</v>
@@ -4106,16 +4106,16 @@
         <v>4.2</v>
       </c>
       <c r="AD23">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE23">
         <v>1.01</v>
       </c>
       <c r="AF23">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AK23">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,46 +4384,46 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="O25">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="P25">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="Q25">
+        <v>2.6</v>
+      </c>
+      <c r="R25">
+        <v>1.97</v>
+      </c>
+      <c r="S25">
+        <v>1.44</v>
+      </c>
+      <c r="T25">
         <v>2.5</v>
       </c>
-      <c r="R25">
-        <v>1.95</v>
-      </c>
-      <c r="S25">
-        <v>1.58</v>
-      </c>
-      <c r="T25">
-        <v>2.4</v>
-      </c>
       <c r="U25">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
         <v>1.06</v>
       </c>
       <c r="Y25">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z25">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AA25">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AB25">
         <v>1.57</v>
@@ -4432,13 +4432,13 @@
         <v>4.5</v>
       </c>
       <c r="AD25">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE25">
         <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AG25">
         <v>1.73</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>1.98</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
         <v>3.2</v>
@@ -4559,43 +4559,43 @@
         <v>2.38</v>
       </c>
       <c r="R26">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V26">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z26">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="AA26">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB26">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC26">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AD26">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE26">
         <v>1.13</v>
@@ -4604,7 +4604,7 @@
         <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK26">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,28 +4710,28 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O27">
         <v>3.6</v>
       </c>
       <c r="P27">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q27">
         <v>2.23</v>
       </c>
       <c r="R27">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.26</v>
+        <v>3.08</v>
       </c>
       <c r="U27">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="V27">
         <v>1.46</v>
@@ -4752,13 +4752,13 @@
         <v>1.72</v>
       </c>
       <c r="AB27">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AC27">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="AD27">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE27">
         <v>1.11</v>
@@ -4767,7 +4767,7 @@
         <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O28">
         <v>3.6</v>
       </c>
       <c r="P28">
-        <v>4.02</v>
+        <v>3.6</v>
       </c>
       <c r="Q28">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="R28">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S28">
         <v>1.35</v>
@@ -4903,16 +4903,16 @@
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA28">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB28">
         <v>2</v>
@@ -4921,16 +4921,16 @@
         <v>2.83</v>
       </c>
       <c r="AD28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE28">
         <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P29">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="Q29">
         <v>2.52</v>
@@ -5051,43 +5051,43 @@
         <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T29">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U29">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="V29">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="AA29">
         <v>1.9</v>
       </c>
       <c r="AB29">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC29">
         <v>3.4</v>
       </c>
       <c r="AD29">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
         <v>1.83</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="O30">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="P30">
         <v>2.08</v>
@@ -5211,34 +5211,34 @@
         <v>4.2</v>
       </c>
       <c r="R30">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="T30">
         <v>2.24</v>
       </c>
       <c r="U30">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="V30">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
         <v>1.01</v>
       </c>
       <c r="X30">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y30">
         <v>1.37</v>
       </c>
       <c r="Z30">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="AA30">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB30">
         <v>1.57</v>
@@ -5256,7 +5256,7 @@
         <v>1.92</v>
       </c>
       <c r="AG30">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="AK30">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O31">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P31">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q31">
         <v>2.44</v>
@@ -5380,16 +5380,16 @@
         <v>1.5</v>
       </c>
       <c r="T31">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="U31">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="V31">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W31">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
         <v>1.07</v>
@@ -5398,7 +5398,7 @@
         <v>1.5</v>
       </c>
       <c r="Z31">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AA31">
         <v>2.47</v>
@@ -5416,10 +5416,10 @@
         <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AG31">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AK31">
         <v>2.05</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O32">
         <v>3.1</v>
       </c>
       <c r="P32">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q32">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R32">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S32">
         <v>1.46</v>
@@ -5549,7 +5549,7 @@
         <v>3.22</v>
       </c>
       <c r="V32">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W32">
         <v>1.04</v>
@@ -5558,31 +5558,31 @@
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA32">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AB32">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC32">
-        <v>3.85</v>
+        <v>3.98</v>
       </c>
       <c r="AD32">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE32">
         <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG32">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,43 +5851,43 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O34">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q34">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="R34">
         <v>1.85</v>
       </c>
       <c r="S34">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T34">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="U34">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="V34">
         <v>1.22</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X34">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Y34">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Z34">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AA34">
         <v>3</v>
@@ -5899,16 +5899,16 @@
         <v>5.75</v>
       </c>
       <c r="AD34">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE34">
         <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AG34">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="O35">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q35">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
         <v>1.29</v>
@@ -6035,13 +6035,13 @@
         <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="V35">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X35">
         <v>1.04</v>
@@ -6050,28 +6050,28 @@
         <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="AA35">
         <v>1.67</v>
       </c>
       <c r="AB35">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AC35">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="AD35">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE35">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF35">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="O36">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P36">
-        <v>2.96</v>
+        <v>4.1</v>
       </c>
       <c r="Q36">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="R36">
+        <v>2.5</v>
+      </c>
+      <c r="S36">
+        <v>1.22</v>
+      </c>
+      <c r="T36">
+        <v>3.55</v>
+      </c>
+      <c r="U36">
+        <v>2.2</v>
+      </c>
+      <c r="V36">
+        <v>1.65</v>
+      </c>
+      <c r="W36">
+        <v>1.13</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
+        <v>1.13</v>
+      </c>
+      <c r="Z36">
+        <v>5</v>
+      </c>
+      <c r="AA36">
+        <v>1.46</v>
+      </c>
+      <c r="AB36">
+        <v>2.42</v>
+      </c>
+      <c r="AC36">
         <v>2.25</v>
       </c>
-      <c r="S36">
-        <v>1.31</v>
-      </c>
-      <c r="T36">
-        <v>3.15</v>
-      </c>
-      <c r="U36">
-        <v>2.44</v>
-      </c>
-      <c r="V36">
-        <v>1.49</v>
-      </c>
-      <c r="W36">
-        <v>1.09</v>
-      </c>
-      <c r="X36">
-        <v>1.04</v>
-      </c>
-      <c r="Y36">
-        <v>1.18</v>
-      </c>
-      <c r="Z36">
-        <v>3.96</v>
-      </c>
-      <c r="AA36">
-        <v>1.75</v>
-      </c>
-      <c r="AB36">
-        <v>2.05</v>
-      </c>
-      <c r="AC36">
-        <v>2.54</v>
-      </c>
       <c r="AD36">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AE36">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF36">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AG36">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK36">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.7</v>
+        <v>3.75</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>4.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q37">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U37">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="V37">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AA37">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AB37">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AC37">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AD37">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AE37">
+        <v>1.14</v>
+      </c>
+      <c r="AF37">
+        <v>1.61</v>
+      </c>
+      <c r="AG37">
+        <v>2.2</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>1.24</v>
+      </c>
+      <c r="AK37">
         <v>1.21</v>
-      </c>
-      <c r="AF37">
-        <v>1.49</v>
-      </c>
-      <c r="AG37">
-        <v>2.4</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.21</v>
-      </c>
-      <c r="AK37">
-        <v>2.09</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q38">
-        <v>2.48</v>
+        <v>4.49</v>
       </c>
       <c r="R38">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="S38">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T38">
-        <v>2.59</v>
+        <v>3.18</v>
       </c>
       <c r="U38">
-        <v>2.96</v>
+        <v>2.43</v>
       </c>
       <c r="V38">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="W38">
+        <v>1.07</v>
+      </c>
+      <c r="X38">
         <v>1.02</v>
       </c>
-      <c r="X38">
-        <v>1.04</v>
-      </c>
       <c r="Y38">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z38">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA38">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AB38">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AC38">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="AD38">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="AG38">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>1.8</v>
+        <v>1.16</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>4.85</v>
+        <v>2.41</v>
       </c>
       <c r="R39">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="U39">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="V39">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="W39">
+        <v>1.06</v>
+      </c>
+      <c r="X39">
+        <v>1.04</v>
+      </c>
+      <c r="Y39">
+        <v>1.33</v>
+      </c>
+      <c r="Z39">
+        <v>3.08</v>
+      </c>
+      <c r="AA39">
+        <v>1.99</v>
+      </c>
+      <c r="AB39">
+        <v>1.73</v>
+      </c>
+      <c r="AC39">
+        <v>3.75</v>
+      </c>
+      <c r="AD39">
+        <v>1.22</v>
+      </c>
+      <c r="AE39">
         <v>1.05</v>
       </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.2</v>
-      </c>
-      <c r="Z39">
-        <v>3.4</v>
-      </c>
-      <c r="AA39">
-        <v>1.76</v>
-      </c>
-      <c r="AB39">
-        <v>1.87</v>
-      </c>
-      <c r="AC39">
-        <v>2.85</v>
-      </c>
-      <c r="AD39">
-        <v>1.32</v>
-      </c>
-      <c r="AE39">
-        <v>1.08</v>
-      </c>
       <c r="AF39">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK39">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,34 +6838,34 @@
         <v>6.25</v>
       </c>
       <c r="Q40">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="R40">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U40">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W40">
         <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="AA40">
         <v>1.73</v>
@@ -6877,16 +6877,16 @@
         <v>2.7</v>
       </c>
       <c r="AD40">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG40">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.18</v>
       </c>
       <c r="AK40">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q41">
         <v>2.33</v>
       </c>
       <c r="R41">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S41">
         <v>1.23</v>
       </c>
       <c r="T41">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="U41">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V41">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W41">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
         <v>1.02</v>
@@ -7028,25 +7028,25 @@
         <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="AA41">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AB41">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="AC41">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="AD41">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AE41">
         <v>1.18</v>
       </c>
       <c r="AF41">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
         <v>2.45</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
         <v>1.87</v>
@@ -7158,13 +7158,13 @@
         <v>3.41</v>
       </c>
       <c r="O42">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q42">
-        <v>3.61</v>
+        <v>3.83</v>
       </c>
       <c r="R42">
         <v>2.36</v>
@@ -7173,10 +7173,10 @@
         <v>1.26</v>
       </c>
       <c r="T42">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="U42">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V42">
         <v>1.51</v>
@@ -7194,10 +7194,10 @@
         <v>4.3</v>
       </c>
       <c r="AA42">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB42">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC42">
         <v>2.59</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,16 +7318,16 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="O43">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P43">
         <v>2.35</v>
       </c>
       <c r="Q43">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="R43">
         <v>2.16</v>
@@ -7336,7 +7336,7 @@
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="U43">
         <v>2.45</v>
@@ -7357,19 +7357,19 @@
         <v>3.5</v>
       </c>
       <c r="AA43">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AB43">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC43">
         <v>2.83</v>
       </c>
       <c r="AD43">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF43">
         <v>1.55</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,31 +7481,31 @@
         </is>
       </c>
       <c r="N44">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="O44">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P44">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Q44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R44">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S44">
         <v>1.3</v>
       </c>
       <c r="T44">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="U44">
         <v>2.5</v>
       </c>
       <c r="V44">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W44">
         <v>1.09</v>
@@ -7514,31 +7514,31 @@
         <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z44">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA44">
         <v>1.66</v>
       </c>
       <c r="AB44">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC44">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AD44">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF44">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG44">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="AK44">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7816,7 +7816,7 @@
         <v>2.45</v>
       </c>
       <c r="Q46">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="R46">
         <v>2.45</v>
@@ -7828,16 +7828,16 @@
         <v>3.1</v>
       </c>
       <c r="U46">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="V46">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W46">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
         <v>1.2</v>
@@ -7846,10 +7846,10 @@
         <v>4.98</v>
       </c>
       <c r="AA46">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AB46">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AC46">
         <v>2.35</v>
@@ -7858,13 +7858,13 @@
         <v>1.57</v>
       </c>
       <c r="AE46">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF46">
         <v>1.5</v>
       </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.56</v>
+        <v>2.13</v>
       </c>
       <c r="O47">
         <v>3.32</v>
@@ -7979,7 +7979,7 @@
         <v>3.33</v>
       </c>
       <c r="Q47">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R47">
         <v>2.3</v>
@@ -8000,25 +8000,25 @@
         <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
         <v>1.21</v>
       </c>
       <c r="Z47">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AA47">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB47">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC47">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AD47">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE47">
         <v>1.12</v>
@@ -8043,7 +8043,7 @@
         <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="O48">
         <v>3.25</v>
       </c>
       <c r="P48">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q48">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="R48">
         <v>2.05</v>
@@ -8151,10 +8151,10 @@
         <v>1.4</v>
       </c>
       <c r="T48">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="U48">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V48">
         <v>1.36</v>
@@ -8178,7 +8178,7 @@
         <v>1.57</v>
       </c>
       <c r="AC48">
-        <v>3.34</v>
+        <v>4.25</v>
       </c>
       <c r="AD48">
         <v>1.18</v>
@@ -8305,55 +8305,55 @@
         <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8631,16 +8631,16 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="R51">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T51">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U51">
         <v>3.06</v>
@@ -8649,25 +8649,25 @@
         <v>1.33</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
         <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z51">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA51">
         <v>2.07</v>
       </c>
       <c r="AB51">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC51">
-        <v>3.05</v>
+        <v>3.81</v>
       </c>
       <c r="AD51">
         <v>1.29</v>
@@ -8676,10 +8676,10 @@
         <v>1.06</v>
       </c>
       <c r="AF51">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="O52">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="P52">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q52">
         <v>2.82</v>
@@ -8803,7 +8803,7 @@
         <v>1.24</v>
       </c>
       <c r="T52">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="U52">
         <v>2.15</v>
@@ -8836,7 +8836,7 @@
         <v>1.61</v>
       </c>
       <c r="AE52">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF52">
         <v>1.43</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O53">
         <v>4.1</v>
@@ -8963,16 +8963,16 @@
         <v>2.6</v>
       </c>
       <c r="S53">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T53">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="U53">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V53">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W53">
         <v>1.22</v>
@@ -8981,7 +8981,7 @@
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z53">
         <v>7.5</v>
@@ -8996,16 +8996,16 @@
         <v>1.8</v>
       </c>
       <c r="AD53">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AE53">
         <v>1.4</v>
       </c>
       <c r="AF53">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AG53">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK53">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="O54">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P54">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q54">
         <v>2.2</v>
@@ -9126,40 +9126,40 @@
         <v>2.07</v>
       </c>
       <c r="S54">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T54">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="U54">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="V54">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
         <v>1.06</v>
       </c>
       <c r="X54">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z54">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AA54">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB54">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC54">
         <v>2.99</v>
       </c>
       <c r="AD54">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE54">
         <v>1.08</v>
@@ -9283,16 +9283,16 @@
         <v>2.95</v>
       </c>
       <c r="Q55">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R55">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="S55">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T55">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="U55">
         <v>2.88</v>
@@ -9301,37 +9301,37 @@
         <v>1.36</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z55">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AA55">
         <v>2.02</v>
       </c>
       <c r="AB55">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC55">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="AD55">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE55">
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AG55">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK55">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9443,58 +9443,58 @@
         <v>3.55</v>
       </c>
       <c r="P56">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="Q56">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R56">
         <v>2.25</v>
       </c>
       <c r="S56">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T56">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U56">
         <v>2.59</v>
       </c>
       <c r="V56">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z56">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA56">
         <v>1.78</v>
       </c>
       <c r="AB56">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC56">
         <v>2.8</v>
       </c>
       <c r="AD56">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE56">
         <v>1.08</v>
       </c>
       <c r="AF56">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG56">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>5.45</v>
+        <v>5.6</v>
       </c>
       <c r="Q57">
         <v>2.15</v>
@@ -9639,7 +9639,7 @@
         <v>2.92</v>
       </c>
       <c r="AA57">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB57">
         <v>1.67</v>
@@ -9784,7 +9784,7 @@
         <v>2.89</v>
       </c>
       <c r="U58">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V58">
         <v>1.41</v>
@@ -9808,13 +9808,13 @@
         <v>1.94</v>
       </c>
       <c r="AC58">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD58">
         <v>1.27</v>
       </c>
       <c r="AE58">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF58">
         <v>1.73</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK58">
         <v>1.89</v>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="O59">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P59">
         <v>2.55</v>
@@ -9941,13 +9941,13 @@
         <v>1.95</v>
       </c>
       <c r="S59">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T59">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="U59">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="V59">
         <v>1.32</v>
@@ -9959,13 +9959,13 @@
         <v>1.08</v>
       </c>
       <c r="Y59">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z59">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="AA59">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AB59">
         <v>1.63</v>
@@ -9974,16 +9974,16 @@
         <v>4.6</v>
       </c>
       <c r="AD59">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE59">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF59">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG59">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10252,31 +10252,31 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="O61">
+        <v>2.95</v>
+      </c>
+      <c r="P61">
+        <v>3.4</v>
+      </c>
+      <c r="Q61">
         <v>2.85</v>
       </c>
-      <c r="P61">
-        <v>3</v>
-      </c>
-      <c r="Q61">
-        <v>2.9</v>
-      </c>
       <c r="R61">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="S61">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T61">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="U61">
         <v>3.14</v>
       </c>
       <c r="V61">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W61">
         <v>1.02</v>
@@ -10285,28 +10285,28 @@
         <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z61">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AA61">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AB61">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AC61">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="AD61">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE61">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF61">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG61">
         <v>1.79</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK61">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,16 +10415,16 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="O62">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P62">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="Q62">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R62">
         <v>2.12</v>
@@ -10433,43 +10433,43 @@
         <v>1.36</v>
       </c>
       <c r="T62">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U62">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V62">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W62">
+        <v>1.06</v>
+      </c>
+      <c r="X62">
         <v>1.03</v>
       </c>
-      <c r="X62">
-        <v>1.01</v>
-      </c>
       <c r="Y62">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z62">
-        <v>3.35</v>
+        <v>3.53</v>
       </c>
       <c r="AA62">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB62">
         <v>1.81</v>
       </c>
       <c r="AC62">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AD62">
         <v>1.26</v>
       </c>
       <c r="AE62">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF62">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG62">
         <v>1.97</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK62">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,25 +10578,25 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O63">
         <v>3</v>
       </c>
       <c r="P63">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q63">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="R63">
         <v>1.91</v>
       </c>
       <c r="S63">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T63">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="U63">
         <v>3.5</v>
@@ -10611,10 +10611,10 @@
         <v>1.05</v>
       </c>
       <c r="Y63">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="Z63">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AA63">
         <v>2.54</v>
@@ -10635,7 +10635,7 @@
         <v>2.06</v>
       </c>
       <c r="AG63">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10741,31 +10741,31 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O64">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P64">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q64">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="R64">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S64">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T64">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="U64">
         <v>3.28</v>
       </c>
       <c r="V64">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W64">
         <v>1.04</v>
@@ -10798,7 +10798,7 @@
         <v>1.9</v>
       </c>
       <c r="AG64">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK64">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10919,10 +10919,10 @@
         <v>1.81</v>
       </c>
       <c r="S65">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="T65">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U65">
         <v>3.5</v>
@@ -10946,7 +10946,7 @@
         <v>2.52</v>
       </c>
       <c r="AB65">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AC65">
         <v>5</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK65">
         <v>1.52</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O66">
         <v>3.05</v>
@@ -11091,7 +11091,7 @@
         <v>3.2</v>
       </c>
       <c r="V66">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W66">
         <v>1.02</v>
@@ -11106,7 +11106,7 @@
         <v>2.66</v>
       </c>
       <c r="AA66">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AB66">
         <v>1.57</v>
@@ -11236,7 +11236,7 @@
         <v>3.4</v>
       </c>
       <c r="P67">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="Q67">
         <v>2.9</v>
@@ -11251,37 +11251,37 @@
         <v>3</v>
       </c>
       <c r="U67">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="V67">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y67">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="AA67">
         <v>1.9</v>
       </c>
       <c r="AB67">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC67">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AD67">
         <v>1.31</v>
       </c>
       <c r="AE67">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF67">
         <v>1.7</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AK67">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,19 +11393,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="O68">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P68">
         <v>2.35</v>
       </c>
       <c r="Q68">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="R68">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S68">
         <v>1.39</v>
@@ -11417,40 +11417,40 @@
         <v>2.6</v>
       </c>
       <c r="V68">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W68">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X68">
         <v>1</v>
       </c>
       <c r="Y68">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z68">
-        <v>3.3</v>
+        <v>4.09</v>
       </c>
       <c r="AA68">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AB68">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC68">
         <v>3</v>
       </c>
       <c r="AD68">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE68">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG68">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11728,56 +11728,56 @@
         <v>4.25</v>
       </c>
       <c r="Q70">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R70">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S70">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T70">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="U70">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V70">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W70">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X70">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z70">
         <v>3.34</v>
       </c>
       <c r="AA70">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB70">
+        <v>1.91</v>
+      </c>
+      <c r="AC70">
+        <v>3.3</v>
+      </c>
+      <c r="AD70">
+        <v>1.29</v>
+      </c>
+      <c r="AE70">
+        <v>1.07</v>
+      </c>
+      <c r="AF70">
+        <v>1.83</v>
+      </c>
+      <c r="AG70">
         <v>1.84</v>
       </c>
-      <c r="AC70">
-        <v>3.14</v>
-      </c>
-      <c r="AD70">
-        <v>1.27</v>
-      </c>
-      <c r="AE70">
-        <v>1.06</v>
-      </c>
-      <c r="AF70">
-        <v>1.8</v>
-      </c>
-      <c r="AG70">
-        <v>1.87</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,19 +11882,19 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O71">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="P71">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q71">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R71">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="S71">
         <v>1.43</v>
@@ -11912,34 +11912,34 @@
         <v>1.03</v>
       </c>
       <c r="X71">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
         <v>1.36</v>
       </c>
       <c r="Z71">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AA71">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB71">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC71">
         <v>3.8</v>
       </c>
       <c r="AD71">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE71">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF71">
         <v>1.85</v>
       </c>
       <c r="AG71">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK71">
         <v>1.73</v>
@@ -12045,49 +12045,49 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="O72">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P72">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="Q72">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R72">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="S72">
         <v>1.28</v>
       </c>
       <c r="T72">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U72">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V72">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W72">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X72">
         <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z72">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA72">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB72">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC72">
         <v>2.25</v>
@@ -12096,13 +12096,13 @@
         <v>1.53</v>
       </c>
       <c r="AE72">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF72">
         <v>1.53</v>
       </c>
       <c r="AG72">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12534,25 +12534,25 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P75">
         <v>4.5</v>
       </c>
       <c r="Q75">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R75">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S75">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T75">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U75">
         <v>3</v>
@@ -12561,37 +12561,37 @@
         <v>1.33</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y75">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z75">
-        <v>3.03</v>
+        <v>2.86</v>
       </c>
       <c r="AA75">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AB75">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AC75">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD75">
         <v>1.23</v>
       </c>
       <c r="AE75">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF75">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AG75">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK75">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -3092,13 +3092,13 @@
         <v>2.4</v>
       </c>
       <c r="R17">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S17">
         <v>1.33</v>
       </c>
       <c r="T17">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="U17">
         <v>2.63</v>
@@ -3113,10 +3113,10 @@
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA17">
         <v>1.7</v>
@@ -4417,13 +4417,13 @@
         <v>1.06</v>
       </c>
       <c r="Y25">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z25">
         <v>2.85</v>
       </c>
       <c r="AA25">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AB25">
         <v>1.57</v>
@@ -4710,28 +4710,28 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O27">
         <v>3.6</v>
       </c>
       <c r="P27">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q27">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="R27">
         <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U27">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="V27">
         <v>1.46</v>
@@ -4740,13 +4740,13 @@
         <v>1.09</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="AA27">
         <v>1.72</v>
@@ -4755,10 +4755,10 @@
         <v>2.07</v>
       </c>
       <c r="AC27">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD27">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE27">
         <v>1.11</v>
@@ -4783,7 +4783,7 @@
         <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>3.45</v>
       </c>
       <c r="Q34">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="R34">
         <v>1.85</v>
@@ -5884,7 +5884,7 @@
         <v>1.14</v>
       </c>
       <c r="Y34">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Z34">
         <v>2.29</v>
@@ -5899,7 +5899,7 @@
         <v>5.75</v>
       </c>
       <c r="AD34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE34">
         <v>1.03</v>
@@ -9295,7 +9295,7 @@
         <v>2.84</v>
       </c>
       <c r="U55">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V55">
         <v>1.36</v>
@@ -9313,10 +9313,10 @@
         <v>3.3</v>
       </c>
       <c r="AA55">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AB55">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC55">
         <v>3.69</v>
@@ -9437,16 +9437,16 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O56">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P56">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q56">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R56">
         <v>2.25</v>
@@ -9458,16 +9458,16 @@
         <v>2.99</v>
       </c>
       <c r="U56">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="V56">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W56">
         <v>1.05</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
         <v>1.24</v>
@@ -9476,7 +9476,7 @@
         <v>4</v>
       </c>
       <c r="AA56">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB56">
         <v>2</v>
@@ -9488,13 +9488,13 @@
         <v>1.39</v>
       </c>
       <c r="AE56">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF56">
         <v>1.67</v>
       </c>
       <c r="AG56">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK56">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9938,19 +9938,19 @@
         <v>3.6</v>
       </c>
       <c r="R59">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S59">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T59">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U59">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="V59">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W59">
         <v>1.03</v>
@@ -9968,16 +9968,16 @@
         <v>2.4</v>
       </c>
       <c r="AB59">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC59">
         <v>4.6</v>
       </c>
       <c r="AD59">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE59">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF59">
         <v>1.87</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AK59">
         <v>1.36</v>
@@ -11239,7 +11239,7 @@
         <v>2.63</v>
       </c>
       <c r="Q67">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="R67">
         <v>2.2</v>
@@ -11260,7 +11260,7 @@
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
         <v>1.25</v>
@@ -11269,25 +11269,25 @@
         <v>3.55</v>
       </c>
       <c r="AA67">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB67">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AC67">
         <v>3.25</v>
       </c>
       <c r="AD67">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE67">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF67">
         <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>1.61</v>
       </c>
       <c r="AG68">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK68">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,7 +11565,7 @@
         <v>2.75</v>
       </c>
       <c r="Q69">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="R69">
         <v>1.91</v>
@@ -11577,43 +11577,43 @@
         <v>2.18</v>
       </c>
       <c r="U69">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="V69">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W69">
         <v>1.02</v>
       </c>
       <c r="X69">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y69">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z69">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AA69">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB69">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AC69">
         <v>5.43</v>
       </c>
       <c r="AD69">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AE69">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF69">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG69">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK69">
         <v>1.41</v>
@@ -12543,10 +12543,10 @@
         <v>4.5</v>
       </c>
       <c r="Q75">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="R75">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S75">
         <v>1.43</v>
@@ -12555,22 +12555,22 @@
         <v>2.69</v>
       </c>
       <c r="U75">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V75">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W75">
         <v>1.06</v>
       </c>
       <c r="X75">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z75">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AA75">
         <v>2.18</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.95</v>
+        <v>1.68</v>
       </c>
       <c r="O30">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>2.08</v>
+        <v>4.6</v>
       </c>
       <c r="Q30">
-        <v>4.2</v>
+        <v>2.44</v>
       </c>
       <c r="R30">
         <v>2</v>
       </c>
       <c r="S30">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T30">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="U30">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="V30">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W30">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y30">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="Z30">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AA30">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
       <c r="AB30">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AC30">
-        <v>3.85</v>
+        <v>5.25</v>
       </c>
       <c r="AD30">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AE30">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF30">
-        <v>1.92</v>
+        <v>2.34</v>
       </c>
       <c r="AG30">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>1.29</v>
+        <v>2.05</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="O31">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P31">
-        <v>4.6</v>
+        <v>2.08</v>
       </c>
       <c r="Q31">
-        <v>2.44</v>
+        <v>4.2</v>
       </c>
       <c r="R31">
         <v>2</v>
       </c>
       <c r="S31">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T31">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="U31">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="V31">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y31">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="Z31">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AA31">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="AB31">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AC31">
-        <v>5.25</v>
+        <v>3.85</v>
       </c>
       <c r="AD31">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AE31">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>2.34</v>
+        <v>1.92</v>
       </c>
       <c r="AG31">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="AK31">
-        <v>2.05</v>
+        <v>1.29</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -12543,10 +12543,10 @@
         <v>4.5</v>
       </c>
       <c r="Q75">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="R75">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S75">
         <v>1.43</v>
@@ -12555,22 +12555,22 @@
         <v>2.69</v>
       </c>
       <c r="U75">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="V75">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W75">
         <v>1.06</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z75">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AA75">
         <v>2.18</v>
@@ -12585,10 +12585,10 @@
         <v>1.23</v>
       </c>
       <c r="AE75">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF75">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AG75">
         <v>1.72</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK75">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="O7">
         <v>2.93</v>
@@ -1465,10 +1465,10 @@
         <v>2.01</v>
       </c>
       <c r="S7">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T7">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="U7">
         <v>3.3</v>
@@ -1489,22 +1489,22 @@
         <v>2.59</v>
       </c>
       <c r="AA7">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB7">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC7">
         <v>4.61</v>
       </c>
       <c r="AD7">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF7">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AG7">
         <v>1.75</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3744,19 +3744,19 @@
         <v>1.83</v>
       </c>
       <c r="R21">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
         <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V21">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W21">
         <v>1.12</v>
@@ -3765,19 +3765,19 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="AA21">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AB21">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AC21">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="AD21">
         <v>1.47</v>
@@ -3786,10 +3786,10 @@
         <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG21">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -5205,13 +5205,13 @@
         <v>3.2</v>
       </c>
       <c r="P30">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="Q30">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S30">
         <v>1.5</v>
@@ -5220,16 +5220,16 @@
         <v>2.21</v>
       </c>
       <c r="U30">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V30">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W30">
         <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y30">
         <v>1.5</v>
@@ -5238,7 +5238,7 @@
         <v>2.4</v>
       </c>
       <c r="AA30">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AB30">
         <v>1.41</v>
@@ -5247,16 +5247,16 @@
         <v>5.25</v>
       </c>
       <c r="AD30">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE30">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF30">
         <v>2.34</v>
       </c>
       <c r="AG30">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5365,10 +5365,10 @@
         <v>3.95</v>
       </c>
       <c r="O31">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="P31">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q31">
         <v>4.2</v>
@@ -5404,7 +5404,7 @@
         <v>2.17</v>
       </c>
       <c r="AB31">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC31">
         <v>3.85</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AK31">
         <v>1.29</v>
@@ -7155,16 +7155,16 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P42">
         <v>1.94</v>
       </c>
       <c r="Q42">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="R42">
         <v>2.36</v>
@@ -7176,7 +7176,7 @@
         <v>3.25</v>
       </c>
       <c r="U42">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
         <v>1.51</v>
@@ -7194,16 +7194,16 @@
         <v>4.3</v>
       </c>
       <c r="AA42">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB42">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AC42">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AD42">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AE42">
         <v>1.12</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="AK42">
         <v>1.28</v>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.13</v>
+        <v>1.54</v>
       </c>
       <c r="O47">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
         <v>3.33</v>
@@ -7991,13 +7991,13 @@
         <v>3.25</v>
       </c>
       <c r="U47">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V47">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
         <v>1.04</v>
@@ -8006,7 +8006,7 @@
         <v>1.21</v>
       </c>
       <c r="Z47">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA47">
         <v>1.67</v>
@@ -8021,7 +8021,7 @@
         <v>1.42</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF47">
         <v>1.73</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -10578,61 +10578,61 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O63">
         <v>3</v>
       </c>
       <c r="P63">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q63">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="R63">
         <v>1.91</v>
       </c>
       <c r="S63">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T63">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="U63">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V63">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W63">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X63">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z63">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AA63">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="AB63">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC63">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AD63">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE63">
         <v>1</v>
       </c>
       <c r="AF63">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG63">
         <v>1.67</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O64">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P64">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q64">
         <v>2.98</v>
@@ -10756,25 +10756,25 @@
         <v>1.85</v>
       </c>
       <c r="S64">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T64">
         <v>2.6</v>
       </c>
       <c r="U64">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="V64">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W64">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X64">
         <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z64">
         <v>2.69</v>
@@ -10783,7 +10783,7 @@
         <v>2.3</v>
       </c>
       <c r="AB64">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AC64">
         <v>4.15</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK64">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10919,10 +10919,10 @@
         <v>1.81</v>
       </c>
       <c r="S65">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="T65">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U65">
         <v>3.5</v>
@@ -10931,7 +10931,7 @@
         <v>1.25</v>
       </c>
       <c r="W65">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X65">
         <v>1.06</v>
@@ -10946,7 +10946,7 @@
         <v>2.52</v>
       </c>
       <c r="AB65">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AC65">
         <v>5</v>
@@ -10961,7 +10961,7 @@
         <v>2.11</v>
       </c>
       <c r="AG65">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK65">
         <v>1.52</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O66">
         <v>3.05</v>
@@ -11091,10 +11091,10 @@
         <v>3.2</v>
       </c>
       <c r="V66">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W66">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
         <v>1.05</v>
@@ -11106,10 +11106,10 @@
         <v>2.66</v>
       </c>
       <c r="AA66">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="AB66">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC66">
         <v>3.88</v>
@@ -11140,7 +11140,7 @@
         <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>1.5</v>
       </c>
       <c r="Z69">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="AA69">
         <v>2.62</v>
@@ -11604,13 +11604,13 @@
         <v>5.43</v>
       </c>
       <c r="AD69">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AE69">
         <v>1.01</v>
       </c>
       <c r="AF69">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG69">
         <v>1.6</v>
@@ -12045,25 +12045,25 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O72">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P72">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="Q72">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="R72">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="S72">
         <v>1.28</v>
       </c>
       <c r="T72">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U72">
         <v>2.25</v>
@@ -12072,13 +12072,13 @@
         <v>1.59</v>
       </c>
       <c r="W72">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X72">
         <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z72">
         <v>4.6</v>
@@ -12087,7 +12087,7 @@
         <v>1.55</v>
       </c>
       <c r="AB72">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC72">
         <v>2.25</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="O5">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="P5">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
       </c>
       <c r="R5">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T5">
         <v>3.21</v>
       </c>
       <c r="U5">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V5">
         <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z5">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA5">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AB5">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC5">
         <v>2.9</v>
       </c>
       <c r="AD5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
         <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK5">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O6">
         <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q6">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="R6">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="S6">
         <v>1.33</v>
       </c>
       <c r="T6">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
         <v>2.5</v>
@@ -1314,10 +1314,10 @@
         <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
         <v>1.24</v>
@@ -1326,25 +1326,25 @@
         <v>3.84</v>
       </c>
       <c r="AA6">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB6">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC6">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="AD6">
         <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
         <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
         <v>1.35</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="O8">
         <v>3.5</v>
       </c>
       <c r="P8">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="O13">
         <v>3.2</v>
@@ -2437,16 +2437,16 @@
         <v>2.5</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
         <v>2.18</v>
       </c>
       <c r="S13">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="U13">
         <v>2.7</v>
@@ -2458,7 +2458,7 @@
         <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.26</v>
@@ -2482,7 +2482,7 @@
         <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
         <v>2</v>
@@ -3095,10 +3095,10 @@
         <v>2.18</v>
       </c>
       <c r="S17">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
         <v>2.63</v>
@@ -3113,10 +3113,10 @@
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="AA17">
         <v>1.7</v>
@@ -3134,7 +3134,7 @@
         <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG17">
         <v>2</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,25 +3243,25 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O18">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="P18">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R18">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="S18">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T18">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="U18">
         <v>2.06</v>
@@ -3270,22 +3270,22 @@
         <v>1.66</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z18">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AA18">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AB18">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC18">
         <v>2.02</v>
@@ -3297,10 +3297,10 @@
         <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK18">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="O19">
+        <v>5.5</v>
+      </c>
+      <c r="P19">
         <v>6</v>
       </c>
-      <c r="P19">
-        <v>8.5</v>
-      </c>
       <c r="Q19">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="R19">
         <v>3</v>
       </c>
       <c r="S19">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="U19">
         <v>2</v>
       </c>
       <c r="V19">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W19">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3442,28 +3442,28 @@
         <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="AA19">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AB19">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="AC19">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AD19">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AE19">
         <v>1.31</v>
       </c>
       <c r="AF19">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>3.05</v>
       </c>
       <c r="P23">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="Q23">
         <v>3.48</v>
@@ -4076,7 +4076,7 @@
         <v>1.53</v>
       </c>
       <c r="T23">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="U23">
         <v>3.38</v>
@@ -4097,7 +4097,7 @@
         <v>2.69</v>
       </c>
       <c r="AA23">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AB23">
         <v>1.61</v>
@@ -4115,7 +4115,7 @@
         <v>1.92</v>
       </c>
       <c r="AG23">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AK23">
         <v>1.48</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O25">
         <v>3.2</v>
@@ -4408,7 +4408,7 @@
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
         <v>1.05</v>
@@ -4420,13 +4420,13 @@
         <v>1.43</v>
       </c>
       <c r="Z25">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AA25">
         <v>2.23</v>
       </c>
       <c r="AB25">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AC25">
         <v>4.5</v>
@@ -4457,7 +4457,7 @@
         <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
         <v>3.4</v>
@@ -4562,31 +4562,31 @@
         <v>2.37</v>
       </c>
       <c r="S26">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
         <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V26">
         <v>1.53</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z26">
         <v>3.76</v>
       </c>
       <c r="AA26">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB26">
         <v>2.07</v>
@@ -4604,7 +4604,7 @@
         <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4719,19 +4719,19 @@
         <v>4.4</v>
       </c>
       <c r="Q27">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="R27">
         <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="V27">
         <v>1.46</v>
@@ -4740,7 +4740,7 @@
         <v>1.09</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
         <v>1.22</v>
@@ -4752,7 +4752,7 @@
         <v>1.72</v>
       </c>
       <c r="AB27">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC27">
         <v>2.66</v>
@@ -4767,7 +4767,7 @@
         <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O28">
         <v>3.6</v>
       </c>
       <c r="P28">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="Q28">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="R28">
         <v>2.14</v>
@@ -4909,19 +4909,19 @@
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AA28">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB28">
         <v>2</v>
       </c>
       <c r="AC28">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AD28">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
         <v>1.09</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK28">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O29">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="Q29">
         <v>2.52</v>
@@ -5054,7 +5054,7 @@
         <v>1.38</v>
       </c>
       <c r="T29">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="U29">
         <v>2.7</v>
@@ -5078,7 +5078,7 @@
         <v>1.9</v>
       </c>
       <c r="AB29">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC29">
         <v>3.4</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="O32">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q32">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="R32">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S32">
         <v>1.46</v>
@@ -5549,7 +5549,7 @@
         <v>3.22</v>
       </c>
       <c r="V32">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W32">
         <v>1.04</v>
@@ -5564,25 +5564,25 @@
         <v>2.83</v>
       </c>
       <c r="AA32">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AB32">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC32">
-        <v>3.98</v>
+        <v>3.84</v>
       </c>
       <c r="AD32">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE32">
         <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG32">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
         <v>1.66</v>
@@ -5878,16 +5878,16 @@
         <v>1.22</v>
       </c>
       <c r="W34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
         <v>1.14</v>
       </c>
       <c r="Y34">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Z34">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AA34">
         <v>3</v>
@@ -5899,16 +5899,16 @@
         <v>5.75</v>
       </c>
       <c r="AD34">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE34">
         <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG34">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK34">
         <v>1.55</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O35">
         <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -6032,10 +6032,10 @@
         <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U35">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="V35">
         <v>1.52</v>
@@ -6053,16 +6053,16 @@
         <v>4.33</v>
       </c>
       <c r="AA35">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB35">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AC35">
         <v>2.54</v>
       </c>
       <c r="AD35">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE35">
         <v>1.18</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,25 +6186,25 @@
         <v>4.1</v>
       </c>
       <c r="Q36">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="R36">
         <v>2.5</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T36">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U36">
         <v>2.2</v>
       </c>
       <c r="V36">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W36">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
         <v>1.02</v>
@@ -6219,7 +6219,7 @@
         <v>1.46</v>
       </c>
       <c r="AB36">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AC36">
         <v>2.25</v>
@@ -6343,7 +6343,7 @@
         <v>3.75</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
         <v>1.75</v>
@@ -6355,10 +6355,10 @@
         <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T37">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="U37">
         <v>2.48</v>
@@ -6382,16 +6382,16 @@
         <v>1.67</v>
       </c>
       <c r="AB37">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC37">
         <v>2.43</v>
       </c>
       <c r="AD37">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE37">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
         <v>1.61</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
         <v>1.21</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>2.38</v>
+      </c>
+      <c r="R38">
+        <v>2.05</v>
+      </c>
+      <c r="S38">
+        <v>1.4</v>
+      </c>
+      <c r="T38">
+        <v>2.75</v>
+      </c>
+      <c r="U38">
+        <v>3</v>
+      </c>
+      <c r="V38">
+        <v>1.33</v>
+      </c>
+      <c r="W38">
+        <v>1.06</v>
+      </c>
+      <c r="X38">
+        <v>1.04</v>
+      </c>
+      <c r="Y38">
+        <v>1.33</v>
+      </c>
+      <c r="Z38">
+        <v>3.08</v>
+      </c>
+      <c r="AA38">
+        <v>1.99</v>
+      </c>
+      <c r="AB38">
+        <v>1.73</v>
+      </c>
+      <c r="AC38">
         <v>3.6</v>
       </c>
-      <c r="P38">
-        <v>1.73</v>
-      </c>
-      <c r="Q38">
-        <v>4.49</v>
-      </c>
-      <c r="R38">
-        <v>2.44</v>
-      </c>
-      <c r="S38">
-        <v>1.28</v>
-      </c>
-      <c r="T38">
-        <v>3.18</v>
-      </c>
-      <c r="U38">
-        <v>2.43</v>
-      </c>
-      <c r="V38">
-        <v>1.48</v>
-      </c>
-      <c r="W38">
-        <v>1.07</v>
-      </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>1.15</v>
-      </c>
-      <c r="Z38">
-        <v>3.4</v>
-      </c>
-      <c r="AA38">
-        <v>1.76</v>
-      </c>
-      <c r="AB38">
-        <v>1.87</v>
-      </c>
-      <c r="AC38">
-        <v>2.85</v>
-      </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE38">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF38">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>1.16</v>
+        <v>1.86</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q39">
-        <v>2.41</v>
+        <v>4.4</v>
       </c>
       <c r="R39">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="U39">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="V39">
+        <v>1.48</v>
+      </c>
+      <c r="W39">
+        <v>1.08</v>
+      </c>
+      <c r="X39">
+        <v>1.03</v>
+      </c>
+      <c r="Y39">
+        <v>1.15</v>
+      </c>
+      <c r="Z39">
+        <v>3.4</v>
+      </c>
+      <c r="AA39">
+        <v>1.76</v>
+      </c>
+      <c r="AB39">
+        <v>1.87</v>
+      </c>
+      <c r="AC39">
+        <v>2.85</v>
+      </c>
+      <c r="AD39">
         <v>1.33</v>
       </c>
-      <c r="W39">
-        <v>1.06</v>
-      </c>
-      <c r="X39">
-        <v>1.04</v>
-      </c>
-      <c r="Y39">
-        <v>1.33</v>
-      </c>
-      <c r="Z39">
-        <v>3.08</v>
-      </c>
-      <c r="AA39">
-        <v>1.99</v>
-      </c>
-      <c r="AB39">
-        <v>1.73</v>
-      </c>
-      <c r="AC39">
-        <v>3.75</v>
-      </c>
-      <c r="AD39">
-        <v>1.22</v>
-      </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="AG39">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.23</v>
+        <v>1.95</v>
       </c>
       <c r="AK39">
-        <v>1.85</v>
+        <v>1.16</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,55 +6829,55 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="O40">
         <v>4.4</v>
       </c>
       <c r="P40">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q40">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T40">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="U40">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="V40">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W40">
         <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z40">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA40">
         <v>1.73</v>
       </c>
       <c r="AB40">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC40">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD40">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
         <v>1.14</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="O41">
         <v>3.6</v>
@@ -7007,10 +7007,10 @@
         <v>2.45</v>
       </c>
       <c r="S41">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T41">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="U41">
         <v>2.15</v>
@@ -7022,28 +7022,28 @@
         <v>1.13</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z41">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA41">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AB41">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="AC41">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AD41">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AE41">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF41">
         <v>1.5</v>
@@ -7318,25 +7318,25 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="O43">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="P43">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="Q43">
         <v>3.37</v>
       </c>
       <c r="R43">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S43">
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="U43">
         <v>2.45</v>
@@ -7354,10 +7354,10 @@
         <v>1.28</v>
       </c>
       <c r="Z43">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA43">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB43">
         <v>1.96</v>
@@ -7375,7 +7375,7 @@
         <v>1.55</v>
       </c>
       <c r="AG43">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="N44">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O44">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P44">
         <v>1.44</v>
@@ -7529,16 +7529,16 @@
         <v>2.62</v>
       </c>
       <c r="AD44">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE44">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AG44">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="AK44">
         <v>1.09</v>
@@ -7822,10 +7822,10 @@
         <v>2.45</v>
       </c>
       <c r="S46">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U46">
         <v>2.29</v>
@@ -7834,7 +7834,7 @@
         <v>1.59</v>
       </c>
       <c r="W46">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
         <v>1.03</v>
@@ -7843,7 +7843,7 @@
         <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>4.98</v>
+        <v>4.5</v>
       </c>
       <c r="AA46">
         <v>1.66</v>
@@ -8133,28 +8133,28 @@
         </is>
       </c>
       <c r="N48">
+        <v>2.6</v>
+      </c>
+      <c r="O48">
         <v>3.2</v>
       </c>
-      <c r="O48">
-        <v>3.25</v>
-      </c>
       <c r="P48">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
       </c>
       <c r="R48">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S48">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T48">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="U48">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="V48">
         <v>1.36</v>
@@ -8184,7 +8184,7 @@
         <v>1.18</v>
       </c>
       <c r="AE48">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
         <v>1.75</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AK48">
         <v>1.4</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="O49">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
         <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="R49">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S49">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T49">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U49">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="V49">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W49">
         <v>1.07</v>
@@ -8329,31 +8329,31 @@
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z49">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA49">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB49">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC49">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD49">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE49">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG49">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK49">
         <v>1.47</v>
@@ -8468,55 +8468,55 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>2.88</v>
       </c>
       <c r="R51">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S51">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U51">
         <v>3.06</v>
@@ -8649,22 +8649,22 @@
         <v>1.33</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
         <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z51">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA51">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AB51">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC51">
         <v>3.81</v>
@@ -8673,10 +8673,10 @@
         <v>1.29</v>
       </c>
       <c r="AE51">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG51">
         <v>1.92</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
         <v>1.5</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O52">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="P52">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="Q52">
         <v>2.82</v>
@@ -8803,7 +8803,7 @@
         <v>1.24</v>
       </c>
       <c r="T52">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="U52">
         <v>2.15</v>
@@ -8833,10 +8833,10 @@
         <v>2.3</v>
       </c>
       <c r="AD52">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AE52">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF52">
         <v>1.43</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
         <v>1.53</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O53">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P53">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -8963,10 +8963,10 @@
         <v>2.6</v>
       </c>
       <c r="S53">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T53">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="U53">
         <v>1.81</v>
@@ -8984,7 +8984,7 @@
         <v>1.03</v>
       </c>
       <c r="Z53">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA53">
         <v>1.29</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK53">
         <v>1.73</v>
@@ -9111,25 +9111,25 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="O54">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P54">
-        <v>4</v>
+        <v>4.66</v>
       </c>
       <c r="Q54">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R54">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S54">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T54">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="U54">
         <v>2.73</v>
@@ -9141,34 +9141,34 @@
         <v>1.06</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z54">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AA54">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB54">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AC54">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AD54">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE54">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF54">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG54">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK54">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9295,7 +9295,7 @@
         <v>2.84</v>
       </c>
       <c r="U55">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V55">
         <v>1.36</v>
@@ -9313,13 +9313,13 @@
         <v>3.3</v>
       </c>
       <c r="AA55">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB55">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC55">
-        <v>3.69</v>
+        <v>3.24</v>
       </c>
       <c r="AD55">
         <v>1.26</v>
@@ -9331,7 +9331,7 @@
         <v>1.74</v>
       </c>
       <c r="AG55">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9437,43 +9437,43 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="O56">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P56">
-        <v>3.8</v>
+        <v>3.11</v>
       </c>
       <c r="Q56">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="R56">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S56">
         <v>1.33</v>
       </c>
       <c r="T56">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U56">
         <v>2.64</v>
       </c>
       <c r="V56">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W56">
         <v>1.05</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
         <v>1.24</v>
       </c>
       <c r="Z56">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AA56">
         <v>1.77</v>
@@ -9485,16 +9485,16 @@
         <v>2.8</v>
       </c>
       <c r="AD56">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE56">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF56">
         <v>1.67</v>
       </c>
       <c r="AG56">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK56">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9603,16 +9603,16 @@
         <v>1.5</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="Q57">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="R57">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S57">
         <v>1.42</v>
@@ -9621,28 +9621,28 @@
         <v>2.75</v>
       </c>
       <c r="U57">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="V57">
         <v>1.35</v>
       </c>
       <c r="W57">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z57">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA57">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AB57">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC57">
         <v>3.58</v>
@@ -9654,10 +9654,10 @@
         <v>1.03</v>
       </c>
       <c r="AF57">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AG57">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK57">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9769,10 +9769,10 @@
         <v>3.3</v>
       </c>
       <c r="P58">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="Q58">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="R58">
         <v>2.2</v>
@@ -9781,16 +9781,16 @@
         <v>1.36</v>
       </c>
       <c r="T58">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="U58">
         <v>2.75</v>
       </c>
       <c r="V58">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W58">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
         <v>1</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK58">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.67</v>
+        <v>2.91</v>
       </c>
       <c r="O59">
         <v>3.15</v>
@@ -9968,7 +9968,7 @@
         <v>2.4</v>
       </c>
       <c r="AB59">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC59">
         <v>4.6</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O61">
         <v>2.95</v>
@@ -10261,25 +10261,25 @@
         <v>3.4</v>
       </c>
       <c r="Q61">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="R61">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="S61">
         <v>1.48</v>
       </c>
       <c r="T61">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U61">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="V61">
         <v>1.3</v>
       </c>
       <c r="W61">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X61">
         <v>1.05</v>
@@ -10291,13 +10291,13 @@
         <v>2.66</v>
       </c>
       <c r="AA61">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AB61">
         <v>1.58</v>
       </c>
       <c r="AC61">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AD61">
         <v>1.18</v>
@@ -10325,7 +10325,7 @@
         <v>1.3</v>
       </c>
       <c r="AK61">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10418,16 +10418,16 @@
         <v>2.4</v>
       </c>
       <c r="O62">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P62">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
       </c>
       <c r="R62">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S62">
         <v>1.36</v>
@@ -10436,28 +10436,28 @@
         <v>2.88</v>
       </c>
       <c r="U62">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="V62">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W62">
         <v>1.06</v>
       </c>
       <c r="X62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z62">
-        <v>3.53</v>
+        <v>3.39</v>
       </c>
       <c r="AA62">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AB62">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AC62">
         <v>3.4</v>
@@ -10466,10 +10466,10 @@
         <v>1.26</v>
       </c>
       <c r="AE62">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF62">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG62">
         <v>1.97</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AK62">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11236,10 +11236,10 @@
         <v>3.4</v>
       </c>
       <c r="P67">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="Q67">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="R67">
         <v>2.2</v>
@@ -11251,43 +11251,43 @@
         <v>3</v>
       </c>
       <c r="U67">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V67">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z67">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="AA67">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB67">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC67">
         <v>3.25</v>
       </c>
       <c r="AD67">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE67">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF67">
         <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK67">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="O68">
         <v>3.5</v>
       </c>
       <c r="P68">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q68">
         <v>3.3</v>
@@ -11411,7 +11411,7 @@
         <v>1.39</v>
       </c>
       <c r="T68">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U68">
         <v>2.6</v>
@@ -11432,25 +11432,25 @@
         <v>4.09</v>
       </c>
       <c r="AA68">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB68">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AC68">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD68">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE68">
         <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG68">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11734,10 +11734,10 @@
         <v>2.15</v>
       </c>
       <c r="S70">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T70">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="U70">
         <v>2.7</v>
@@ -11755,7 +11755,7 @@
         <v>1.29</v>
       </c>
       <c r="Z70">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA70">
         <v>1.88</v>
@@ -11776,7 +11776,7 @@
         <v>1.83</v>
       </c>
       <c r="AG70">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK70">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O72">
         <v>3.8</v>
@@ -12054,10 +12054,10 @@
         <v>4</v>
       </c>
       <c r="Q72">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R72">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S72">
         <v>1.28</v>
@@ -12066,10 +12066,10 @@
         <v>3.5</v>
       </c>
       <c r="U72">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V72">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W72">
         <v>1.14</v>
@@ -12081,7 +12081,7 @@
         <v>1.18</v>
       </c>
       <c r="Z72">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA72">
         <v>1.55</v>
@@ -12099,10 +12099,10 @@
         <v>1.17</v>
       </c>
       <c r="AF72">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG72">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12386,19 +12386,19 @@
         <v>0</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X74">
         <v>0</v>
@@ -12425,10 +12425,10 @@
         <v>0</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12546,19 +12546,19 @@
         <v>2.3</v>
       </c>
       <c r="R75">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S75">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T75">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U75">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="V75">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W75">
         <v>1.06</v>
@@ -12567,10 +12567,10 @@
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z75">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AA75">
         <v>2.18</v>
@@ -12588,10 +12588,10 @@
         <v>1.03</v>
       </c>
       <c r="AF75">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG75">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK75">
         <v>1.95</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -11571,10 +11571,10 @@
         <v>1.91</v>
       </c>
       <c r="S69">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="T69">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="U69">
         <v>3.8</v>
@@ -11583,13 +11583,13 @@
         <v>1.19</v>
       </c>
       <c r="W69">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X69">
         <v>1.06</v>
       </c>
       <c r="Y69">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z69">
         <v>2.46</v>
@@ -11604,16 +11604,16 @@
         <v>5.43</v>
       </c>
       <c r="AD69">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AE69">
         <v>1.01</v>
       </c>
       <c r="AF69">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG69">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11885,16 +11885,16 @@
         <v>2.1</v>
       </c>
       <c r="O71">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="P71">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q71">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="R71">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="S71">
         <v>1.43</v>
@@ -11903,22 +11903,22 @@
         <v>2.62</v>
       </c>
       <c r="U71">
-        <v>3.04</v>
+        <v>2.86</v>
       </c>
       <c r="V71">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W71">
         <v>1.03</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y71">
         <v>1.36</v>
       </c>
       <c r="Z71">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AA71">
         <v>2.15</v>
@@ -11936,10 +11936,10 @@
         <v>1.08</v>
       </c>
       <c r="AF71">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG71">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1474,7 +1474,7 @@
         <v>3.3</v>
       </c>
       <c r="V7">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
         <v>1.03</v>
@@ -1486,22 +1486,22 @@
         <v>1.49</v>
       </c>
       <c r="Z7">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AA7">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AB7">
         <v>1.55</v>
       </c>
       <c r="AC7">
-        <v>4.61</v>
+        <v>4.5</v>
       </c>
       <c r="AD7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE7">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
         <v>1.98</v>
@@ -1523,7 +1523,7 @@
         <v>1.33</v>
       </c>
       <c r="AK7">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3243,31 +3243,31 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O18">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P18">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Q18">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="R18">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="S18">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="U18">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="V18">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W18">
         <v>1.14</v>
@@ -3276,31 +3276,31 @@
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z18">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AA18">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB18">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC18">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AD18">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AE18">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF18">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG18">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>2.97</v>
+        <v>2.66</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O19">
         <v>5.5</v>
       </c>
       <c r="P19">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q19">
         <v>1.53</v>
@@ -3424,13 +3424,13 @@
         <v>1.19</v>
       </c>
       <c r="T19">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V19">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W19">
         <v>1.16</v>
@@ -3445,10 +3445,10 @@
         <v>5.95</v>
       </c>
       <c r="AA19">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB19">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AC19">
         <v>1.9</v>
@@ -3457,13 +3457,13 @@
         <v>1.8</v>
       </c>
       <c r="AE19">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG19">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>2.73</v>
       </c>
       <c r="O23">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="P23">
         <v>2.79</v>
@@ -4073,7 +4073,7 @@
         <v>1.92</v>
       </c>
       <c r="S23">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="T23">
         <v>2.43</v>
@@ -4097,10 +4097,10 @@
         <v>2.69</v>
       </c>
       <c r="AA23">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AB23">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC23">
         <v>4.2</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="O32">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P32">
         <v>3.2</v>
@@ -5549,13 +5549,13 @@
         <v>3.22</v>
       </c>
       <c r="V32">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W32">
         <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
         <v>1.33</v>
@@ -5567,16 +5567,16 @@
         <v>2.19</v>
       </c>
       <c r="AB32">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC32">
-        <v>3.84</v>
+        <v>3.98</v>
       </c>
       <c r="AD32">
         <v>1.18</v>
       </c>
       <c r="AE32">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF32">
         <v>1.85</v>
@@ -7318,25 +7318,25 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O43">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="P43">
+        <v>2.37</v>
+      </c>
+      <c r="Q43">
+        <v>3.4</v>
+      </c>
+      <c r="R43">
         <v>2.13</v>
-      </c>
-      <c r="Q43">
-        <v>3.37</v>
-      </c>
-      <c r="R43">
-        <v>2.12</v>
       </c>
       <c r="S43">
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="U43">
         <v>2.45</v>
@@ -7357,10 +7357,10 @@
         <v>3.8</v>
       </c>
       <c r="AA43">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB43">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC43">
         <v>2.83</v>
@@ -7369,13 +7369,13 @@
         <v>1.33</v>
       </c>
       <c r="AE43">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF43">
         <v>1.55</v>
       </c>
       <c r="AG43">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7979,25 +7979,25 @@
         <v>3.33</v>
       </c>
       <c r="Q47">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="R47">
         <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T47">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="V47">
         <v>1.45</v>
       </c>
       <c r="W47">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
         <v>1.04</v>
@@ -8009,10 +8009,10 @@
         <v>3.95</v>
       </c>
       <c r="AA47">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB47">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC47">
         <v>2.88</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>1.36</v>
       </c>
       <c r="W55">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9310,13 +9310,13 @@
         <v>1.3</v>
       </c>
       <c r="Z55">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AA55">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AB55">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC55">
         <v>3.24</v>
@@ -9328,10 +9328,10 @@
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG55">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9769,10 +9769,10 @@
         <v>3.3</v>
       </c>
       <c r="P58">
-        <v>3.95</v>
+        <v>3.17</v>
       </c>
       <c r="Q58">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R58">
         <v>2.2</v>
@@ -9781,13 +9781,13 @@
         <v>1.36</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="U58">
         <v>2.75</v>
       </c>
       <c r="V58">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W58">
         <v>1.08</v>
@@ -9805,7 +9805,7 @@
         <v>1.92</v>
       </c>
       <c r="AB58">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC58">
         <v>3.4</v>
@@ -9836,7 +9836,7 @@
         <v>1.27</v>
       </c>
       <c r="AK58">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10415,19 +10415,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O62">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P62">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
       </c>
       <c r="R62">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S62">
         <v>1.36</v>
@@ -10436,10 +10436,10 @@
         <v>2.88</v>
       </c>
       <c r="U62">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="V62">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W62">
         <v>1.06</v>
@@ -10451,13 +10451,13 @@
         <v>1.31</v>
       </c>
       <c r="Z62">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="AA62">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB62">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC62">
         <v>3.4</v>
@@ -10469,7 +10469,7 @@
         <v>1.04</v>
       </c>
       <c r="AF62">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG62">
         <v>1.97</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
         <v>1.52</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1166,7 +1166,7 @@
         <v>1.76</v>
       </c>
       <c r="AB5">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
         <v>2.9</v>
@@ -1178,10 +1178,10 @@
         <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.31</v>
       </c>
       <c r="AK5">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>2.05</v>
       </c>
       <c r="Q6">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R6">
         <v>2.15</v>
@@ -1308,10 +1308,10 @@
         <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W6">
         <v>1.11</v>
@@ -1326,13 +1326,13 @@
         <v>3.84</v>
       </c>
       <c r="AA6">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB6">
         <v>2</v>
       </c>
       <c r="AC6">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="AD6">
         <v>1.38</v>
@@ -1344,7 +1344,7 @@
         <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="O7">
         <v>2.93</v>
@@ -1459,10 +1459,10 @@
         <v>2.25</v>
       </c>
       <c r="Q7">
-        <v>3.91</v>
+        <v>3.26</v>
       </c>
       <c r="R7">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="S7">
         <v>1.49</v>
@@ -1486,7 +1486,7 @@
         <v>1.49</v>
       </c>
       <c r="Z7">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AA7">
         <v>2.38</v>
@@ -1495,10 +1495,10 @@
         <v>1.55</v>
       </c>
       <c r="AC7">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD7">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE7">
         <v>1.03</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="O10">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
         <v>2.73</v>
@@ -1957,13 +1957,13 @@
         <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U10">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
         <v>1.1</v>
@@ -1984,7 +1984,7 @@
         <v>1.98</v>
       </c>
       <c r="AC10">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AD10">
         <v>1.33</v>
@@ -3095,28 +3095,28 @@
         <v>2.18</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T17">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="U17">
         <v>2.63</v>
       </c>
       <c r="V17">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="AA17">
         <v>1.7</v>
@@ -3741,22 +3741,22 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R21">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T21">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V21">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W21">
         <v>1.12</v>
@@ -3765,31 +3765,31 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z21">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="AA21">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AB21">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC21">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD21">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG21">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK21">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O25">
         <v>3.2</v>
@@ -4399,7 +4399,7 @@
         <v>1.97</v>
       </c>
       <c r="S25">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T25">
         <v>2.5</v>
@@ -4408,10 +4408,10 @@
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1.06</v>
@@ -4423,10 +4423,10 @@
         <v>2.86</v>
       </c>
       <c r="AA25">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AB25">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AC25">
         <v>4.5</v>
@@ -4728,7 +4728,7 @@
         <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U27">
         <v>2.59</v>
@@ -4746,19 +4746,19 @@
         <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>3.86</v>
+        <v>3.98</v>
       </c>
       <c r="AA27">
         <v>1.72</v>
       </c>
       <c r="AB27">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC27">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AD27">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE27">
         <v>1.11</v>
@@ -4783,7 +4783,7 @@
         <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,10 +4882,10 @@
         <v>3.28</v>
       </c>
       <c r="Q28">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R28">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S28">
         <v>1.35</v>
@@ -4909,10 +4909,10 @@
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AA28">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AB28">
         <v>2</v>
@@ -4946,7 +4946,7 @@
         <v>1.31</v>
       </c>
       <c r="AK28">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5042,10 +5042,10 @@
         <v>3.4</v>
       </c>
       <c r="P29">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="Q29">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="R29">
         <v>2.1</v>
@@ -5054,16 +5054,16 @@
         <v>1.38</v>
       </c>
       <c r="T29">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="U29">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V29">
         <v>1.39</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
         <v>1.03</v>
@@ -5075,10 +5075,10 @@
         <v>3.4</v>
       </c>
       <c r="AA29">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB29">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC29">
         <v>3.4</v>
@@ -5109,7 +5109,7 @@
         <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P30">
         <v>4.75</v>
@@ -5217,28 +5217,28 @@
         <v>1.5</v>
       </c>
       <c r="T30">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="U30">
         <v>3.4</v>
       </c>
       <c r="V30">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y30">
         <v>1.5</v>
       </c>
       <c r="Z30">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AA30">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AB30">
         <v>1.41</v>
@@ -5250,13 +5250,13 @@
         <v>1.1</v>
       </c>
       <c r="AE30">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF30">
         <v>2.34</v>
       </c>
       <c r="AG30">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AK30">
         <v>2.05</v>
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="O31">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P31">
         <v>2.05</v>
       </c>
       <c r="Q31">
-        <v>4.2</v>
+        <v>5.08</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="S31">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T31">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="U31">
         <v>3.27</v>
       </c>
       <c r="V31">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
         <v>1.01</v>
@@ -5410,16 +5410,16 @@
         <v>3.85</v>
       </c>
       <c r="AD31">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
         <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG31">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AK31">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         <v>2.1</v>
       </c>
       <c r="O32">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P32">
         <v>3.2</v>
@@ -5854,13 +5854,13 @@
         <v>2.45</v>
       </c>
       <c r="O34">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P34">
         <v>3.45</v>
       </c>
       <c r="Q34">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="R34">
         <v>1.85</v>
@@ -5884,22 +5884,22 @@
         <v>1.14</v>
       </c>
       <c r="Y34">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Z34">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AA34">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AB34">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC34">
         <v>5.75</v>
       </c>
       <c r="AD34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE34">
         <v>1.03</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK34">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6020,7 +6020,7 @@
         <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q35">
         <v>2.75</v>
@@ -6029,7 +6029,7 @@
         <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T35">
         <v>3.4</v>
@@ -6053,25 +6053,25 @@
         <v>4.33</v>
       </c>
       <c r="AA35">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB35">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AC35">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="AD35">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE35">
         <v>1.18</v>
       </c>
       <c r="AF35">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>1.46</v>
       </c>
       <c r="AB36">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AC36">
         <v>2.25</v>
@@ -6349,10 +6349,10 @@
         <v>1.75</v>
       </c>
       <c r="Q37">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
         <v>1.31</v>
@@ -6388,7 +6388,7 @@
         <v>2.43</v>
       </c>
       <c r="AD37">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE37">
         <v>1.13</v>
@@ -6512,7 +6512,7 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R38">
         <v>2.05</v>
@@ -6536,7 +6536,7 @@
         <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z38">
         <v>3.08</v>
@@ -6548,19 +6548,19 @@
         <v>1.73</v>
       </c>
       <c r="AC38">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AD38">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE38">
         <v>1.04</v>
       </c>
       <c r="AF38">
+        <v>1.84</v>
+      </c>
+      <c r="AG38">
         <v>1.85</v>
-      </c>
-      <c r="AG38">
-        <v>1.84</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>1.73</v>
       </c>
       <c r="Q39">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="R39">
         <v>2.23</v>
@@ -6684,22 +6684,22 @@
         <v>1.29</v>
       </c>
       <c r="T39">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U39">
         <v>2.43</v>
       </c>
       <c r="V39">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W39">
         <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z39">
         <v>3.4</v>
@@ -6720,10 +6720,10 @@
         <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>2.45</v>
       </c>
       <c r="S41">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
         <v>3.4</v>
@@ -7031,22 +7031,22 @@
         <v>4.6</v>
       </c>
       <c r="AA41">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB41">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AC41">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AD41">
         <v>1.58</v>
       </c>
       <c r="AE41">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF41">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG41">
         <v>2.45</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="O42">
         <v>3.8</v>
       </c>
       <c r="P42">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Q42">
         <v>3.87</v>
@@ -7173,7 +7173,7 @@
         <v>1.26</v>
       </c>
       <c r="T42">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="U42">
         <v>2.5</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
         <v>1.28</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O43">
         <v>3.2</v>
@@ -7357,7 +7357,7 @@
         <v>3.8</v>
       </c>
       <c r="AA43">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB43">
         <v>1.95</v>
@@ -7985,7 +7985,7 @@
         <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T47">
         <v>3.3</v>
@@ -8003,7 +8003,7 @@
         <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z47">
         <v>3.95</v>
@@ -8012,10 +8012,10 @@
         <v>1.66</v>
       </c>
       <c r="AB47">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC47">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD47">
         <v>1.42</v>
@@ -8145,16 +8145,16 @@
         <v>3.25</v>
       </c>
       <c r="R48">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="S48">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T48">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="U48">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="V48">
         <v>1.36</v>
@@ -8169,16 +8169,16 @@
         <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA48">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="AB48">
         <v>1.57</v>
       </c>
       <c r="AC48">
-        <v>4.25</v>
+        <v>3.42</v>
       </c>
       <c r="AD48">
         <v>1.18</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AK48">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8468,16 +8468,16 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R50">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="S50">
         <v>1.2</v>
       </c>
       <c r="T50">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="U50">
         <v>2</v>
@@ -8498,25 +8498,25 @@
         <v>5.85</v>
       </c>
       <c r="AA50">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB50">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="AC50">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AD50">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE50">
         <v>1.29</v>
       </c>
       <c r="AF50">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG50">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.11</v>
       </c>
       <c r="AK50">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8788,10 +8788,10 @@
         <v>2.2</v>
       </c>
       <c r="O52">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="Q52">
         <v>2.82</v>
@@ -8836,7 +8836,7 @@
         <v>1.64</v>
       </c>
       <c r="AE52">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF52">
         <v>1.43</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK52">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,22 +8951,22 @@
         <v>1.9</v>
       </c>
       <c r="O53">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P53">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
       </c>
       <c r="R53">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S53">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T53">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="U53">
         <v>1.81</v>
@@ -8984,28 +8984,28 @@
         <v>1.03</v>
       </c>
       <c r="Z53">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA53">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB53">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AC53">
         <v>1.8</v>
       </c>
       <c r="AD53">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AE53">
         <v>1.4</v>
       </c>
       <c r="AF53">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AG53">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK53">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>3.45</v>
       </c>
       <c r="P54">
-        <v>4.66</v>
+        <v>4.3</v>
       </c>
       <c r="Q54">
         <v>2.25</v>
@@ -9126,19 +9126,19 @@
         <v>2.09</v>
       </c>
       <c r="S54">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T54">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="U54">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="V54">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W54">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
         <v>1.01</v>
@@ -9159,7 +9159,7 @@
         <v>2.94</v>
       </c>
       <c r="AD54">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE54">
         <v>1.09</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK54">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9289,10 +9289,10 @@
         <v>2.01</v>
       </c>
       <c r="S55">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T55">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="U55">
         <v>2.88</v>
@@ -9328,10 +9328,10 @@
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG55">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9437,25 +9437,25 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O56">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="Q56">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="R56">
         <v>2.35</v>
       </c>
       <c r="S56">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T56">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U56">
         <v>2.64</v>
@@ -9473,7 +9473,7 @@
         <v>1.24</v>
       </c>
       <c r="Z56">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="AA56">
         <v>1.77</v>
@@ -9488,7 +9488,7 @@
         <v>1.33</v>
       </c>
       <c r="AE56">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF56">
         <v>1.67</v>
@@ -9603,16 +9603,16 @@
         <v>1.5</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q57">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="S57">
         <v>1.42</v>
@@ -9627,7 +9627,7 @@
         <v>1.35</v>
       </c>
       <c r="W57">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X57">
         <v>1.02</v>
@@ -9645,16 +9645,16 @@
         <v>1.68</v>
       </c>
       <c r="AC57">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD57">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE57">
         <v>1.03</v>
       </c>
       <c r="AF57">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AG57">
         <v>1.67</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK57">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="O59">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P59">
         <v>2.55</v>
@@ -9938,16 +9938,16 @@
         <v>3.6</v>
       </c>
       <c r="R59">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S59">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="T59">
         <v>2.48</v>
       </c>
       <c r="U59">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V59">
         <v>1.31</v>
@@ -9968,7 +9968,7 @@
         <v>2.4</v>
       </c>
       <c r="AB59">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC59">
         <v>4.6</v>
@@ -10252,16 +10252,16 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O61">
         <v>2.95</v>
       </c>
       <c r="P61">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q61">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="R61">
         <v>2.06</v>
@@ -10270,7 +10270,7 @@
         <v>1.48</v>
       </c>
       <c r="T61">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="U61">
         <v>3</v>
@@ -10279,7 +10279,7 @@
         <v>1.3</v>
       </c>
       <c r="W61">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X61">
         <v>1.05</v>
@@ -10291,13 +10291,13 @@
         <v>2.66</v>
       </c>
       <c r="AA61">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AB61">
         <v>1.58</v>
       </c>
       <c r="AC61">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AD61">
         <v>1.18</v>
@@ -10306,10 +10306,10 @@
         <v>1.03</v>
       </c>
       <c r="AF61">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG61">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK61">
         <v>1.55</v>
@@ -10421,7 +10421,7 @@
         <v>3.34</v>
       </c>
       <c r="P62">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
@@ -10454,10 +10454,10 @@
         <v>3.35</v>
       </c>
       <c r="AA62">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB62">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC62">
         <v>3.4</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK62">
         <v>1.52</v>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O63">
         <v>3</v>
@@ -10587,7 +10587,7 @@
         <v>3.3</v>
       </c>
       <c r="Q63">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="R63">
         <v>1.91</v>
@@ -10611,31 +10611,31 @@
         <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z63">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AA63">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AB63">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC63">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AD63">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE63">
         <v>1</v>
       </c>
       <c r="AF63">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG63">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK63">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,34 +10741,34 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O64">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P64">
         <v>3.1</v>
       </c>
       <c r="Q64">
-        <v>2.98</v>
+        <v>3.07</v>
       </c>
       <c r="R64">
         <v>1.85</v>
       </c>
       <c r="S64">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="T64">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="U64">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="V64">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W64">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X64">
         <v>1.03</v>
@@ -10780,10 +10780,10 @@
         <v>2.69</v>
       </c>
       <c r="AA64">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AB64">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC64">
         <v>4.15</v>
@@ -10916,13 +10916,13 @@
         <v>3</v>
       </c>
       <c r="R65">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S65">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="T65">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U65">
         <v>3.5</v>
@@ -10934,7 +10934,7 @@
         <v>1.04</v>
       </c>
       <c r="X65">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y65">
         <v>1.51</v>
@@ -11070,10 +11070,10 @@
         <v>1.9</v>
       </c>
       <c r="O66">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P66">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="Q66">
         <v>2.62</v>
@@ -11097,22 +11097,22 @@
         <v>1.05</v>
       </c>
       <c r="X66">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z66">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AA66">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB66">
         <v>1.62</v>
       </c>
       <c r="AC66">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="AD66">
         <v>1.18</v>
@@ -11236,13 +11236,13 @@
         <v>3.4</v>
       </c>
       <c r="P67">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q67">
         <v>2.9</v>
       </c>
       <c r="R67">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S67">
         <v>1.33</v>
@@ -11251,7 +11251,7 @@
         <v>3</v>
       </c>
       <c r="U67">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="V67">
         <v>1.4</v>
@@ -11260,7 +11260,7 @@
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
         <v>1.22</v>
@@ -11278,7 +11278,7 @@
         <v>3.25</v>
       </c>
       <c r="AD67">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE67">
         <v>1.08</v>
@@ -11399,13 +11399,13 @@
         <v>3.5</v>
       </c>
       <c r="P68">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q68">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R68">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S68">
         <v>1.39</v>
@@ -11429,16 +11429,16 @@
         <v>1.22</v>
       </c>
       <c r="Z68">
-        <v>4.09</v>
+        <v>3.72</v>
       </c>
       <c r="AA68">
         <v>1.83</v>
       </c>
       <c r="AB68">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD68">
         <v>1.38</v>
@@ -11447,10 +11447,10 @@
         <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG68">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.35</v>
       </c>
       <c r="AK68">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AL68">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1130,7 +1130,7 @@
         <v>3.32</v>
       </c>
       <c r="P5">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
@@ -1178,10 +1178,10 @@
         <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -1320,16 +1320,16 @@
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
         <v>3.84</v>
       </c>
       <c r="AA6">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB6">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC6">
         <v>2.83</v>
@@ -1344,7 +1344,7 @@
         <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1465,43 +1465,43 @@
         <v>1.94</v>
       </c>
       <c r="S7">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T7">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U7">
         <v>3.3</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="Z7">
         <v>2.59</v>
       </c>
       <c r="AA7">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AB7">
         <v>1.55</v>
       </c>
       <c r="AC7">
-        <v>4.45</v>
+        <v>4.61</v>
       </c>
       <c r="AD7">
         <v>1.14</v>
       </c>
       <c r="AE7">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF7">
         <v>1.98</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>3.46</v>
+        <v>3.9</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1939,55 +1939,55 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
         <v>3.5</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q10">
         <v>2.73</v>
       </c>
       <c r="R10">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
         <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="U10">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V10">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
         <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
         <v>3.79</v>
       </c>
       <c r="AA10">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AC10">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AD10">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE10">
         <v>1.09</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="O13">
         <v>3.2</v>
@@ -2443,7 +2443,7 @@
         <v>2.18</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
         <v>2.75</v>
@@ -2452,7 +2452,7 @@
         <v>2.7</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
         <v>1.08</v>
@@ -2482,10 +2482,10 @@
         <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -3092,13 +3092,13 @@
         <v>2.4</v>
       </c>
       <c r="R17">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S17">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T17">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="U17">
         <v>2.63</v>
@@ -3113,16 +3113,16 @@
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA17">
         <v>1.7</v>
       </c>
       <c r="AB17">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AC17">
         <v>2.8</v>
@@ -3134,7 +3134,7 @@
         <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
         <v>2</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O20">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4067,22 +4067,22 @@
         <v>2.79</v>
       </c>
       <c r="Q23">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="R23">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S23">
         <v>1.48</v>
       </c>
       <c r="T23">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="U23">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W23">
         <v>1.02</v>
@@ -4091,31 +4091,31 @@
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z23">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="AA23">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AB23">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC23">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AD23">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE23">
         <v>1.01</v>
       </c>
       <c r="AF23">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AG23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4384,34 +4384,34 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="O25">
         <v>3.2</v>
       </c>
       <c r="P25">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="Q25">
         <v>2.6</v>
       </c>
       <c r="R25">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S25">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T25">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U25">
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
         <v>1.06</v>
@@ -4420,10 +4420,10 @@
         <v>1.43</v>
       </c>
       <c r="Z25">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="AA25">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AB25">
         <v>1.57</v>
@@ -4550,10 +4550,10 @@
         <v>1.95</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -4580,16 +4580,16 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z26">
         <v>3.76</v>
       </c>
       <c r="AA26">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB26">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC26">
         <v>2.75</v>
@@ -4620,7 +4620,7 @@
         <v>1.31</v>
       </c>
       <c r="AK26">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         <v>3.6</v>
       </c>
       <c r="P27">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q27">
         <v>2.23</v>
@@ -4746,13 +4746,13 @@
         <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>3.98</v>
+        <v>3.86</v>
       </c>
       <c r="AA27">
         <v>1.72</v>
       </c>
       <c r="AB27">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC27">
         <v>2.77</v>
@@ -4761,7 +4761,7 @@
         <v>1.41</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
         <v>1.67</v>
@@ -4879,13 +4879,13 @@
         <v>3.6</v>
       </c>
       <c r="P28">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="Q28">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R28">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S28">
         <v>1.35</v>
@@ -4909,13 +4909,13 @@
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AA28">
         <v>1.84</v>
       </c>
       <c r="AB28">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC28">
         <v>2.85</v>
@@ -4946,7 +4946,7 @@
         <v>1.31</v>
       </c>
       <c r="AK28">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O29">
         <v>3.4</v>
@@ -5045,7 +5045,7 @@
         <v>3.9</v>
       </c>
       <c r="Q29">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="R29">
         <v>2.1</v>
@@ -5066,7 +5066,7 @@
         <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
         <v>1.3</v>
@@ -5084,7 +5084,7 @@
         <v>3.4</v>
       </c>
       <c r="AD29">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE29">
         <v>1.05</v>
@@ -6017,7 +6017,7 @@
         <v>2.25</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
         <v>2.8</v>
@@ -6035,10 +6035,10 @@
         <v>3.4</v>
       </c>
       <c r="U35">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="V35">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
         <v>1.09</v>
@@ -6053,16 +6053,16 @@
         <v>4.33</v>
       </c>
       <c r="AA35">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB35">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AC35">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="AD35">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE35">
         <v>1.18</v>
@@ -6071,7 +6071,7 @@
         <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.19</v>
       </c>
       <c r="AK36">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,7 +6349,7 @@
         <v>1.75</v>
       </c>
       <c r="Q37">
-        <v>4.56</v>
+        <v>4</v>
       </c>
       <c r="R37">
         <v>2.25</v>
@@ -6373,7 +6373,7 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z37">
         <v>4.33</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
         <v>1.21</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q38">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="R38">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="S38">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="V38">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA38">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="AB38">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AC38">
-        <v>3.52</v>
+        <v>2.85</v>
       </c>
       <c r="AD38">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AE38">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF38">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="AG38">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>1.86</v>
+        <v>1.16</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>2.3</v>
+      </c>
+      <c r="R39">
+        <v>2.05</v>
+      </c>
+      <c r="S39">
+        <v>1.4</v>
+      </c>
+      <c r="T39">
+        <v>2.75</v>
+      </c>
+      <c r="U39">
+        <v>3</v>
+      </c>
+      <c r="V39">
+        <v>1.33</v>
+      </c>
+      <c r="W39">
+        <v>1.06</v>
+      </c>
+      <c r="X39">
+        <v>1.04</v>
+      </c>
+      <c r="Y39">
+        <v>1.33</v>
+      </c>
+      <c r="Z39">
+        <v>3.08</v>
+      </c>
+      <c r="AA39">
+        <v>1.99</v>
+      </c>
+      <c r="AB39">
         <v>1.73</v>
       </c>
-      <c r="Q39">
-        <v>4.5</v>
-      </c>
-      <c r="R39">
-        <v>2.23</v>
-      </c>
-      <c r="S39">
-        <v>1.29</v>
-      </c>
-      <c r="T39">
-        <v>3.3</v>
-      </c>
-      <c r="U39">
-        <v>2.43</v>
-      </c>
-      <c r="V39">
-        <v>1.53</v>
-      </c>
-      <c r="W39">
-        <v>1.08</v>
-      </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.17</v>
-      </c>
-      <c r="Z39">
-        <v>3.4</v>
-      </c>
-      <c r="AA39">
-        <v>1.76</v>
-      </c>
-      <c r="AB39">
-        <v>1.87</v>
-      </c>
       <c r="AC39">
-        <v>2.85</v>
+        <v>3.52</v>
       </c>
       <c r="AD39">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF39">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG39">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="AK39">
-        <v>1.16</v>
+        <v>1.86</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="O40">
         <v>4.4</v>
       </c>
       <c r="P40">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Q40">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="R40">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="S40">
         <v>1.33</v>
@@ -6859,28 +6859,28 @@
         <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA40">
         <v>1.73</v>
       </c>
       <c r="AB40">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC40">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE40">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF40">
         <v>1.9</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="O44">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P44">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -7499,7 +7499,7 @@
         <v>1.3</v>
       </c>
       <c r="T44">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="U44">
         <v>2.5</v>
@@ -7514,22 +7514,22 @@
         <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA44">
         <v>1.66</v>
       </c>
       <c r="AB44">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC44">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD44">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE44">
         <v>1.13</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AK44">
         <v>1.09</v>
@@ -7810,10 +7810,10 @@
         <v>2.4</v>
       </c>
       <c r="O46">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q46">
         <v>3.04</v>
@@ -7825,16 +7825,16 @@
         <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V46">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W46">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
         <v>1.03</v>
@@ -7843,13 +7843,13 @@
         <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA46">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AB46">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AC46">
         <v>2.35</v>
@@ -7864,7 +7864,7 @@
         <v>1.5</v>
       </c>
       <c r="AG46">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -8154,13 +8154,13 @@
         <v>2.66</v>
       </c>
       <c r="U48">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="V48">
         <v>1.36</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
         <v>1.05</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AK48">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8468,13 +8468,13 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R50">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="S50">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T50">
         <v>4.4</v>
@@ -8486,13 +8486,13 @@
         <v>1.7</v>
       </c>
       <c r="W50">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z50">
         <v>5.85</v>
@@ -8501,16 +8501,16 @@
         <v>1.42</v>
       </c>
       <c r="AB50">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="AC50">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AD50">
         <v>1.72</v>
       </c>
       <c r="AE50">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF50">
         <v>1.64</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AK50">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8643,10 +8643,10 @@
         <v>2.5</v>
       </c>
       <c r="U51">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="V51">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W51">
         <v>1.04</v>
@@ -8655,19 +8655,19 @@
         <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z51">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA51">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AB51">
         <v>1.78</v>
       </c>
       <c r="AC51">
-        <v>3.81</v>
+        <v>3.05</v>
       </c>
       <c r="AD51">
         <v>1.29</v>
@@ -8676,10 +8676,10 @@
         <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG51">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
         <v>1.5</v>
@@ -8794,7 +8794,7 @@
         <v>2.45</v>
       </c>
       <c r="Q52">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="R52">
         <v>2.5</v>
@@ -8833,10 +8833,10 @@
         <v>2.3</v>
       </c>
       <c r="AD52">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AE52">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF52">
         <v>1.43</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8960,10 +8960,10 @@
         <v>2.3</v>
       </c>
       <c r="R53">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="S53">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T53">
         <v>4.3</v>
@@ -8990,7 +8990,7 @@
         <v>1.25</v>
       </c>
       <c r="AB53">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AC53">
         <v>1.8</v>
@@ -8999,13 +8999,13 @@
         <v>2.04</v>
       </c>
       <c r="AE53">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF53">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AG53">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>1.85</v>
       </c>
       <c r="O56">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P56">
         <v>3.5</v>
@@ -9772,7 +9772,7 @@
         <v>3.17</v>
       </c>
       <c r="Q58">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="R58">
         <v>2.2</v>
@@ -9787,7 +9787,7 @@
         <v>2.75</v>
       </c>
       <c r="V58">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W58">
         <v>1.08</v>
@@ -9805,7 +9805,7 @@
         <v>1.92</v>
       </c>
       <c r="AB58">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC58">
         <v>3.4</v>
@@ -9836,7 +9836,7 @@
         <v>1.27</v>
       </c>
       <c r="AK58">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9929,31 +9929,31 @@
         <v>2.87</v>
       </c>
       <c r="O59">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="P59">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
       </c>
       <c r="R59">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S59">
         <v>1.44</v>
       </c>
       <c r="T59">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U59">
         <v>3.3</v>
       </c>
       <c r="V59">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W59">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X59">
         <v>1.08</v>
@@ -9968,7 +9968,7 @@
         <v>2.4</v>
       </c>
       <c r="AB59">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC59">
         <v>4.6</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AK59">
         <v>1.36</v>
@@ -11571,10 +11571,10 @@
         <v>1.91</v>
       </c>
       <c r="S69">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="T69">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="U69">
         <v>3.8</v>
@@ -11583,13 +11583,13 @@
         <v>1.19</v>
       </c>
       <c r="W69">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X69">
         <v>1.06</v>
       </c>
       <c r="Y69">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z69">
         <v>2.46</v>
@@ -11607,7 +11607,7 @@
         <v>1.09</v>
       </c>
       <c r="AE69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF69">
         <v>2.14</v>
@@ -11629,7 +11629,7 @@
         <v>1.34</v>
       </c>
       <c r="AK69">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="O70">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -11758,22 +11758,22 @@
         <v>3.42</v>
       </c>
       <c r="AA70">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB70">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AC70">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD70">
         <v>1.29</v>
       </c>
       <c r="AE70">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG70">
         <v>1.85</v>
@@ -11885,10 +11885,10 @@
         <v>2.1</v>
       </c>
       <c r="O71">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P71">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q71">
         <v>2.68</v>
@@ -11903,7 +11903,7 @@
         <v>2.62</v>
       </c>
       <c r="U71">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="V71">
         <v>1.35</v>
@@ -11912,13 +11912,13 @@
         <v>1.03</v>
       </c>
       <c r="X71">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
         <v>1.36</v>
       </c>
       <c r="Z71">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AA71">
         <v>2.15</v>
@@ -11930,7 +11930,7 @@
         <v>3.8</v>
       </c>
       <c r="AD71">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE71">
         <v>1.08</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O72">
         <v>3.8</v>
@@ -12054,10 +12054,10 @@
         <v>4</v>
       </c>
       <c r="Q72">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R72">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S72">
         <v>1.28</v>
@@ -12081,7 +12081,7 @@
         <v>1.18</v>
       </c>
       <c r="Z72">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="AA72">
         <v>1.55</v>
@@ -12096,13 +12096,13 @@
         <v>1.53</v>
       </c>
       <c r="AE72">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF72">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG72">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK72">
         <v>2.05</v>
@@ -12217,55 +12217,55 @@
         <v>0</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,55 +12380,55 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S74">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T74">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U74">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V74">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W74">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF74">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG74">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12543,16 +12543,16 @@
         <v>4.5</v>
       </c>
       <c r="Q75">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R75">
         <v>2.14</v>
       </c>
       <c r="S75">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T75">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U75">
         <v>3.08</v>
@@ -12570,7 +12570,7 @@
         <v>1.34</v>
       </c>
       <c r="Z75">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="AA75">
         <v>2.18</v>
@@ -12579,7 +12579,7 @@
         <v>1.66</v>
       </c>
       <c r="AC75">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="AD75">
         <v>1.23</v>
@@ -12591,7 +12591,7 @@
         <v>1.95</v>
       </c>
       <c r="AG75">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK75">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -3122,7 +3122,7 @@
         <v>1.7</v>
       </c>
       <c r="AB17">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AC17">
         <v>2.8</v>
@@ -3134,7 +3134,7 @@
         <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG17">
         <v>2</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.7</v>
+        <v>3.94</v>
       </c>
       <c r="O30">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="P30">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q30">
-        <v>2.38</v>
+        <v>5.08</v>
       </c>
       <c r="R30">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="S30">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T30">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="U30">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="V30">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
+        <v>1.01</v>
+      </c>
+      <c r="X30">
+        <v>1.09</v>
+      </c>
+      <c r="Y30">
+        <v>1.37</v>
+      </c>
+      <c r="Z30">
+        <v>3</v>
+      </c>
+      <c r="AA30">
+        <v>2.17</v>
+      </c>
+      <c r="AB30">
+        <v>1.58</v>
+      </c>
+      <c r="AC30">
+        <v>3.85</v>
+      </c>
+      <c r="AD30">
+        <v>1.22</v>
+      </c>
+      <c r="AE30">
         <v>1.03</v>
       </c>
-      <c r="X30">
-        <v>1.07</v>
-      </c>
-      <c r="Y30">
-        <v>1.5</v>
-      </c>
-      <c r="Z30">
-        <v>2.41</v>
-      </c>
-      <c r="AA30">
-        <v>2.46</v>
-      </c>
-      <c r="AB30">
-        <v>1.41</v>
-      </c>
-      <c r="AC30">
-        <v>5.25</v>
-      </c>
-      <c r="AD30">
-        <v>1.1</v>
-      </c>
-      <c r="AE30">
-        <v>1.01</v>
-      </c>
       <c r="AF30">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="AG30">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AK30">
-        <v>2.05</v>
+        <v>1.18</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.94</v>
+        <v>1.7</v>
       </c>
       <c r="O31">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="P31">
+        <v>4.75</v>
+      </c>
+      <c r="Q31">
+        <v>2.38</v>
+      </c>
+      <c r="R31">
+        <v>1.9</v>
+      </c>
+      <c r="S31">
+        <v>1.5</v>
+      </c>
+      <c r="T31">
+        <v>2.24</v>
+      </c>
+      <c r="U31">
+        <v>3.4</v>
+      </c>
+      <c r="V31">
+        <v>1.2</v>
+      </c>
+      <c r="W31">
+        <v>1.03</v>
+      </c>
+      <c r="X31">
+        <v>1.07</v>
+      </c>
+      <c r="Y31">
+        <v>1.5</v>
+      </c>
+      <c r="Z31">
+        <v>2.41</v>
+      </c>
+      <c r="AA31">
+        <v>2.46</v>
+      </c>
+      <c r="AB31">
+        <v>1.41</v>
+      </c>
+      <c r="AC31">
+        <v>5.25</v>
+      </c>
+      <c r="AD31">
+        <v>1.1</v>
+      </c>
+      <c r="AE31">
+        <v>1.01</v>
+      </c>
+      <c r="AF31">
+        <v>2.34</v>
+      </c>
+      <c r="AG31">
+        <v>1.52</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.09</v>
+      </c>
+      <c r="AK31">
         <v>2.05</v>
-      </c>
-      <c r="Q31">
-        <v>5.08</v>
-      </c>
-      <c r="R31">
-        <v>1.78</v>
-      </c>
-      <c r="S31">
-        <v>1.51</v>
-      </c>
-      <c r="T31">
-        <v>2.34</v>
-      </c>
-      <c r="U31">
-        <v>3.27</v>
-      </c>
-      <c r="V31">
-        <v>1.31</v>
-      </c>
-      <c r="W31">
-        <v>1.01</v>
-      </c>
-      <c r="X31">
-        <v>1.09</v>
-      </c>
-      <c r="Y31">
-        <v>1.37</v>
-      </c>
-      <c r="Z31">
-        <v>3</v>
-      </c>
-      <c r="AA31">
-        <v>2.17</v>
-      </c>
-      <c r="AB31">
-        <v>1.58</v>
-      </c>
-      <c r="AC31">
-        <v>3.85</v>
-      </c>
-      <c r="AD31">
-        <v>1.22</v>
-      </c>
-      <c r="AE31">
-        <v>1.03</v>
-      </c>
-      <c r="AF31">
-        <v>1.95</v>
-      </c>
-      <c r="AG31">
-        <v>1.77</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.35</v>
-      </c>
-      <c r="AK31">
-        <v>1.18</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>3.45</v>
       </c>
       <c r="Q34">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R34">
         <v>1.85</v>
@@ -5884,10 +5884,10 @@
         <v>1.14</v>
       </c>
       <c r="Y34">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Z34">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AA34">
         <v>3.2</v>
@@ -5908,23 +5908,23 @@
         <v>2.15</v>
       </c>
       <c r="AG34">
+        <v>1.56</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.35</v>
+      </c>
+      <c r="AK34">
         <v>1.58</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.34</v>
-      </c>
-      <c r="AK34">
-        <v>1.59</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.67</v>
+        <v>3.75</v>
       </c>
       <c r="O36">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P36">
-        <v>4.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q36">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="R36">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="T36">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="U36">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="V36">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
+        <v>1.17</v>
+      </c>
+      <c r="Z36">
+        <v>4.33</v>
+      </c>
+      <c r="AA36">
+        <v>1.67</v>
+      </c>
+      <c r="AB36">
+        <v>2.15</v>
+      </c>
+      <c r="AC36">
+        <v>2.43</v>
+      </c>
+      <c r="AD36">
+        <v>1.44</v>
+      </c>
+      <c r="AE36">
         <v>1.13</v>
       </c>
-      <c r="Z36">
-        <v>5</v>
-      </c>
-      <c r="AA36">
-        <v>1.46</v>
-      </c>
-      <c r="AB36">
-        <v>2.42</v>
-      </c>
-      <c r="AC36">
-        <v>2.25</v>
-      </c>
-      <c r="AD36">
-        <v>1.57</v>
-      </c>
-      <c r="AE36">
+      <c r="AF36">
+        <v>1.61</v>
+      </c>
+      <c r="AG36">
+        <v>2.2</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.24</v>
+      </c>
+      <c r="AK36">
         <v>1.21</v>
-      </c>
-      <c r="AF36">
-        <v>1.47</v>
-      </c>
-      <c r="AG36">
-        <v>2.45</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.19</v>
-      </c>
-      <c r="AK36">
-        <v>2.07</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>1.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q37">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="R37">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="T37">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="U37">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="V37">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA37">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AB37">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="AC37">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AD37">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF37">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK37">
-        <v>1.21</v>
+        <v>2.07</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -9283,7 +9283,7 @@
         <v>2.95</v>
       </c>
       <c r="Q55">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="R55">
         <v>2.01</v>
@@ -9310,28 +9310,28 @@
         <v>1.3</v>
       </c>
       <c r="Z55">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AA55">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AB55">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC55">
-        <v>3.24</v>
+        <v>3.69</v>
       </c>
       <c r="AD55">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE55">
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG55">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9449,13 +9449,13 @@
         <v>2.43</v>
       </c>
       <c r="R56">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="S56">
         <v>1.32</v>
       </c>
       <c r="T56">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U56">
         <v>2.64</v>
@@ -9479,7 +9479,7 @@
         <v>1.77</v>
       </c>
       <c r="AB56">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC56">
         <v>2.8</v>
@@ -9603,16 +9603,16 @@
         <v>1.5</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P57">
         <v>6.25</v>
       </c>
       <c r="Q57">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R57">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="S57">
         <v>1.42</v>
@@ -9621,7 +9621,7 @@
         <v>2.75</v>
       </c>
       <c r="U57">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="V57">
         <v>1.35</v>
@@ -9630,7 +9630,7 @@
         <v>1.02</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
         <v>1.3</v>
@@ -9639,16 +9639,16 @@
         <v>2.97</v>
       </c>
       <c r="AA57">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AB57">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC57">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD57">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE57">
         <v>1.03</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK57">
         <v>2.3</v>
@@ -9781,13 +9781,13 @@
         <v>1.36</v>
       </c>
       <c r="T58">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="U58">
         <v>2.75</v>
       </c>
       <c r="V58">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W58">
         <v>1.08</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB60">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O61">
         <v>2.95</v>
@@ -10261,10 +10261,10 @@
         <v>3</v>
       </c>
       <c r="Q61">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="R61">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S61">
         <v>1.48</v>
@@ -10297,7 +10297,7 @@
         <v>1.58</v>
       </c>
       <c r="AC61">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AD61">
         <v>1.18</v>
@@ -10309,7 +10309,7 @@
         <v>1.9</v>
       </c>
       <c r="AG61">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y67">
         <v>1.22</v>
@@ -11272,13 +11272,13 @@
         <v>1.9</v>
       </c>
       <c r="AB67">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC67">
         <v>3.25</v>
       </c>
       <c r="AD67">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AE67">
         <v>1.08</v>
@@ -11426,13 +11426,13 @@
         <v>1</v>
       </c>
       <c r="Y68">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z68">
         <v>3.72</v>
       </c>
       <c r="AA68">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB68">
         <v>2</v>
@@ -11447,10 +11447,10 @@
         <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG68">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O70">
         <v>3.5</v>
@@ -11758,25 +11758,25 @@
         <v>3.42</v>
       </c>
       <c r="AA70">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB70">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AC70">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD70">
         <v>1.29</v>
       </c>
       <c r="AE70">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF70">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AG70">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G73">
@@ -12217,34 +12217,34 @@
         <v>0</v>
       </c>
       <c r="Q73">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="R73">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S73">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T73">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U73">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="V73">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W73">
         <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z73">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA73">
         <v>2.02</v>
@@ -12253,19 +12253,19 @@
         <v>1.74</v>
       </c>
       <c r="AC73">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="AD73">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE73">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF73">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AG73">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK73">
-        <v>2.41</v>
+        <v>1.98</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q74">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="R74">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="S74">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T74">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U74">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="V74">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W74">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
         <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z74">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AA74">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AB74">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AC74">
-        <v>3.38</v>
+        <v>3.92</v>
       </c>
       <c r="AD74">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE74">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF74">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AG74">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK74">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,52 +12534,52 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P75">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="R75">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S75">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T75">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="U75">
+        <v>2.96</v>
+      </c>
+      <c r="V75">
+        <v>1.32</v>
+      </c>
+      <c r="W75">
+        <v>1.05</v>
+      </c>
+      <c r="X75">
+        <v>1.01</v>
+      </c>
+      <c r="Y75">
+        <v>1.3</v>
+      </c>
+      <c r="Z75">
         <v>3.08</v>
       </c>
-      <c r="V75">
-        <v>1.3</v>
-      </c>
-      <c r="W75">
-        <v>1.06</v>
-      </c>
-      <c r="X75">
-        <v>1.02</v>
-      </c>
-      <c r="Y75">
-        <v>1.34</v>
-      </c>
-      <c r="Z75">
-        <v>2.83</v>
-      </c>
       <c r="AA75">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="AB75">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC75">
-        <v>3.92</v>
+        <v>3.54</v>
       </c>
       <c r="AD75">
         <v>1.23</v>
@@ -12588,10 +12588,10 @@
         <v>1.03</v>
       </c>
       <c r="AF75">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AG75">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK75">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -3134,7 +3134,7 @@
         <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
         <v>2</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.94</v>
+        <v>1.7</v>
       </c>
       <c r="O30">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="P30">
+        <v>4.75</v>
+      </c>
+      <c r="Q30">
+        <v>2.38</v>
+      </c>
+      <c r="R30">
+        <v>1.9</v>
+      </c>
+      <c r="S30">
+        <v>1.5</v>
+      </c>
+      <c r="T30">
+        <v>2.24</v>
+      </c>
+      <c r="U30">
+        <v>3.4</v>
+      </c>
+      <c r="V30">
+        <v>1.2</v>
+      </c>
+      <c r="W30">
+        <v>1.03</v>
+      </c>
+      <c r="X30">
+        <v>1.07</v>
+      </c>
+      <c r="Y30">
+        <v>1.5</v>
+      </c>
+      <c r="Z30">
+        <v>2.41</v>
+      </c>
+      <c r="AA30">
+        <v>2.46</v>
+      </c>
+      <c r="AB30">
+        <v>1.41</v>
+      </c>
+      <c r="AC30">
+        <v>5.25</v>
+      </c>
+      <c r="AD30">
+        <v>1.1</v>
+      </c>
+      <c r="AE30">
+        <v>1.01</v>
+      </c>
+      <c r="AF30">
+        <v>2.34</v>
+      </c>
+      <c r="AG30">
+        <v>1.52</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.09</v>
+      </c>
+      <c r="AK30">
         <v>2.05</v>
-      </c>
-      <c r="Q30">
-        <v>5.08</v>
-      </c>
-      <c r="R30">
-        <v>1.78</v>
-      </c>
-      <c r="S30">
-        <v>1.51</v>
-      </c>
-      <c r="T30">
-        <v>2.34</v>
-      </c>
-      <c r="U30">
-        <v>3.27</v>
-      </c>
-      <c r="V30">
-        <v>1.31</v>
-      </c>
-      <c r="W30">
-        <v>1.01</v>
-      </c>
-      <c r="X30">
-        <v>1.09</v>
-      </c>
-      <c r="Y30">
-        <v>1.37</v>
-      </c>
-      <c r="Z30">
-        <v>3</v>
-      </c>
-      <c r="AA30">
-        <v>2.17</v>
-      </c>
-      <c r="AB30">
-        <v>1.58</v>
-      </c>
-      <c r="AC30">
-        <v>3.85</v>
-      </c>
-      <c r="AD30">
-        <v>1.22</v>
-      </c>
-      <c r="AE30">
-        <v>1.03</v>
-      </c>
-      <c r="AF30">
-        <v>1.95</v>
-      </c>
-      <c r="AG30">
-        <v>1.77</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.35</v>
-      </c>
-      <c r="AK30">
-        <v>1.18</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.7</v>
+        <v>3.94</v>
       </c>
       <c r="O31">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="P31">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q31">
-        <v>2.38</v>
+        <v>5.08</v>
       </c>
       <c r="R31">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="S31">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T31">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="U31">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="V31">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
+        <v>1.01</v>
+      </c>
+      <c r="X31">
+        <v>1.09</v>
+      </c>
+      <c r="Y31">
+        <v>1.37</v>
+      </c>
+      <c r="Z31">
+        <v>3</v>
+      </c>
+      <c r="AA31">
+        <v>2.17</v>
+      </c>
+      <c r="AB31">
+        <v>1.58</v>
+      </c>
+      <c r="AC31">
+        <v>3.85</v>
+      </c>
+      <c r="AD31">
+        <v>1.22</v>
+      </c>
+      <c r="AE31">
         <v>1.03</v>
       </c>
-      <c r="X31">
-        <v>1.07</v>
-      </c>
-      <c r="Y31">
-        <v>1.5</v>
-      </c>
-      <c r="Z31">
-        <v>2.41</v>
-      </c>
-      <c r="AA31">
-        <v>2.46</v>
-      </c>
-      <c r="AB31">
-        <v>1.41</v>
-      </c>
-      <c r="AC31">
-        <v>5.25</v>
-      </c>
-      <c r="AD31">
-        <v>1.1</v>
-      </c>
-      <c r="AE31">
-        <v>1.01</v>
-      </c>
       <c r="AF31">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="AG31">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AK31">
-        <v>2.05</v>
+        <v>1.18</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -9440,10 +9440,10 @@
         <v>1.85</v>
       </c>
       <c r="O56">
+        <v>3.62</v>
+      </c>
+      <c r="P56">
         <v>3.55</v>
-      </c>
-      <c r="P56">
-        <v>3.5</v>
       </c>
       <c r="Q56">
         <v>2.43</v>
@@ -11607,7 +11607,7 @@
         <v>1.09</v>
       </c>
       <c r="AE69">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF69">
         <v>2.14</v>
@@ -12048,16 +12048,16 @@
         <v>1.7</v>
       </c>
       <c r="O72">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P72">
         <v>4</v>
       </c>
       <c r="Q72">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R72">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S72">
         <v>1.28</v>
@@ -12096,13 +12096,13 @@
         <v>1.53</v>
       </c>
       <c r="AE72">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF72">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG72">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q73">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="R73">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="S73">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T73">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U73">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="V73">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W73">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X73">
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z73">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AA73">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AB73">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC73">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="AD73">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE73">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF73">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AG73">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK73">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="O74">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P74">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q74">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="R74">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="S74">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T74">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U74">
+        <v>2.96</v>
+      </c>
+      <c r="V74">
+        <v>1.32</v>
+      </c>
+      <c r="W74">
+        <v>1.05</v>
+      </c>
+      <c r="X74">
+        <v>1</v>
+      </c>
+      <c r="Y74">
+        <v>1.3</v>
+      </c>
+      <c r="Z74">
         <v>3.08</v>
       </c>
-      <c r="V74">
-        <v>1.3</v>
-      </c>
-      <c r="W74">
-        <v>1.06</v>
-      </c>
-      <c r="X74">
-        <v>1.02</v>
-      </c>
-      <c r="Y74">
-        <v>1.34</v>
-      </c>
-      <c r="Z74">
-        <v>2.83</v>
-      </c>
       <c r="AA74">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="AB74">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC74">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="AD74">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE74">
         <v>1.03</v>
       </c>
       <c r="AF74">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AG74">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK74">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q75">
-        <v>2.03</v>
+        <v>2.47</v>
       </c>
       <c r="R75">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="S75">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T75">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="U75">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="V75">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W75">
+        <v>1.07</v>
+      </c>
+      <c r="X75">
+        <v>1.03</v>
+      </c>
+      <c r="Y75">
+        <v>1.34</v>
+      </c>
+      <c r="Z75">
+        <v>3.11</v>
+      </c>
+      <c r="AA75">
+        <v>2.05</v>
+      </c>
+      <c r="AB75">
+        <v>1.75</v>
+      </c>
+      <c r="AC75">
+        <v>3.52</v>
+      </c>
+      <c r="AD75">
+        <v>1.24</v>
+      </c>
+      <c r="AE75">
         <v>1.05</v>
       </c>
-      <c r="X75">
-        <v>1.01</v>
-      </c>
-      <c r="Y75">
-        <v>1.3</v>
-      </c>
-      <c r="Z75">
-        <v>3.08</v>
-      </c>
-      <c r="AA75">
-        <v>2.02</v>
-      </c>
-      <c r="AB75">
-        <v>1.74</v>
-      </c>
-      <c r="AC75">
-        <v>3.54</v>
-      </c>
-      <c r="AD75">
-        <v>1.23</v>
-      </c>
-      <c r="AE75">
-        <v>1.03</v>
-      </c>
       <c r="AF75">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AG75">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="O5">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
         <v>2.85</v>
@@ -1139,10 +1139,10 @@
         <v>2.14</v>
       </c>
       <c r="S5">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T5">
-        <v>3.21</v>
+        <v>2.86</v>
       </c>
       <c r="U5">
         <v>2.63</v>
@@ -1157,31 +1157,31 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AA5">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AC5">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AD5">
         <v>1.34</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1293,7 +1293,7 @@
         <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -1308,34 +1308,34 @@
         <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="V6">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AA6">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AB6">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC6">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="AD6">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
         <v>1.09</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="O7">
         <v>2.93</v>
       </c>
       <c r="P7">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q7">
         <v>3.26</v>
@@ -1480,10 +1480,10 @@
         <v>1</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="Z7">
         <v>2.59</v>
@@ -1492,16 +1492,16 @@
         <v>2.35</v>
       </c>
       <c r="AB7">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC7">
-        <v>4.61</v>
+        <v>4.67</v>
       </c>
       <c r="AD7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE7">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
         <v>1.98</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P8">
-        <v>3.9</v>
+        <v>4.13</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>3.5</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q10">
         <v>2.73</v>
@@ -1969,7 +1969,7 @@
         <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
         <v>1.24</v>
@@ -1993,10 +1993,10 @@
         <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -3738,25 +3738,25 @@
         <v>4.9</v>
       </c>
       <c r="P21">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="Q21">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R21">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V21">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="W21">
         <v>1.12</v>
@@ -3765,31 +3765,31 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="AA21">
         <v>1.59</v>
       </c>
       <c r="AB21">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AC21">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD21">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE21">
         <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG21">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK21">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O25">
         <v>3.2</v>
       </c>
       <c r="P25">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="Q25">
         <v>2.6</v>
@@ -4399,7 +4399,7 @@
         <v>1.95</v>
       </c>
       <c r="S25">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T25">
         <v>2.45</v>
@@ -4408,7 +4408,7 @@
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
         <v>1.04</v>
@@ -4420,13 +4420,13 @@
         <v>1.43</v>
       </c>
       <c r="Z25">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="AA25">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="AB25">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC25">
         <v>4.5</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P27">
         <v>3.85</v>
@@ -4728,7 +4728,7 @@
         <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
         <v>2.59</v>
@@ -4737,7 +4737,7 @@
         <v>1.46</v>
       </c>
       <c r="W27">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
         <v>1.03</v>
@@ -4752,22 +4752,22 @@
         <v>1.72</v>
       </c>
       <c r="AB27">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC27">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AD27">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
         <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4879,7 +4879,7 @@
         <v>3.6</v>
       </c>
       <c r="P28">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="Q28">
         <v>2.42</v>
@@ -4903,7 +4903,7 @@
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y28">
         <v>1.2</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
         <v>1.88</v>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P29">
         <v>3.9</v>
@@ -5057,7 +5057,7 @@
         <v>2.65</v>
       </c>
       <c r="U29">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
         <v>1.39</v>
@@ -5078,13 +5078,13 @@
         <v>1.89</v>
       </c>
       <c r="AB29">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC29">
         <v>3.4</v>
       </c>
       <c r="AD29">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE29">
         <v>1.05</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.7</v>
+        <v>3.94</v>
       </c>
       <c r="O30">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="P30">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q30">
-        <v>2.38</v>
+        <v>4.33</v>
       </c>
       <c r="R30">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="S30">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T30">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="U30">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="V30">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
+        <v>1.01</v>
+      </c>
+      <c r="X30">
+        <v>1.09</v>
+      </c>
+      <c r="Y30">
+        <v>1.37</v>
+      </c>
+      <c r="Z30">
+        <v>3</v>
+      </c>
+      <c r="AA30">
+        <v>2.17</v>
+      </c>
+      <c r="AB30">
+        <v>1.58</v>
+      </c>
+      <c r="AC30">
+        <v>3.84</v>
+      </c>
+      <c r="AD30">
+        <v>1.22</v>
+      </c>
+      <c r="AE30">
         <v>1.03</v>
       </c>
-      <c r="X30">
-        <v>1.07</v>
-      </c>
-      <c r="Y30">
-        <v>1.5</v>
-      </c>
-      <c r="Z30">
-        <v>2.41</v>
-      </c>
-      <c r="AA30">
-        <v>2.46</v>
-      </c>
-      <c r="AB30">
-        <v>1.41</v>
-      </c>
-      <c r="AC30">
-        <v>5.25</v>
-      </c>
-      <c r="AD30">
-        <v>1.1</v>
-      </c>
-      <c r="AE30">
-        <v>1.01</v>
-      </c>
       <c r="AF30">
-        <v>2.34</v>
+        <v>1.92</v>
       </c>
       <c r="AG30">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
       <c r="AK30">
-        <v>2.05</v>
+        <v>1.18</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.94</v>
+        <v>1.69</v>
       </c>
       <c r="O31">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>2.05</v>
+        <v>5.2</v>
       </c>
       <c r="Q31">
-        <v>5.08</v>
+        <v>2.43</v>
       </c>
       <c r="R31">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="S31">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T31">
+        <v>2.45</v>
+      </c>
+      <c r="U31">
+        <v>3.4</v>
+      </c>
+      <c r="V31">
+        <v>1.29</v>
+      </c>
+      <c r="W31">
+        <v>1.05</v>
+      </c>
+      <c r="X31">
+        <v>1.11</v>
+      </c>
+      <c r="Y31">
+        <v>1.5</v>
+      </c>
+      <c r="Z31">
+        <v>2.41</v>
+      </c>
+      <c r="AA31">
+        <v>2.45</v>
+      </c>
+      <c r="AB31">
+        <v>1.45</v>
+      </c>
+      <c r="AC31">
+        <v>5.25</v>
+      </c>
+      <c r="AD31">
+        <v>1.14</v>
+      </c>
+      <c r="AE31">
+        <v>1.02</v>
+      </c>
+      <c r="AF31">
         <v>2.34</v>
       </c>
-      <c r="U31">
-        <v>3.27</v>
-      </c>
-      <c r="V31">
-        <v>1.31</v>
-      </c>
-      <c r="W31">
-        <v>1.01</v>
-      </c>
-      <c r="X31">
-        <v>1.09</v>
-      </c>
-      <c r="Y31">
-        <v>1.37</v>
-      </c>
-      <c r="Z31">
-        <v>3</v>
-      </c>
-      <c r="AA31">
-        <v>2.17</v>
-      </c>
-      <c r="AB31">
-        <v>1.58</v>
-      </c>
-      <c r="AC31">
-        <v>3.85</v>
-      </c>
-      <c r="AD31">
-        <v>1.22</v>
-      </c>
-      <c r="AE31">
-        <v>1.03</v>
-      </c>
-      <c r="AF31">
-        <v>1.95</v>
-      </c>
       <c r="AG31">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.35</v>
       </c>
       <c r="AK31">
-        <v>1.18</v>
+        <v>2.05</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>2.38</v>
+      </c>
+      <c r="R38">
+        <v>2.05</v>
+      </c>
+      <c r="S38">
+        <v>1.4</v>
+      </c>
+      <c r="T38">
+        <v>2.75</v>
+      </c>
+      <c r="U38">
+        <v>3</v>
+      </c>
+      <c r="V38">
+        <v>1.33</v>
+      </c>
+      <c r="W38">
+        <v>1.06</v>
+      </c>
+      <c r="X38">
+        <v>1</v>
+      </c>
+      <c r="Y38">
+        <v>1.28</v>
+      </c>
+      <c r="Z38">
+        <v>3.08</v>
+      </c>
+      <c r="AA38">
+        <v>1.99</v>
+      </c>
+      <c r="AB38">
         <v>1.73</v>
       </c>
-      <c r="Q38">
-        <v>4.5</v>
-      </c>
-      <c r="R38">
-        <v>2.23</v>
-      </c>
-      <c r="S38">
-        <v>1.29</v>
-      </c>
-      <c r="T38">
-        <v>3.3</v>
-      </c>
-      <c r="U38">
-        <v>2.43</v>
-      </c>
-      <c r="V38">
-        <v>1.53</v>
-      </c>
-      <c r="W38">
-        <v>1.08</v>
-      </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>1.19</v>
-      </c>
-      <c r="Z38">
-        <v>3.4</v>
-      </c>
-      <c r="AA38">
-        <v>1.76</v>
-      </c>
-      <c r="AB38">
+      <c r="AC38">
+        <v>3.6</v>
+      </c>
+      <c r="AD38">
+        <v>1.28</v>
+      </c>
+      <c r="AE38">
+        <v>1.04</v>
+      </c>
+      <c r="AF38">
+        <v>1.85</v>
+      </c>
+      <c r="AG38">
+        <v>1.84</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>1.23</v>
+      </c>
+      <c r="AK38">
         <v>1.87</v>
-      </c>
-      <c r="AC38">
-        <v>2.85</v>
-      </c>
-      <c r="AD38">
-        <v>1.47</v>
-      </c>
-      <c r="AE38">
-        <v>1.13</v>
-      </c>
-      <c r="AF38">
-        <v>1.57</v>
-      </c>
-      <c r="AG38">
-        <v>2.21</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.19</v>
-      </c>
-      <c r="AK38">
-        <v>1.16</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q39">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="R39">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="U39">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="V39">
+        <v>1.48</v>
+      </c>
+      <c r="W39">
+        <v>1.08</v>
+      </c>
+      <c r="X39">
+        <v>1.02</v>
+      </c>
+      <c r="Y39">
+        <v>1.18</v>
+      </c>
+      <c r="Z39">
+        <v>3.4</v>
+      </c>
+      <c r="AA39">
+        <v>1.76</v>
+      </c>
+      <c r="AB39">
+        <v>1.87</v>
+      </c>
+      <c r="AC39">
+        <v>2.85</v>
+      </c>
+      <c r="AD39">
         <v>1.33</v>
       </c>
-      <c r="W39">
-        <v>1.06</v>
-      </c>
-      <c r="X39">
-        <v>1.04</v>
-      </c>
-      <c r="Y39">
-        <v>1.33</v>
-      </c>
-      <c r="Z39">
-        <v>3.08</v>
-      </c>
-      <c r="AA39">
-        <v>1.99</v>
-      </c>
-      <c r="AB39">
-        <v>1.73</v>
-      </c>
-      <c r="AC39">
-        <v>3.52</v>
-      </c>
-      <c r="AD39">
-        <v>1.28</v>
-      </c>
       <c r="AE39">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AF39">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AG39">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AK39">
-        <v>1.86</v>
+        <v>1.16</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7028,22 +7028,22 @@
         <v>1.12</v>
       </c>
       <c r="Z41">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA41">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB41">
+        <v>2.23</v>
+      </c>
+      <c r="AC41">
         <v>2.3</v>
-      </c>
-      <c r="AC41">
-        <v>2.45</v>
       </c>
       <c r="AD41">
         <v>1.58</v>
       </c>
       <c r="AE41">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF41">
         <v>1.49</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O42">
         <v>3.8</v>
@@ -7164,16 +7164,16 @@
         <v>1.98</v>
       </c>
       <c r="Q42">
-        <v>3.87</v>
+        <v>3.23</v>
       </c>
       <c r="R42">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="S42">
         <v>1.26</v>
       </c>
       <c r="T42">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="U42">
         <v>2.5</v>
@@ -7200,7 +7200,7 @@
         <v>2.22</v>
       </c>
       <c r="AC42">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="AD42">
         <v>1.41</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="AK42">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7976,16 +7976,16 @@
         <v>3.8</v>
       </c>
       <c r="P47">
-        <v>3.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q47">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="R47">
         <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T47">
         <v>3.3</v>
@@ -8003,7 +8003,7 @@
         <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z47">
         <v>3.95</v>
@@ -8012,10 +8012,10 @@
         <v>1.66</v>
       </c>
       <c r="AB47">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC47">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD47">
         <v>1.42</v>
@@ -8043,7 +8043,7 @@
         <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8136,7 +8136,7 @@
         <v>2.6</v>
       </c>
       <c r="O48">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P48">
         <v>2.5</v>
@@ -8145,52 +8145,52 @@
         <v>3.25</v>
       </c>
       <c r="R48">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="S48">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="T48">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="U48">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="V48">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W48">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
         <v>1.05</v>
       </c>
       <c r="Y48">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z48">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="AA48">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AB48">
         <v>1.57</v>
       </c>
       <c r="AC48">
-        <v>3.42</v>
+        <v>4.25</v>
       </c>
       <c r="AD48">
         <v>1.18</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF48">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG48">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AK48">
         <v>1.4</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P49">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q49">
         <v>2.97</v>
       </c>
       <c r="R49">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S49">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="U49">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="V49">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W49">
         <v>1.07</v>
@@ -8329,31 +8329,31 @@
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z49">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA49">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB49">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC49">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD49">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE49">
         <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG49">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8477,7 +8477,7 @@
         <v>1.14</v>
       </c>
       <c r="T50">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="U50">
         <v>2</v>
@@ -8495,13 +8495,13 @@
         <v>1.12</v>
       </c>
       <c r="Z50">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
       <c r="AA50">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB50">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC50">
         <v>2.05</v>
@@ -8513,10 +8513,10 @@
         <v>1.25</v>
       </c>
       <c r="AF50">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG50">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8788,13 +8788,13 @@
         <v>2.2</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="Q52">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="R52">
         <v>2.5</v>
@@ -8806,7 +8806,7 @@
         <v>3.6</v>
       </c>
       <c r="U52">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="V52">
         <v>1.62</v>
@@ -8858,7 +8858,7 @@
         <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="O53">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P53">
-        <v>2.83</v>
+        <v>3.28</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
       </c>
       <c r="R53">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="S53">
         <v>1.17</v>
@@ -8999,7 +8999,7 @@
         <v>2.04</v>
       </c>
       <c r="AE53">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF53">
         <v>1.3</v>
@@ -9126,16 +9126,16 @@
         <v>2.09</v>
       </c>
       <c r="S54">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T54">
+        <v>2.92</v>
+      </c>
+      <c r="U54">
         <v>2.73</v>
       </c>
-      <c r="U54">
-        <v>2.93</v>
-      </c>
       <c r="V54">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
         <v>1.05</v>
@@ -9162,13 +9162,13 @@
         <v>1.31</v>
       </c>
       <c r="AE54">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG54">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK54">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9289,10 +9289,10 @@
         <v>2.01</v>
       </c>
       <c r="S55">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T55">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U55">
         <v>2.88</v>
@@ -9301,7 +9301,7 @@
         <v>1.36</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9322,16 +9322,16 @@
         <v>3.69</v>
       </c>
       <c r="AD55">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE55">
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AG55">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Q57">
         <v>2.08</v>
@@ -9639,10 +9639,10 @@
         <v>2.97</v>
       </c>
       <c r="AA57">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AB57">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC57">
         <v>3.58</v>
@@ -9654,10 +9654,10 @@
         <v>1.03</v>
       </c>
       <c r="AF57">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AG57">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="O59">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="P59">
         <v>2.6</v>
@@ -9944,7 +9944,7 @@
         <v>1.44</v>
       </c>
       <c r="T59">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U59">
         <v>3.3</v>
@@ -9953,7 +9953,7 @@
         <v>1.33</v>
       </c>
       <c r="W59">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X59">
         <v>1.08</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="O61">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P61">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="Q61">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R61">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S61">
         <v>1.48</v>
@@ -10279,22 +10279,22 @@
         <v>1.3</v>
       </c>
       <c r="W61">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X61">
         <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Z61">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="AA61">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AB61">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC61">
         <v>3.9</v>
@@ -10303,13 +10303,13 @@
         <v>1.18</v>
       </c>
       <c r="AE61">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF61">
         <v>1.9</v>
       </c>
       <c r="AG61">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK61">
         <v>1.55</v>
@@ -10593,10 +10593,10 @@
         <v>1.91</v>
       </c>
       <c r="S63">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T63">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="U63">
         <v>3.25</v>
@@ -10611,28 +10611,28 @@
         <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Z63">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AA63">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="AB63">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AC63">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AD63">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE63">
         <v>1</v>
       </c>
       <c r="AF63">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG63">
         <v>1.65</v>
@@ -10651,7 +10651,7 @@
         <v>1.29</v>
       </c>
       <c r="AK63">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,25 +10750,25 @@
         <v>3.1</v>
       </c>
       <c r="Q64">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="R64">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S64">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T64">
         <v>2.34</v>
       </c>
       <c r="U64">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="V64">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W64">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X64">
         <v>1.03</v>
@@ -10783,7 +10783,7 @@
         <v>2.32</v>
       </c>
       <c r="AB64">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AC64">
         <v>4.15</v>
@@ -10798,7 +10798,7 @@
         <v>1.9</v>
       </c>
       <c r="AG64">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK64">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10922,7 +10922,7 @@
         <v>1.58</v>
       </c>
       <c r="T65">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U65">
         <v>3.5</v>
@@ -10937,7 +10937,7 @@
         <v>1.07</v>
       </c>
       <c r="Y65">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Z65">
         <v>2.36</v>
@@ -10955,10 +10955,10 @@
         <v>1.1</v>
       </c>
       <c r="AE65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF65">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG65">
         <v>1.65</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,22 +11076,22 @@
         <v>3.75</v>
       </c>
       <c r="Q66">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R66">
         <v>2.08</v>
       </c>
       <c r="S66">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T66">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="U66">
         <v>3.2</v>
       </c>
       <c r="V66">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W66">
         <v>1.05</v>
@@ -11106,7 +11106,7 @@
         <v>2.7</v>
       </c>
       <c r="AA66">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB66">
         <v>1.62</v>
@@ -11121,7 +11121,7 @@
         <v>1.03</v>
       </c>
       <c r="AF66">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG66">
         <v>1.75</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK66">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11885,10 +11885,10 @@
         <v>2.1</v>
       </c>
       <c r="O71">
+        <v>3.4</v>
+      </c>
+      <c r="P71">
         <v>3.3</v>
-      </c>
-      <c r="P71">
-        <v>3.6</v>
       </c>
       <c r="Q71">
         <v>2.68</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="O74">
+        <v>3.4</v>
+      </c>
+      <c r="P74">
         <v>3.9</v>
       </c>
-      <c r="P74">
-        <v>5.5</v>
-      </c>
       <c r="Q74">
-        <v>2.03</v>
+        <v>2.47</v>
       </c>
       <c r="R74">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S74">
         <v>1.36</v>
       </c>
       <c r="T74">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U74">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="V74">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W74">
+        <v>1.07</v>
+      </c>
+      <c r="X74">
+        <v>1.03</v>
+      </c>
+      <c r="Y74">
+        <v>1.34</v>
+      </c>
+      <c r="Z74">
+        <v>3.11</v>
+      </c>
+      <c r="AA74">
+        <v>2.05</v>
+      </c>
+      <c r="AB74">
+        <v>1.75</v>
+      </c>
+      <c r="AC74">
+        <v>3.52</v>
+      </c>
+      <c r="AD74">
+        <v>1.24</v>
+      </c>
+      <c r="AE74">
         <v>1.05</v>
       </c>
-      <c r="X74">
-        <v>1</v>
-      </c>
-      <c r="Y74">
-        <v>1.3</v>
-      </c>
-      <c r="Z74">
-        <v>3.08</v>
-      </c>
-      <c r="AA74">
-        <v>2.02</v>
-      </c>
-      <c r="AB74">
-        <v>1.74</v>
-      </c>
-      <c r="AC74">
-        <v>3.5</v>
-      </c>
-      <c r="AD74">
-        <v>1.22</v>
-      </c>
-      <c r="AE74">
-        <v>1.03</v>
-      </c>
       <c r="AF74">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AG74">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK74">
-        <v>2.46</v>
+        <v>1.8</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P75">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="Q75">
-        <v>2.47</v>
+        <v>2.03</v>
       </c>
       <c r="R75">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S75">
         <v>1.36</v>
       </c>
       <c r="T75">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U75">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="V75">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X75">
+        <v>1</v>
+      </c>
+      <c r="Y75">
+        <v>1.3</v>
+      </c>
+      <c r="Z75">
+        <v>3.08</v>
+      </c>
+      <c r="AA75">
+        <v>2.02</v>
+      </c>
+      <c r="AB75">
+        <v>1.74</v>
+      </c>
+      <c r="AC75">
+        <v>3.5</v>
+      </c>
+      <c r="AD75">
+        <v>1.22</v>
+      </c>
+      <c r="AE75">
         <v>1.03</v>
       </c>
-      <c r="Y75">
-        <v>1.34</v>
-      </c>
-      <c r="Z75">
-        <v>3.11</v>
-      </c>
-      <c r="AA75">
-        <v>2.05</v>
-      </c>
-      <c r="AB75">
-        <v>1.75</v>
-      </c>
-      <c r="AC75">
-        <v>3.52</v>
-      </c>
-      <c r="AD75">
-        <v>1.24</v>
-      </c>
-      <c r="AE75">
-        <v>1.05</v>
-      </c>
       <c r="AF75">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AG75">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK75">
-        <v>1.8</v>
+        <v>2.46</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O13">
         <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -2443,16 +2443,16 @@
         <v>2.18</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U13">
         <v>2.7</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
         <v>1.08</v>
@@ -2470,7 +2470,7 @@
         <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC13">
         <v>3.08</v>
@@ -2485,7 +2485,7 @@
         <v>1.68</v>
       </c>
       <c r="AG13">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -3095,10 +3095,10 @@
         <v>2.21</v>
       </c>
       <c r="S17">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T17">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="U17">
         <v>2.63</v>
@@ -3107,7 +3107,7 @@
         <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
         <v>1.04</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O18">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>6.8</v>
       </c>
       <c r="Q18">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="R18">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="S18">
         <v>1.17</v>
@@ -3264,10 +3264,10 @@
         <v>4.5</v>
       </c>
       <c r="U18">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="V18">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W18">
         <v>1.14</v>
@@ -3279,13 +3279,13 @@
         <v>1.07</v>
       </c>
       <c r="Z18">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="AA18">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB18">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC18">
         <v>2</v>
@@ -3297,10 +3297,10 @@
         <v>1.26</v>
       </c>
       <c r="AF18">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,10 +3409,10 @@
         <v>1.33</v>
       </c>
       <c r="O19">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P19">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>1.53</v>
@@ -3421,37 +3421,37 @@
         <v>3</v>
       </c>
       <c r="S19">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T19">
-        <v>3.76</v>
+        <v>3.98</v>
       </c>
       <c r="U19">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W19">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z19">
-        <v>5.95</v>
+        <v>6.15</v>
       </c>
       <c r="AA19">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AB19">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AC19">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AD19">
         <v>1.8</v>
@@ -3460,10 +3460,10 @@
         <v>1.34</v>
       </c>
       <c r="AF19">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AG19">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.73</v>
+        <v>2.48</v>
       </c>
       <c r="O23">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="P23">
-        <v>2.79</v>
+        <v>2.52</v>
       </c>
       <c r="Q23">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="R23">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S23">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="T23">
-        <v>2.57</v>
+        <v>2.42</v>
       </c>
       <c r="U23">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="V23">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W23">
         <v>1.02</v>
@@ -4091,16 +4091,16 @@
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z23">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="AA23">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AB23">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AC23">
         <v>4.25</v>
@@ -4112,10 +4112,10 @@
         <v>1.01</v>
       </c>
       <c r="AF23">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AG23">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AK23">
         <v>1.48</v>
@@ -4553,13 +4553,13 @@
         <v>3.5</v>
       </c>
       <c r="P26">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
       </c>
       <c r="R26">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
         <v>1.33</v>
@@ -4568,28 +4568,28 @@
         <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V26">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W26">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>3.76</v>
+        <v>3.92</v>
       </c>
       <c r="AA26">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB26">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AC26">
         <v>2.75</v>
@@ -4604,7 +4604,7 @@
         <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
         <v>1.72</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.94</v>
+        <v>1.69</v>
       </c>
       <c r="O30">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
+        <v>5.2</v>
+      </c>
+      <c r="Q30">
+        <v>2.43</v>
+      </c>
+      <c r="R30">
+        <v>1.85</v>
+      </c>
+      <c r="S30">
+        <v>1.5</v>
+      </c>
+      <c r="T30">
+        <v>2.45</v>
+      </c>
+      <c r="U30">
+        <v>3.4</v>
+      </c>
+      <c r="V30">
+        <v>1.29</v>
+      </c>
+      <c r="W30">
+        <v>1.05</v>
+      </c>
+      <c r="X30">
+        <v>1.11</v>
+      </c>
+      <c r="Y30">
+        <v>1.5</v>
+      </c>
+      <c r="Z30">
+        <v>2.41</v>
+      </c>
+      <c r="AA30">
+        <v>2.45</v>
+      </c>
+      <c r="AB30">
+        <v>1.45</v>
+      </c>
+      <c r="AC30">
+        <v>5.25</v>
+      </c>
+      <c r="AD30">
+        <v>1.14</v>
+      </c>
+      <c r="AE30">
+        <v>1.02</v>
+      </c>
+      <c r="AF30">
+        <v>2.34</v>
+      </c>
+      <c r="AG30">
+        <v>1.57</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.35</v>
+      </c>
+      <c r="AK30">
         <v>2.05</v>
-      </c>
-      <c r="Q30">
-        <v>4.33</v>
-      </c>
-      <c r="R30">
-        <v>1.78</v>
-      </c>
-      <c r="S30">
-        <v>1.51</v>
-      </c>
-      <c r="T30">
-        <v>2.34</v>
-      </c>
-      <c r="U30">
-        <v>3.27</v>
-      </c>
-      <c r="V30">
-        <v>1.31</v>
-      </c>
-      <c r="W30">
-        <v>1.01</v>
-      </c>
-      <c r="X30">
-        <v>1.09</v>
-      </c>
-      <c r="Y30">
-        <v>1.37</v>
-      </c>
-      <c r="Z30">
-        <v>3</v>
-      </c>
-      <c r="AA30">
-        <v>2.17</v>
-      </c>
-      <c r="AB30">
-        <v>1.58</v>
-      </c>
-      <c r="AC30">
-        <v>3.84</v>
-      </c>
-      <c r="AD30">
-        <v>1.22</v>
-      </c>
-      <c r="AE30">
-        <v>1.03</v>
-      </c>
-      <c r="AF30">
-        <v>1.92</v>
-      </c>
-      <c r="AG30">
-        <v>1.77</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.65</v>
-      </c>
-      <c r="AK30">
-        <v>1.18</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.69</v>
+        <v>3.94</v>
       </c>
       <c r="O31">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="P31">
-        <v>5.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q31">
-        <v>2.43</v>
+        <v>4.33</v>
       </c>
       <c r="R31">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="S31">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T31">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="U31">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="V31">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y31">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="Z31">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="AA31">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="AB31">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AC31">
-        <v>5.25</v>
+        <v>3.84</v>
       </c>
       <c r="AD31">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>2.34</v>
+        <v>1.92</v>
       </c>
       <c r="AG31">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AK31">
-        <v>2.05</v>
+        <v>1.18</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5555,34 +5555,34 @@
         <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z32">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="AA32">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AB32">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC32">
-        <v>3.98</v>
+        <v>3.84</v>
       </c>
       <c r="AD32">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE32">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG32">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK32">
         <v>1.66</v>
@@ -5860,7 +5860,7 @@
         <v>3.45</v>
       </c>
       <c r="Q34">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R34">
         <v>1.85</v>
@@ -5875,19 +5875,19 @@
         <v>4</v>
       </c>
       <c r="V34">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X34">
         <v>1.14</v>
       </c>
       <c r="Y34">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="Z34">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AA34">
         <v>3.2</v>
@@ -5908,7 +5908,7 @@
         <v>2.15</v>
       </c>
       <c r="AG34">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.35</v>
       </c>
       <c r="AK34">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6068,10 +6068,10 @@
         <v>1.18</v>
       </c>
       <c r="AF35">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG35">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6180,10 +6180,10 @@
         <v>3.75</v>
       </c>
       <c r="O36">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P36">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q36">
         <v>4</v>
@@ -6192,16 +6192,16 @@
         <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="U36">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="V36">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
         <v>1.09</v>
@@ -6210,22 +6210,22 @@
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA36">
         <v>1.67</v>
       </c>
       <c r="AB36">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC36">
         <v>2.43</v>
       </c>
       <c r="AD36">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE36">
         <v>1.13</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
         <v>1.21</v>
@@ -6340,25 +6340,25 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="Q37">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
         <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="U37">
         <v>2.2</v>
@@ -6382,7 +6382,7 @@
         <v>1.46</v>
       </c>
       <c r="AB37">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AC37">
         <v>2.25</v>
@@ -6397,7 +6397,7 @@
         <v>1.47</v>
       </c>
       <c r="AG37">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.19</v>
       </c>
       <c r="AK37">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q38">
-        <v>2.38</v>
+        <v>4.4</v>
       </c>
       <c r="R38">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="S38">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="U38">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="V38">
+        <v>1.48</v>
+      </c>
+      <c r="W38">
+        <v>1.08</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
+        <v>1.18</v>
+      </c>
+      <c r="Z38">
+        <v>3.4</v>
+      </c>
+      <c r="AA38">
+        <v>1.76</v>
+      </c>
+      <c r="AB38">
+        <v>1.87</v>
+      </c>
+      <c r="AC38">
+        <v>2.85</v>
+      </c>
+      <c r="AD38">
         <v>1.33</v>
       </c>
-      <c r="W38">
-        <v>1.06</v>
-      </c>
-      <c r="X38">
-        <v>1</v>
-      </c>
-      <c r="Y38">
-        <v>1.28</v>
-      </c>
-      <c r="Z38">
-        <v>3.08</v>
-      </c>
-      <c r="AA38">
-        <v>1.99</v>
-      </c>
-      <c r="AB38">
-        <v>1.73</v>
-      </c>
-      <c r="AC38">
-        <v>3.6</v>
-      </c>
-      <c r="AD38">
-        <v>1.28</v>
-      </c>
       <c r="AE38">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AG38">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AK38">
-        <v>1.87</v>
+        <v>1.16</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>2.38</v>
+      </c>
+      <c r="R39">
+        <v>2.05</v>
+      </c>
+      <c r="S39">
+        <v>1.4</v>
+      </c>
+      <c r="T39">
+        <v>2.75</v>
+      </c>
+      <c r="U39">
+        <v>3</v>
+      </c>
+      <c r="V39">
+        <v>1.33</v>
+      </c>
+      <c r="W39">
+        <v>1.06</v>
+      </c>
+      <c r="X39">
+        <v>1</v>
+      </c>
+      <c r="Y39">
+        <v>1.28</v>
+      </c>
+      <c r="Z39">
+        <v>3.08</v>
+      </c>
+      <c r="AA39">
+        <v>1.99</v>
+      </c>
+      <c r="AB39">
         <v>1.73</v>
       </c>
-      <c r="Q39">
-        <v>4.4</v>
-      </c>
-      <c r="R39">
-        <v>2.23</v>
-      </c>
-      <c r="S39">
-        <v>1.29</v>
-      </c>
-      <c r="T39">
-        <v>3.18</v>
-      </c>
-      <c r="U39">
-        <v>2.43</v>
-      </c>
-      <c r="V39">
-        <v>1.48</v>
-      </c>
-      <c r="W39">
-        <v>1.08</v>
-      </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.18</v>
-      </c>
-      <c r="Z39">
-        <v>3.4</v>
-      </c>
-      <c r="AA39">
-        <v>1.76</v>
-      </c>
-      <c r="AB39">
+      <c r="AC39">
+        <v>3.6</v>
+      </c>
+      <c r="AD39">
+        <v>1.28</v>
+      </c>
+      <c r="AE39">
+        <v>1.04</v>
+      </c>
+      <c r="AF39">
+        <v>1.85</v>
+      </c>
+      <c r="AG39">
+        <v>1.84</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.23</v>
+      </c>
+      <c r="AK39">
         <v>1.87</v>
-      </c>
-      <c r="AC39">
-        <v>2.85</v>
-      </c>
-      <c r="AD39">
-        <v>1.33</v>
-      </c>
-      <c r="AE39">
-        <v>1.18</v>
-      </c>
-      <c r="AF39">
-        <v>1.58</v>
-      </c>
-      <c r="AG39">
-        <v>2.2</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>2</v>
-      </c>
-      <c r="AK39">
-        <v>1.16</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O40">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P40">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Q40">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="R40">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U40">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="V40">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
         <v>1.07</v>
@@ -6862,16 +6862,16 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z40">
-        <v>4.1</v>
+        <v>3.89</v>
       </c>
       <c r="AA40">
         <v>1.73</v>
       </c>
       <c r="AB40">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC40">
         <v>2.7</v>
@@ -6883,10 +6883,10 @@
         <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG40">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AK40">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="O43">
         <v>3.2</v>
       </c>
       <c r="P43">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="Q43">
         <v>3.4</v>
@@ -7336,7 +7336,7 @@
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="U43">
         <v>2.45</v>
@@ -7348,7 +7348,7 @@
         <v>1.07</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y43">
         <v>1.28</v>
@@ -7363,7 +7363,7 @@
         <v>1.95</v>
       </c>
       <c r="AC43">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AD43">
         <v>1.33</v>
@@ -7375,7 +7375,7 @@
         <v>1.55</v>
       </c>
       <c r="AG43">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK43">
         <v>1.4</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="O44">
         <v>4.2</v>
       </c>
       <c r="P44">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="Q44">
         <v>6</v>
@@ -7496,49 +7496,49 @@
         <v>2.38</v>
       </c>
       <c r="S44">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="U44">
         <v>2.5</v>
       </c>
       <c r="V44">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W44">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z44">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA44">
         <v>1.66</v>
       </c>
       <c r="AB44">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC44">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD44">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE44">
         <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG44">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="AK44">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7807,16 +7807,16 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P46">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q46">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R46">
         <v>2.45</v>
@@ -7825,16 +7825,16 @@
         <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="U46">
         <v>2.27</v>
       </c>
       <c r="V46">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W46">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X46">
         <v>1.03</v>
@@ -7846,10 +7846,10 @@
         <v>4.55</v>
       </c>
       <c r="AA46">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="AC46">
         <v>2.35</v>
@@ -7864,7 +7864,7 @@
         <v>1.5</v>
       </c>
       <c r="AG46">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O56">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q56">
         <v>2.43</v>
@@ -10098,55 +10098,55 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA60">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB60">
         <v>2</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O62">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P62">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
@@ -10448,16 +10448,16 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z62">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="AA62">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB62">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC62">
         <v>3.4</v>
@@ -10466,7 +10466,7 @@
         <v>1.26</v>
       </c>
       <c r="AE62">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF62">
         <v>1.71</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11260,7 +11260,7 @@
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y67">
         <v>1.22</v>
@@ -11281,7 +11281,7 @@
         <v>1.31</v>
       </c>
       <c r="AE67">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF67">
         <v>1.7</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="O68">
         <v>3.5</v>
       </c>
       <c r="P68">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q68">
         <v>3.25</v>
@@ -11432,13 +11432,13 @@
         <v>3.72</v>
       </c>
       <c r="AA68">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB68">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC68">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD68">
         <v>1.38</v>
@@ -11466,7 +11466,7 @@
         <v>1.35</v>
       </c>
       <c r="AK68">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="O70">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q70">
         <v>2.2</v>
@@ -11734,13 +11734,13 @@
         <v>2.15</v>
       </c>
       <c r="S70">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T70">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U70">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V70">
         <v>1.41</v>
@@ -11752,16 +11752,16 @@
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
         <v>3.42</v>
       </c>
       <c r="AA70">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB70">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AC70">
         <v>3.3</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK70">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11891,10 +11891,10 @@
         <v>3.3</v>
       </c>
       <c r="Q71">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
       <c r="R71">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="S71">
         <v>1.43</v>
@@ -11903,10 +11903,10 @@
         <v>2.62</v>
       </c>
       <c r="U71">
-        <v>2.84</v>
+        <v>3.04</v>
       </c>
       <c r="V71">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W71">
         <v>1.03</v>
@@ -11936,10 +11936,10 @@
         <v>1.08</v>
       </c>
       <c r="AF71">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG71">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>2.3</v>
       </c>
       <c r="R73">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="S73">
         <v>1.43</v>
@@ -12229,7 +12229,7 @@
         <v>2.75</v>
       </c>
       <c r="U73">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="V73">
         <v>1.32</v>
@@ -12247,7 +12247,7 @@
         <v>2.86</v>
       </c>
       <c r="AA73">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AB73">
         <v>1.67</v>
@@ -12377,7 +12377,7 @@
         <v>3.4</v>
       </c>
       <c r="P74">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="Q74">
         <v>2.47</v>
@@ -12558,7 +12558,7 @@
         <v>2.96</v>
       </c>
       <c r="V75">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W75">
         <v>1.05</v>
@@ -12573,10 +12573,10 @@
         <v>3.08</v>
       </c>
       <c r="AA75">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB75">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC75">
         <v>3.5</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="O7">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="P7">
         <v>2.23</v>
@@ -1465,46 +1465,46 @@
         <v>1.94</v>
       </c>
       <c r="S7">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="U7">
         <v>3.3</v>
       </c>
       <c r="V7">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="Z7">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AA7">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AB7">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AC7">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="AD7">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AG7">
         <v>1.75</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>2.3</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,31 +3732,31 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="O21">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="P21">
-        <v>6.3</v>
+        <v>6.78</v>
       </c>
       <c r="Q21">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R21">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S21">
         <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="U21">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V21">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
         <v>1.12</v>
@@ -3765,31 +3765,31 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
+        <v>1.17</v>
+      </c>
+      <c r="Z21">
+        <v>4.6</v>
+      </c>
+      <c r="AA21">
+        <v>1.6</v>
+      </c>
+      <c r="AB21">
+        <v>2.13</v>
+      </c>
+      <c r="AC21">
+        <v>2.41</v>
+      </c>
+      <c r="AD21">
+        <v>1.48</v>
+      </c>
+      <c r="AE21">
         <v>1.15</v>
       </c>
-      <c r="Z21">
-        <v>4.25</v>
-      </c>
-      <c r="AA21">
-        <v>1.59</v>
-      </c>
-      <c r="AB21">
-        <v>2.23</v>
-      </c>
-      <c r="AC21">
-        <v>2.43</v>
-      </c>
-      <c r="AD21">
-        <v>1.47</v>
-      </c>
-      <c r="AE21">
-        <v>1.14</v>
-      </c>
       <c r="AF21">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG21">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.48</v>
+        <v>2.73</v>
       </c>
       <c r="O23">
         <v>3.05</v>
       </c>
       <c r="P23">
-        <v>2.52</v>
+        <v>2.79</v>
       </c>
       <c r="Q23">
         <v>3.48</v>
@@ -4073,7 +4073,7 @@
         <v>1.92</v>
       </c>
       <c r="S23">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="T23">
         <v>2.42</v>
@@ -4094,19 +4094,19 @@
         <v>1.42</v>
       </c>
       <c r="Z23">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AA23">
         <v>2.43</v>
       </c>
       <c r="AB23">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC23">
         <v>4.25</v>
       </c>
       <c r="AD23">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE23">
         <v>1.01</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O25">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="P25">
-        <v>4.1</v>
+        <v>3.48</v>
       </c>
       <c r="Q25">
         <v>2.6</v>
       </c>
       <c r="R25">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S25">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="T25">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U25">
         <v>3.3</v>
@@ -4411,22 +4411,22 @@
         <v>1.25</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1.06</v>
       </c>
       <c r="Y25">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z25">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AA25">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AB25">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AC25">
         <v>4.5</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O32">
         <v>3.1</v>
@@ -5534,10 +5534,10 @@
         <v>3.2</v>
       </c>
       <c r="Q32">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="R32">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S32">
         <v>1.46</v>
@@ -5546,10 +5546,10 @@
         <v>2.47</v>
       </c>
       <c r="U32">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="V32">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W32">
         <v>1.04</v>
@@ -5558,22 +5558,22 @@
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z32">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AA32">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AB32">
         <v>1.66</v>
       </c>
       <c r="AC32">
-        <v>3.84</v>
+        <v>4.02</v>
       </c>
       <c r="AD32">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE32">
         <v>1.02</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
         <v>1.66</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="O41">
         <v>3.6</v>
       </c>
       <c r="P41">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q41">
         <v>2.33</v>
@@ -7010,7 +7010,7 @@
         <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="U41">
         <v>2.15</v>
@@ -7025,7 +7025,7 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="Z41">
         <v>4.8</v>
@@ -7037,19 +7037,19 @@
         <v>2.23</v>
       </c>
       <c r="AC41">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD41">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE41">
         <v>1.16</v>
       </c>
       <c r="AF41">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>3.8</v>
       </c>
       <c r="P42">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q42">
         <v>3.23</v>
@@ -7173,10 +7173,10 @@
         <v>1.26</v>
       </c>
       <c r="T42">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="V42">
         <v>1.51</v>
@@ -7188,28 +7188,28 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
         <v>4.3</v>
       </c>
       <c r="AA42">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB42">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="AC42">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AD42">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE42">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF42">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG42">
         <v>2.3</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="AK42">
         <v>1.3</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="P47">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q47">
         <v>2.06</v>
@@ -7997,7 +7997,7 @@
         <v>1.45</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
         <v>1.04</v>
@@ -8009,10 +8009,10 @@
         <v>3.95</v>
       </c>
       <c r="AA47">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB47">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="AC47">
         <v>2.88</v>
@@ -8021,7 +8021,7 @@
         <v>1.42</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
         <v>1.73</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK47">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,43 +8133,43 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O48">
         <v>3.1</v>
       </c>
       <c r="P48">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q48">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="R48">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S48">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T48">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="U48">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V48">
         <v>1.28</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X48">
         <v>1.05</v>
       </c>
       <c r="Y48">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z48">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AA48">
         <v>2.38</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AK48">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="O49">
         <v>3.35</v>
       </c>
       <c r="P49">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="Q49">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="R49">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S49">
         <v>1.36</v>
@@ -8335,10 +8335,10 @@
         <v>3.2</v>
       </c>
       <c r="AA49">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AB49">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC49">
         <v>3.34</v>
@@ -8785,16 +8785,16 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O52">
         <v>3.5</v>
       </c>
       <c r="P52">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="Q52">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="R52">
         <v>2.5</v>
@@ -8806,7 +8806,7 @@
         <v>3.6</v>
       </c>
       <c r="U52">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V52">
         <v>1.62</v>
@@ -8815,7 +8815,7 @@
         <v>1.13</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
         <v>1.11</v>
@@ -8833,7 +8833,7 @@
         <v>2.3</v>
       </c>
       <c r="AD52">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE52">
         <v>1.21</v>
@@ -8858,7 +8858,7 @@
         <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,7 +8951,7 @@
         <v>1.98</v>
       </c>
       <c r="O53">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P53">
         <v>3.28</v>
@@ -8963,7 +8963,7 @@
         <v>2.8</v>
       </c>
       <c r="S53">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T53">
         <v>4.3</v>
@@ -8984,22 +8984,22 @@
         <v>1.03</v>
       </c>
       <c r="Z53">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA53">
         <v>1.25</v>
       </c>
       <c r="AB53">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AC53">
         <v>1.8</v>
       </c>
       <c r="AD53">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AE53">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF53">
         <v>1.3</v>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="O59">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="P59">
         <v>2.6</v>
@@ -9944,7 +9944,7 @@
         <v>1.44</v>
       </c>
       <c r="T59">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="U59">
         <v>3.3</v>
@@ -9962,13 +9962,13 @@
         <v>1.42</v>
       </c>
       <c r="Z59">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="AA59">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AB59">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC59">
         <v>4.6</v>
@@ -9977,7 +9977,7 @@
         <v>1.18</v>
       </c>
       <c r="AE59">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF59">
         <v>1.87</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O62">
         <v>3.4</v>
@@ -10436,7 +10436,7 @@
         <v>2.88</v>
       </c>
       <c r="U62">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="V62">
         <v>1.39</v>
@@ -10445,7 +10445,7 @@
         <v>1.06</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
         <v>1.27</v>
@@ -10457,7 +10457,7 @@
         <v>2</v>
       </c>
       <c r="AB62">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC62">
         <v>3.4</v>
@@ -10469,7 +10469,7 @@
         <v>1.06</v>
       </c>
       <c r="AF62">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG62">
         <v>1.97</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,28 +10578,28 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
         <v>3</v>
       </c>
-      <c r="P63">
-        <v>3.3</v>
-      </c>
-      <c r="Q63">
-        <v>2.83</v>
-      </c>
       <c r="R63">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="S63">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T63">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="U63">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V63">
         <v>1.25</v>
@@ -10608,50 +10608,50 @@
         <v>1.04</v>
       </c>
       <c r="X63">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y63">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Z63">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AA63">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="AB63">
+        <v>1.41</v>
+      </c>
+      <c r="AC63">
+        <v>5</v>
+      </c>
+      <c r="AD63">
+        <v>1.1</v>
+      </c>
+      <c r="AE63">
+        <v>1.01</v>
+      </c>
+      <c r="AF63">
+        <v>2.15</v>
+      </c>
+      <c r="AG63">
+        <v>1.62</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
+        <v>1.33</v>
+      </c>
+      <c r="AK63">
         <v>1.53</v>
-      </c>
-      <c r="AC63">
-        <v>4.6</v>
-      </c>
-      <c r="AD63">
-        <v>1.14</v>
-      </c>
-      <c r="AE63">
-        <v>1</v>
-      </c>
-      <c r="AF63">
-        <v>2.05</v>
-      </c>
-      <c r="AG63">
-        <v>1.65</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.29</v>
-      </c>
-      <c r="AK63">
-        <v>1.58</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O64">
         <v>2.9</v>
@@ -10759,13 +10759,13 @@
         <v>1.4</v>
       </c>
       <c r="T64">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="U64">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="V64">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W64">
         <v>1.06</v>
@@ -10780,13 +10780,13 @@
         <v>2.69</v>
       </c>
       <c r="AA64">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AB64">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AC64">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD64">
         <v>1.16</v>
@@ -10795,7 +10795,7 @@
         <v>1.01</v>
       </c>
       <c r="AF64">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG64">
         <v>1.78</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK64">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q65">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R65">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="S65">
+        <v>1.55</v>
+      </c>
+      <c r="T65">
+        <v>2.37</v>
+      </c>
+      <c r="U65">
+        <v>3.25</v>
+      </c>
+      <c r="V65">
+        <v>1.23</v>
+      </c>
+      <c r="W65">
+        <v>1.01</v>
+      </c>
+      <c r="X65">
+        <v>1.06</v>
+      </c>
+      <c r="Y65">
+        <v>1.49</v>
+      </c>
+      <c r="Z65">
+        <v>2.38</v>
+      </c>
+      <c r="AA65">
+        <v>2.37</v>
+      </c>
+      <c r="AB65">
+        <v>1.47</v>
+      </c>
+      <c r="AC65">
+        <v>4.65</v>
+      </c>
+      <c r="AD65">
+        <v>1.13</v>
+      </c>
+      <c r="AE65">
+        <v>1</v>
+      </c>
+      <c r="AF65">
+        <v>2.05</v>
+      </c>
+      <c r="AG65">
+        <v>1.67</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>1.29</v>
+      </c>
+      <c r="AK65">
         <v>1.58</v>
-      </c>
-      <c r="T65">
-        <v>2.2</v>
-      </c>
-      <c r="U65">
-        <v>3.5</v>
-      </c>
-      <c r="V65">
-        <v>1.25</v>
-      </c>
-      <c r="W65">
-        <v>1.04</v>
-      </c>
-      <c r="X65">
-        <v>1.07</v>
-      </c>
-      <c r="Y65">
-        <v>1.53</v>
-      </c>
-      <c r="Z65">
-        <v>2.36</v>
-      </c>
-      <c r="AA65">
-        <v>2.52</v>
-      </c>
-      <c r="AB65">
-        <v>1.41</v>
-      </c>
-      <c r="AC65">
-        <v>5</v>
-      </c>
-      <c r="AD65">
-        <v>1.1</v>
-      </c>
-      <c r="AE65">
-        <v>1.01</v>
-      </c>
-      <c r="AF65">
-        <v>2.1</v>
-      </c>
-      <c r="AG65">
-        <v>1.65</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.33</v>
-      </c>
-      <c r="AK65">
-        <v>1.53</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11079,22 +11079,22 @@
         <v>2.6</v>
       </c>
       <c r="R66">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S66">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T66">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U66">
         <v>3.2</v>
       </c>
       <c r="V66">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W66">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
         <v>1.04</v>
@@ -11109,13 +11109,13 @@
         <v>2.17</v>
       </c>
       <c r="AB66">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC66">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AD66">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE66">
         <v>1.03</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK66">
         <v>1.73</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O67">
         <v>3.4</v>
@@ -11239,10 +11239,10 @@
         <v>2.95</v>
       </c>
       <c r="Q67">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="R67">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="S67">
         <v>1.33</v>
@@ -11251,7 +11251,7 @@
         <v>3</v>
       </c>
       <c r="U67">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="V67">
         <v>1.4</v>
@@ -11260,34 +11260,34 @@
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="AA67">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB67">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC67">
         <v>3.25</v>
       </c>
       <c r="AD67">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE67">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF67">
         <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="O73">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P73">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q73">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="R73">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="S73">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T73">
         <v>2.75</v>
       </c>
       <c r="U73">
-        <v>3.23</v>
+        <v>2.96</v>
       </c>
       <c r="V73">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W73">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y73">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z73">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="AA73">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AB73">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC73">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD73">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE73">
         <v>1.03</v>
       </c>
       <c r="AF73">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AG73">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK73">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O74">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="Q74">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="R74">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="S74">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T74">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U74">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="V74">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W74">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
+        <v>1.02</v>
+      </c>
+      <c r="Y74">
+        <v>1.33</v>
+      </c>
+      <c r="Z74">
+        <v>2.86</v>
+      </c>
+      <c r="AA74">
+        <v>2.11</v>
+      </c>
+      <c r="AB74">
+        <v>1.67</v>
+      </c>
+      <c r="AC74">
+        <v>3.6</v>
+      </c>
+      <c r="AD74">
+        <v>1.2</v>
+      </c>
+      <c r="AE74">
         <v>1.03</v>
       </c>
-      <c r="Y74">
-        <v>1.34</v>
-      </c>
-      <c r="Z74">
-        <v>3.11</v>
-      </c>
-      <c r="AA74">
-        <v>2.05</v>
-      </c>
-      <c r="AB74">
-        <v>1.75</v>
-      </c>
-      <c r="AC74">
-        <v>3.52</v>
-      </c>
-      <c r="AD74">
-        <v>1.24</v>
-      </c>
-      <c r="AE74">
-        <v>1.05</v>
-      </c>
       <c r="AF74">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG74">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK74">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="O75">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q75">
-        <v>2.03</v>
+        <v>2.47</v>
       </c>
       <c r="R75">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S75">
         <v>1.36</v>
       </c>
       <c r="T75">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U75">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="V75">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W75">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z75">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AA75">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB75">
         <v>1.75</v>
       </c>
       <c r="AC75">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="AD75">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE75">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF75">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AG75">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>2.46</v>
+        <v>1.8</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O5">
         <v>3.3</v>
       </c>
       <c r="P5">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q5">
         <v>2.85</v>
       </c>
       <c r="R5">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="U5">
         <v>2.63</v>
@@ -1154,25 +1154,25 @@
         <v>1.1</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5">
         <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA5">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB5">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AD5">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
         <v>1.1</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK5">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,34 +1287,34 @@
         </is>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
         <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q6">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="V6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1.02</v>
@@ -1323,28 +1323,28 @@
         <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA6">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB6">
         <v>2</v>
       </c>
       <c r="AC6">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD6">
         <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
         <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.12</v>
+        <v>2.71</v>
       </c>
       <c r="O7">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="P7">
         <v>2.23</v>
       </c>
       <c r="Q7">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="R7">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="S7">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T7">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="U7">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V7">
         <v>1.34</v>
       </c>
       <c r="W7">
+        <v>1.02</v>
+      </c>
+      <c r="X7">
+        <v>1.06</v>
+      </c>
+      <c r="Y7">
+        <v>1.44</v>
+      </c>
+      <c r="Z7">
+        <v>2.7</v>
+      </c>
+      <c r="AA7">
+        <v>2.47</v>
+      </c>
+      <c r="AB7">
+        <v>1.49</v>
+      </c>
+      <c r="AC7">
+        <v>4.5</v>
+      </c>
+      <c r="AD7">
+        <v>1.2</v>
+      </c>
+      <c r="AE7">
         <v>1.05</v>
-      </c>
-      <c r="X7">
-        <v>1.05</v>
-      </c>
-      <c r="Y7">
-        <v>1.42</v>
-      </c>
-      <c r="Z7">
-        <v>2.49</v>
-      </c>
-      <c r="AA7">
-        <v>2.45</v>
-      </c>
-      <c r="AB7">
-        <v>1.52</v>
-      </c>
-      <c r="AC7">
-        <v>4.6</v>
-      </c>
-      <c r="AD7">
-        <v>1.13</v>
-      </c>
-      <c r="AE7">
-        <v>1.01</v>
       </c>
       <c r="AF7">
         <v>2.01</v>
       </c>
       <c r="AG7">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>4.13</v>
+        <v>4.18</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="O9">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="P9">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,22 +1942,22 @@
         <v>2.25</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q10">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
         <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="U10">
         <v>2.5</v>
@@ -1966,37 +1966,37 @@
         <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>3.79</v>
+        <v>3.94</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB10">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AC10">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AD10">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE10">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF10">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG10">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O11">
-        <v>4.58</v>
+        <v>4.15</v>
       </c>
       <c r="P11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="O12">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="P12">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O13">
         <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="Q13">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R13">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="S13">
         <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="U13">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA13">
         <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC13">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD13">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q17">
         <v>2.4</v>
       </c>
       <c r="R17">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T17">
         <v>3.1</v>
       </c>
       <c r="U17">
-        <v>2.63</v>
+        <v>2.34</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB17">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC17">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AD17">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE17">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF17">
         <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="O18">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="P18">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="Q18">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="R18">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="S18">
         <v>1.17</v>
@@ -3264,43 +3264,43 @@
         <v>4.5</v>
       </c>
       <c r="U18">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="V18">
         <v>1.67</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z18">
-        <v>5.85</v>
+        <v>5.3</v>
       </c>
       <c r="AA18">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB18">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AC18">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AD18">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AE18">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF18">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AG18">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK18">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O19">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="P19">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="Q19">
         <v>1.53</v>
@@ -3421,37 +3421,37 @@
         <v>3</v>
       </c>
       <c r="S19">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T19">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="U19">
         <v>2</v>
       </c>
       <c r="V19">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W19">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>6.15</v>
+        <v>5.95</v>
       </c>
       <c r="AA19">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AB19">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AC19">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AD19">
         <v>1.8</v>
@@ -3463,7 +3463,7 @@
         <v>1.58</v>
       </c>
       <c r="AG19">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P20">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="Q20">
-        <v>3.69</v>
+        <v>3.35</v>
       </c>
       <c r="R20">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S20">
         <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="U20">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="V20">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W20">
         <v>1.03</v>
@@ -3602,28 +3602,28 @@
         <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z20">
         <v>2.8</v>
       </c>
       <c r="AA20">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB20">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC20">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AD20">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE20">
         <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AG20">
         <v>1.8</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="O21">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="P21">
-        <v>6.78</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R21">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T21">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="U21">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V21">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W21">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
         <v>4.6</v>
       </c>
       <c r="AA21">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB21">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="AC21">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="AD21">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE21">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG21">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK21">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="O23">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="P23">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="Q23">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="R23">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="S23">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T23">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="U23">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W23">
         <v>1.02</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y23">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z23">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AA23">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AB23">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC23">
         <v>4.25</v>
       </c>
       <c r="AD23">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE23">
         <v>1.01</v>
       </c>
       <c r="AF23">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AK23">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="O24">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="P24">
-        <v>4.28</v>
+        <v>4.1</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W24">
         <v>0</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="O25">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P25">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="Q25">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R25">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="S25">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="T25">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="U25">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V25">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
         <v>1.06</v>
       </c>
       <c r="Y25">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z25">
-        <v>2.52</v>
+        <v>2.98</v>
       </c>
       <c r="AA25">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AB25">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC25">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD25">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE25">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AG25">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AK25">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,61 +4550,61 @@
         <v>1.95</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
         <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="V26">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W26">
         <v>1.09</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z26">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA26">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB26">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AC26">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD26">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF26">
         <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="O27">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q27">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="R27">
         <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U27">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="V27">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="AA27">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB27">
+        <v>2.12</v>
+      </c>
+      <c r="AC27">
+        <v>2.75</v>
+      </c>
+      <c r="AD27">
+        <v>1.4</v>
+      </c>
+      <c r="AE27">
+        <v>1.17</v>
+      </c>
+      <c r="AF27">
+        <v>1.58</v>
+      </c>
+      <c r="AG27">
         <v>2</v>
-      </c>
-      <c r="AC27">
-        <v>2.66</v>
-      </c>
-      <c r="AD27">
-        <v>1.37</v>
-      </c>
-      <c r="AE27">
-        <v>1.11</v>
-      </c>
-      <c r="AF27">
-        <v>1.67</v>
-      </c>
-      <c r="AG27">
-        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4879,28 +4879,28 @@
         <v>3.6</v>
       </c>
       <c r="P28">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="Q28">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="R28">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S28">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U28">
         <v>2.6</v>
       </c>
       <c r="V28">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
         <v>1</v>
@@ -4909,13 +4909,13 @@
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.74</v>
+        <v>3.99</v>
       </c>
       <c r="AA28">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AC28">
         <v>2.85</v>
@@ -4924,13 +4924,13 @@
         <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK28">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O29">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
         <v>3.9</v>
@@ -5054,31 +5054,31 @@
         <v>1.38</v>
       </c>
       <c r="T29">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z29">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA29">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB29">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AC29">
         <v>3.4</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="O30">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
         <v>5.2</v>
       </c>
       <c r="Q30">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="R30">
         <v>1.85</v>
@@ -5217,31 +5217,31 @@
         <v>1.5</v>
       </c>
       <c r="T30">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="U30">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="V30">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y30">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z30">
         <v>2.41</v>
       </c>
       <c r="AA30">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AB30">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AC30">
         <v>5.25</v>
@@ -5253,10 +5253,10 @@
         <v>1.02</v>
       </c>
       <c r="AF30">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AG30">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="AK30">
         <v>2.05</v>
@@ -5365,28 +5365,28 @@
         <v>3.94</v>
       </c>
       <c r="O31">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="P31">
         <v>2.05</v>
       </c>
       <c r="Q31">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R31">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="S31">
         <v>1.51</v>
       </c>
       <c r="T31">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="U31">
-        <v>3.27</v>
+        <v>3.14</v>
       </c>
       <c r="V31">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W31">
         <v>1.01</v>
@@ -5395,10 +5395,10 @@
         <v>1.09</v>
       </c>
       <c r="Y31">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z31">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA31">
         <v>2.17</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AK31">
         <v>1.18</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O32">
         <v>3.1</v>
       </c>
       <c r="P32">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q32">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R32">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="S32">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T32">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="U32">
-        <v>3.24</v>
+        <v>3.07</v>
       </c>
       <c r="V32">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
+        <v>1.05</v>
+      </c>
+      <c r="X32">
         <v>1.04</v>
       </c>
-      <c r="X32">
-        <v>1.02</v>
-      </c>
       <c r="Y32">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA32">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="AB32">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC32">
-        <v>4.02</v>
+        <v>3.6</v>
       </c>
       <c r="AD32">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE32">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="O34">
         <v>2.85</v>
       </c>
       <c r="P34">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q34">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="R34">
         <v>1.85</v>
@@ -5872,22 +5872,22 @@
         <v>2.2</v>
       </c>
       <c r="U34">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="V34">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W34">
         <v>1.01</v>
       </c>
       <c r="X34">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y34">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Z34">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AA34">
         <v>3.2</v>
@@ -5899,16 +5899,16 @@
         <v>5.75</v>
       </c>
       <c r="AD34">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF34">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG34">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AK34">
         <v>1.55</v>
@@ -6017,62 +6017,62 @@
         <v>2.25</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="Q35">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="R35">
+        <v>2.2</v>
+      </c>
+      <c r="S35">
+        <v>1.33</v>
+      </c>
+      <c r="T35">
+        <v>3.31</v>
+      </c>
+      <c r="U35">
+        <v>2.5</v>
+      </c>
+      <c r="V35">
+        <v>1.45</v>
+      </c>
+      <c r="W35">
+        <v>1.11</v>
+      </c>
+      <c r="X35">
+        <v>1.05</v>
+      </c>
+      <c r="Y35">
+        <v>1.21</v>
+      </c>
+      <c r="Z35">
+        <v>3.9</v>
+      </c>
+      <c r="AA35">
+        <v>1.75</v>
+      </c>
+      <c r="AB35">
+        <v>2.05</v>
+      </c>
+      <c r="AC35">
+        <v>2.72</v>
+      </c>
+      <c r="AD35">
+        <v>1.36</v>
+      </c>
+      <c r="AE35">
+        <v>1.15</v>
+      </c>
+      <c r="AF35">
+        <v>1.6</v>
+      </c>
+      <c r="AG35">
         <v>2.3</v>
       </c>
-      <c r="S35">
-        <v>1.31</v>
-      </c>
-      <c r="T35">
-        <v>3.4</v>
-      </c>
-      <c r="U35">
-        <v>2.41</v>
-      </c>
-      <c r="V35">
-        <v>1.5</v>
-      </c>
-      <c r="W35">
-        <v>1.09</v>
-      </c>
-      <c r="X35">
-        <v>1.04</v>
-      </c>
-      <c r="Y35">
-        <v>1.17</v>
-      </c>
-      <c r="Z35">
-        <v>4.33</v>
-      </c>
-      <c r="AA35">
-        <v>1.68</v>
-      </c>
-      <c r="AB35">
-        <v>2.14</v>
-      </c>
-      <c r="AC35">
-        <v>2.54</v>
-      </c>
-      <c r="AD35">
-        <v>1.47</v>
-      </c>
-      <c r="AE35">
-        <v>1.18</v>
-      </c>
-      <c r="AF35">
-        <v>1.54</v>
-      </c>
-      <c r="AG35">
-        <v>2.28</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="O36">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="P36">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Q36">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="R36">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S36">
         <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W36">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z36">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA36">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AC36">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AD36">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE36">
         <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AG36">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O37">
         <v>3.7</v>
       </c>
       <c r="P37">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R37">
         <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T37">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="U37">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V37">
         <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA37">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB37">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="AC37">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD37">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE37">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AF37">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG37">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,40 +6503,40 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="O38">
         <v>3.7</v>
       </c>
       <c r="P38">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q38">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="R38">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T38">
         <v>3.18</v>
       </c>
       <c r="U38">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="V38">
         <v>1.48</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z38">
         <v>3.4</v>
@@ -6557,10 +6557,10 @@
         <v>1.18</v>
       </c>
       <c r="AF38">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>2</v>
+        <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,10 +6675,10 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R39">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
         <v>1.4</v>
@@ -6705,10 +6705,10 @@
         <v>3.08</v>
       </c>
       <c r="AA39">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AB39">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC39">
         <v>3.6</v>
@@ -6720,10 +6720,10 @@
         <v>1.04</v>
       </c>
       <c r="AF39">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG39">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="O40">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="P40">
         <v>6.5</v>
@@ -6841,7 +6841,7 @@
         <v>1.75</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S40">
         <v>1.32</v>
@@ -6850,10 +6850,10 @@
         <v>3.05</v>
       </c>
       <c r="U40">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W40">
         <v>1.07</v>
@@ -6862,31 +6862,31 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="AA40">
         <v>1.73</v>
       </c>
       <c r="AB40">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC40">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD40">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE40">
         <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG40">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK40">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,28 +6992,28 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P41">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q41">
         <v>2.33</v>
       </c>
       <c r="R41">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="S41">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T41">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="U41">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="V41">
         <v>1.62</v>
@@ -7025,31 +7025,31 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="Z41">
-        <v>4.8</v>
+        <v>6.12</v>
       </c>
       <c r="AA41">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AB41">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="AC41">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AD41">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AE41">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF41">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O42">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="P42">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q42">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="R42">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S42">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U42">
-        <v>2.29</v>
+        <v>2.53</v>
       </c>
       <c r="V42">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="W42">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AA42">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AB42">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC42">
-        <v>2.49</v>
+        <v>2.85</v>
       </c>
       <c r="AD42">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="O43">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="Q43">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R43">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S43">
         <v>1.3</v>
@@ -7357,10 +7357,10 @@
         <v>3.8</v>
       </c>
       <c r="AA43">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB43">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC43">
         <v>3.1</v>
@@ -7369,13 +7369,13 @@
         <v>1.33</v>
       </c>
       <c r="AE43">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF43">
         <v>1.55</v>
       </c>
       <c r="AG43">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AK43">
         <v>1.4</v>
@@ -7481,22 +7481,22 @@
         </is>
       </c>
       <c r="N44">
+        <v>5</v>
+      </c>
+      <c r="O44">
+        <v>4</v>
+      </c>
+      <c r="P44">
+        <v>1.5</v>
+      </c>
+      <c r="Q44">
         <v>5.5</v>
       </c>
-      <c r="O44">
-        <v>4.2</v>
-      </c>
-      <c r="P44">
-        <v>1.49</v>
-      </c>
-      <c r="Q44">
-        <v>6</v>
-      </c>
       <c r="R44">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T44">
         <v>3.2</v>
@@ -7505,40 +7505,40 @@
         <v>2.5</v>
       </c>
       <c r="V44">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W44">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA44">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB44">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC44">
         <v>2.62</v>
       </c>
       <c r="AD44">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE44">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF44">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG44">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="AK44">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O46">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q46">
         <v>3</v>
       </c>
       <c r="R46">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S46">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T46">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="U46">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V46">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
         <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="AA46">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB46">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="AC46">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AD46">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AE46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF46">
         <v>1.5</v>
       </c>
       <c r="AG46">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7973,19 +7973,19 @@
         <v>1.53</v>
       </c>
       <c r="O47">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="P47">
         <v>5</v>
       </c>
       <c r="Q47">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="R47">
         <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
         <v>3.3</v>
@@ -8003,7 +8003,7 @@
         <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z47">
         <v>3.95</v>
@@ -8012,22 +8012,22 @@
         <v>1.67</v>
       </c>
       <c r="AB47">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AC47">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD47">
         <v>1.42</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF47">
         <v>1.73</v>
       </c>
       <c r="AG47">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="O49">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P49">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="Q49">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="R49">
         <v>2.05</v>
@@ -8326,7 +8326,7 @@
         <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
         <v>1.26</v>
@@ -8350,10 +8350,10 @@
         <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG49">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="R50">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="S50">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T50">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="U50">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V50">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W50">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z50">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AA50">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AB50">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AC50">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AD50">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AE50">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AF50">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG50">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK50">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8637,22 +8637,22 @@
         <v>2</v>
       </c>
       <c r="S51">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T51">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U51">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="V51">
         <v>1.32</v>
       </c>
       <c r="W51">
+        <v>1.03</v>
+      </c>
+      <c r="X51">
         <v>1.04</v>
-      </c>
-      <c r="X51">
-        <v>1.03</v>
       </c>
       <c r="Y51">
         <v>1.26</v>
@@ -8673,13 +8673,13 @@
         <v>1.29</v>
       </c>
       <c r="AE51">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG51">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="P52">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="Q52">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="R52">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S52">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T52">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="V52">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W52">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
         <v>1.11</v>
       </c>
       <c r="Z52">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA52">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB52">
         <v>2.55</v>
       </c>
       <c r="AC52">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD52">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE52">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AF52">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AG52">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,58 +8948,58 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="O53">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P53">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
       </c>
       <c r="R53">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S53">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T53">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="U53">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V53">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W53">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Z53">
         <v>8</v>
       </c>
       <c r="AA53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB53">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AC53">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD53">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AE53">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AF53">
         <v>1.3</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK53">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="O54">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P54">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q54">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R54">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="S54">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T54">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="U54">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="V54">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W54">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z54">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA54">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB54">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC54">
         <v>2.94</v>
       </c>
       <c r="AD54">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE54">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF54">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG54">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,61 +9274,61 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="O55">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="P55">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="Q55">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="R55">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S55">
         <v>1.38</v>
       </c>
       <c r="T55">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U55">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V55">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W55">
         <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y55">
         <v>1.3</v>
       </c>
       <c r="Z55">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AA55">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AB55">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AC55">
-        <v>3.69</v>
+        <v>3.8</v>
       </c>
       <c r="AD55">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE55">
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AG55">
         <v>1.91</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O56">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P56">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q56">
         <v>2.43</v>
@@ -9452,34 +9452,34 @@
         <v>2.17</v>
       </c>
       <c r="S56">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T56">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U56">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="V56">
         <v>1.43</v>
       </c>
       <c r="W56">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z56">
-        <v>3.78</v>
+        <v>4.08</v>
       </c>
       <c r="AA56">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB56">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AC56">
         <v>2.8</v>
@@ -9488,13 +9488,13 @@
         <v>1.33</v>
       </c>
       <c r="AE56">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF56">
         <v>1.67</v>
       </c>
       <c r="AG56">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.24</v>
       </c>
       <c r="AK56">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,28 +9600,28 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P57">
-        <v>6</v>
+        <v>5.18</v>
       </c>
       <c r="Q57">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="R57">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S57">
         <v>1.42</v>
       </c>
       <c r="T57">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U57">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="V57">
         <v>1.35</v>
@@ -9633,31 +9633,31 @@
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z57">
         <v>2.97</v>
       </c>
       <c r="AA57">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AB57">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC57">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD57">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE57">
         <v>1.03</v>
       </c>
       <c r="AF57">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AG57">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK57">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>3.3</v>
       </c>
       <c r="P58">
-        <v>3.17</v>
+        <v>3.94</v>
       </c>
       <c r="Q58">
         <v>2.45</v>
@@ -9778,7 +9778,7 @@
         <v>2.2</v>
       </c>
       <c r="S58">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T58">
         <v>3</v>
@@ -9787,10 +9787,10 @@
         <v>2.75</v>
       </c>
       <c r="V58">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
         <v>1</v>
@@ -9805,7 +9805,7 @@
         <v>1.92</v>
       </c>
       <c r="AB58">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC58">
         <v>3.4</v>
@@ -9814,7 +9814,7 @@
         <v>1.27</v>
       </c>
       <c r="AE58">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF58">
         <v>1.73</v>
@@ -9926,37 +9926,37 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O59">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="P59">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q59">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R59">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="S59">
         <v>1.44</v>
       </c>
       <c r="T59">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="U59">
         <v>3.3</v>
       </c>
       <c r="V59">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W59">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X59">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y59">
         <v>1.42</v>
@@ -9968,10 +9968,10 @@
         <v>2.41</v>
       </c>
       <c r="AB59">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC59">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AD59">
         <v>1.18</v>
@@ -9980,7 +9980,7 @@
         <v>1.02</v>
       </c>
       <c r="AF59">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AG59">
         <v>1.83</v>
@@ -9999,7 +9999,7 @@
         <v>1.33</v>
       </c>
       <c r="AK59">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,22 +10098,22 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>4.98</v>
+        <v>4.7</v>
       </c>
       <c r="R60">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S60">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T60">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U60">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="V60">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W60">
         <v>1.1</v>
@@ -10122,47 +10122,47 @@
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z60">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA60">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AB60">
+        <v>2.02</v>
+      </c>
+      <c r="AC60">
+        <v>2.7</v>
+      </c>
+      <c r="AD60">
+        <v>1.36</v>
+      </c>
+      <c r="AE60">
+        <v>1.1</v>
+      </c>
+      <c r="AF60">
+        <v>1.65</v>
+      </c>
+      <c r="AG60">
+        <v>2.03</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
         <v>2</v>
       </c>
-      <c r="AC60">
-        <v>2.81</v>
-      </c>
-      <c r="AD60">
-        <v>1.33</v>
-      </c>
-      <c r="AE60">
-        <v>1.09</v>
-      </c>
-      <c r="AF60">
-        <v>1.68</v>
-      </c>
-      <c r="AG60">
-        <v>2.02</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>1.2</v>
-      </c>
       <c r="AK60">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O61">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P61">
         <v>3.02</v>
       </c>
       <c r="Q61">
+        <v>2.72</v>
+      </c>
+      <c r="R61">
+        <v>1.91</v>
+      </c>
+      <c r="S61">
+        <v>1.44</v>
+      </c>
+      <c r="T61">
+        <v>2.63</v>
+      </c>
+      <c r="U61">
+        <v>3.2</v>
+      </c>
+      <c r="V61">
+        <v>1.28</v>
+      </c>
+      <c r="W61">
+        <v>1.02</v>
+      </c>
+      <c r="X61">
+        <v>1.07</v>
+      </c>
+      <c r="Y61">
+        <v>1.4</v>
+      </c>
+      <c r="Z61">
         <v>2.88</v>
       </c>
-      <c r="R61">
-        <v>2</v>
-      </c>
-      <c r="S61">
-        <v>1.48</v>
-      </c>
-      <c r="T61">
-        <v>2.57</v>
-      </c>
-      <c r="U61">
-        <v>3</v>
-      </c>
-      <c r="V61">
-        <v>1.3</v>
-      </c>
-      <c r="W61">
-        <v>1.06</v>
-      </c>
-      <c r="X61">
-        <v>1.05</v>
-      </c>
-      <c r="Y61">
-        <v>1.39</v>
-      </c>
-      <c r="Z61">
-        <v>2.84</v>
-      </c>
       <c r="AA61">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="AB61">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC61">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AD61">
         <v>1.18</v>
       </c>
       <c r="AE61">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF61">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG61">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10421,13 +10421,13 @@
         <v>3.4</v>
       </c>
       <c r="P62">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q62">
         <v>2.8</v>
       </c>
       <c r="R62">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S62">
         <v>1.36</v>
@@ -10436,10 +10436,10 @@
         <v>2.88</v>
       </c>
       <c r="U62">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="V62">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W62">
         <v>1.06</v>
@@ -10451,13 +10451,13 @@
         <v>1.27</v>
       </c>
       <c r="Z62">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="AA62">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB62">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC62">
         <v>3.4</v>
@@ -10466,10 +10466,10 @@
         <v>1.26</v>
       </c>
       <c r="AE62">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF62">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG62">
         <v>1.97</v>
@@ -10578,37 +10578,37 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q63">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R63">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S63">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T63">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="U63">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V63">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W63">
         <v>1.04</v>
       </c>
       <c r="X63">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y63">
         <v>1.51</v>
@@ -10617,19 +10617,19 @@
         <v>2.36</v>
       </c>
       <c r="AA63">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AB63">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC63">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AD63">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF63">
         <v>2.15</v>
@@ -10741,25 +10741,25 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O64">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P64">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q64">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R64">
         <v>2</v>
       </c>
       <c r="S64">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T64">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="U64">
         <v>3.28</v>
@@ -10768,34 +10768,34 @@
         <v>1.26</v>
       </c>
       <c r="W64">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y64">
         <v>1.4</v>
       </c>
       <c r="Z64">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="AA64">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB64">
         <v>1.56</v>
       </c>
       <c r="AC64">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD64">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG64">
         <v>1.78</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
         <v>1.52</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="O65">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P65">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="Q65">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="R65">
+        <v>2.1</v>
+      </c>
+      <c r="S65">
+        <v>1.45</v>
+      </c>
+      <c r="T65">
+        <v>2.62</v>
+      </c>
+      <c r="U65">
+        <v>3.2</v>
+      </c>
+      <c r="V65">
+        <v>1.32</v>
+      </c>
+      <c r="W65">
+        <v>1.04</v>
+      </c>
+      <c r="X65">
+        <v>1.04</v>
+      </c>
+      <c r="Y65">
+        <v>1.36</v>
+      </c>
+      <c r="Z65">
+        <v>2.9</v>
+      </c>
+      <c r="AA65">
+        <v>2.14</v>
+      </c>
+      <c r="AB65">
+        <v>1.66</v>
+      </c>
+      <c r="AC65">
+        <v>3.74</v>
+      </c>
+      <c r="AD65">
+        <v>1.19</v>
+      </c>
+      <c r="AE65">
+        <v>1.03</v>
+      </c>
+      <c r="AF65">
         <v>1.91</v>
       </c>
-      <c r="S65">
-        <v>1.55</v>
-      </c>
-      <c r="T65">
-        <v>2.37</v>
-      </c>
-      <c r="U65">
-        <v>3.25</v>
-      </c>
-      <c r="V65">
-        <v>1.23</v>
-      </c>
-      <c r="W65">
-        <v>1.01</v>
-      </c>
-      <c r="X65">
-        <v>1.06</v>
-      </c>
-      <c r="Y65">
-        <v>1.49</v>
-      </c>
-      <c r="Z65">
-        <v>2.38</v>
-      </c>
-      <c r="AA65">
-        <v>2.37</v>
-      </c>
-      <c r="AB65">
-        <v>1.47</v>
-      </c>
-      <c r="AC65">
-        <v>4.65</v>
-      </c>
-      <c r="AD65">
-        <v>1.13</v>
-      </c>
-      <c r="AE65">
-        <v>1</v>
-      </c>
-      <c r="AF65">
-        <v>2.05</v>
-      </c>
       <c r="AG65">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK65">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="O66">
         <v>3</v>
       </c>
       <c r="P66">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="Q66">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="R66">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="S66">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T66">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="U66">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V66">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="W66">
+        <v>1.01</v>
+      </c>
+      <c r="X66">
         <v>1.06</v>
       </c>
-      <c r="X66">
-        <v>1.04</v>
-      </c>
       <c r="Y66">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z66">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AA66">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="AB66">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AC66">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AD66">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE66">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF66">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AG66">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK66">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11393,22 +11393,22 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="O68">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P68">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q68">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R68">
         <v>2.25</v>
       </c>
       <c r="S68">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T68">
         <v>2.95</v>
@@ -11426,19 +11426,19 @@
         <v>1</v>
       </c>
       <c r="Y68">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z68">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="AA68">
         <v>1.83</v>
       </c>
       <c r="AB68">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AC68">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="AD68">
         <v>1.38</v>
@@ -11447,10 +11447,10 @@
         <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG68">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK68">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>1.6</v>
       </c>
       <c r="T69">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="U69">
         <v>3.8</v>
@@ -11586,10 +11586,10 @@
         <v>1.02</v>
       </c>
       <c r="X69">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y69">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z69">
         <v>2.46</v>
@@ -11598,10 +11598,10 @@
         <v>2.62</v>
       </c>
       <c r="AB69">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AC69">
-        <v>5.43</v>
+        <v>5.52</v>
       </c>
       <c r="AD69">
         <v>1.09</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK69">
         <v>1.4</v>
@@ -11722,7 +11722,7 @@
         <v>1.68</v>
       </c>
       <c r="O70">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
         <v>4.2</v>
@@ -11740,10 +11740,10 @@
         <v>3</v>
       </c>
       <c r="U70">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="V70">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W70">
         <v>1.06</v>
@@ -11752,16 +11752,16 @@
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z70">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA70">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB70">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC70">
         <v>3.3</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK70">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,19 +11882,19 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O71">
         <v>3.4</v>
       </c>
       <c r="P71">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="Q71">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="R71">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="S71">
         <v>1.43</v>
@@ -11906,40 +11906,40 @@
         <v>3.04</v>
       </c>
       <c r="V71">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W71">
         <v>1.03</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y71">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z71">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AA71">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB71">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AC71">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="AD71">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE71">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF71">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG71">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK71">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O72">
         <v>3.75</v>
       </c>
       <c r="P72">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -12066,10 +12066,10 @@
         <v>3.5</v>
       </c>
       <c r="U72">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="V72">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W72">
         <v>1.14</v>
@@ -12081,7 +12081,7 @@
         <v>1.18</v>
       </c>
       <c r="Z72">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AA72">
         <v>1.55</v>
@@ -12090,7 +12090,7 @@
         <v>2.35</v>
       </c>
       <c r="AC72">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD72">
         <v>1.53</v>
@@ -12099,10 +12099,10 @@
         <v>1.17</v>
       </c>
       <c r="AF72">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG72">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK72">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="O73">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P73">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q73">
+        <v>2.42</v>
+      </c>
+      <c r="R73">
         <v>2.03</v>
       </c>
-      <c r="R73">
-        <v>2.28</v>
-      </c>
       <c r="S73">
+        <v>1.4</v>
+      </c>
+      <c r="T73">
+        <v>2.59</v>
+      </c>
+      <c r="U73">
+        <v>2.9</v>
+      </c>
+      <c r="V73">
         <v>1.36</v>
-      </c>
-      <c r="T73">
-        <v>2.75</v>
-      </c>
-      <c r="U73">
-        <v>2.96</v>
-      </c>
-      <c r="V73">
-        <v>1.35</v>
       </c>
       <c r="W73">
         <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z73">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="AA73">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB73">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC73">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AD73">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE73">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF73">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="AG73">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK73">
-        <v>2.46</v>
+        <v>1.81</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="O74">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P74">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q74">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="R74">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S74">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T74">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="U74">
-        <v>3.23</v>
+        <v>3.04</v>
       </c>
       <c r="V74">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W74">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y74">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z74">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="AA74">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AB74">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AC74">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AD74">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE74">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AG74">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,65 +12534,65 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P75">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="Q75">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="R75">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S75">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="T75">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="U75">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V75">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X75">
         <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z75">
-        <v>3.11</v>
+        <v>2.74</v>
       </c>
       <c r="AA75">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="AB75">
+        <v>1.61</v>
+      </c>
+      <c r="AC75">
+        <v>3.6</v>
+      </c>
+      <c r="AD75">
+        <v>1.19</v>
+      </c>
+      <c r="AE75">
+        <v>1.02</v>
+      </c>
+      <c r="AF75">
+        <v>1.91</v>
+      </c>
+      <c r="AG75">
         <v>1.75</v>
       </c>
-      <c r="AC75">
-        <v>3.52</v>
-      </c>
-      <c r="AD75">
-        <v>1.24</v>
-      </c>
-      <c r="AE75">
-        <v>1.05</v>
-      </c>
-      <c r="AF75">
-        <v>1.87</v>
-      </c>
-      <c r="AG75">
-        <v>1.82</v>
-      </c>
       <c r="AH75" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK75">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -627,51 +627,51 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
         <v>2.65</v>
       </c>
       <c r="P2">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="Q2">
-        <v>3.93</v>
+        <v>3.66</v>
       </c>
       <c r="R2">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="S2">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="T2">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="U2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V2">
         <v>1.2</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
         <v>1.07</v>
       </c>
       <c r="Y2">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Z2">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AA2">
         <v>2.83</v>
@@ -680,62 +680,62 @@
         <v>1.33</v>
       </c>
       <c r="AC2">
-        <v>6.2</v>
+        <v>6.05</v>
       </c>
       <c r="AD2">
         <v>1.06</v>
       </c>
       <c r="AE2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AG2">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -787,118 +787,118 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
         <v>1.8</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P3">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="Q3">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="S3">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="T3">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="U3">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Z3">
         <v>2.29</v>
       </c>
       <c r="AA3">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AB3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AC3">
-        <v>5.48</v>
+        <v>6</v>
       </c>
       <c r="AD3">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="AG3">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>["74"]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -950,118 +950,118 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="Q4">
         <v>2.6</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="T4">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z4">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="AA4">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AC4">
-        <v>3.04</v>
+        <v>3.72</v>
       </c>
       <c r="AD4">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AG4">
+        <v>1.8</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>["59"]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.25</v>
+      </c>
+      <c r="AK4">
+        <v>1.69</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>3</v>
+      </c>
+      <c r="AN4">
         <v>2</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.24</v>
-      </c>
-      <c r="AK4">
-        <v>1.61</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-1</v>
-      </c>
-      <c r="AN4">
-        <v>-1</v>
-      </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1104,81 +1104,81 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q5">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="R5">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S5">
         <v>1.3</v>
       </c>
       <c r="T5">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="U5">
         <v>2.63</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
         <v>1.1</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z5">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="AA5">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB5">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC5">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AD5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
         <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
         <v>2.2</v>
@@ -1190,41 +1190,41 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "33", "68"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AK5">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,130 +1264,130 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q6">
         <v>3.5</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U6">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA6">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB6">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AD6">
         <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
         <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+6"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "90+8"]</t>
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1593,127 +1593,127 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
+        <v>1.87</v>
+      </c>
+      <c r="O8">
+        <v>3.3</v>
+      </c>
+      <c r="P8">
+        <v>4.3</v>
+      </c>
+      <c r="Q8">
+        <v>2.54</v>
+      </c>
+      <c r="R8">
+        <v>1.97</v>
+      </c>
+      <c r="S8">
+        <v>1.48</v>
+      </c>
+      <c r="T8">
+        <v>2.47</v>
+      </c>
+      <c r="U8">
+        <v>3.15</v>
+      </c>
+      <c r="V8">
+        <v>1.31</v>
+      </c>
+      <c r="W8">
+        <v>1.03</v>
+      </c>
+      <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>1.36</v>
+      </c>
+      <c r="Z8">
+        <v>2.72</v>
+      </c>
+      <c r="AA8">
+        <v>2.21</v>
+      </c>
+      <c r="AB8">
+        <v>1.64</v>
+      </c>
+      <c r="AC8">
+        <v>3.82</v>
+      </c>
+      <c r="AD8">
+        <v>1.19</v>
+      </c>
+      <c r="AE8">
+        <v>1.03</v>
+      </c>
+      <c r="AF8">
+        <v>1.97</v>
+      </c>
+      <c r="AG8">
+        <v>1.75</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>["8", "73"]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.31</v>
+      </c>
+      <c r="AK8">
+        <v>1.85</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>5</v>
+      </c>
+      <c r="AN8">
         <v>2</v>
       </c>
-      <c r="O8">
-        <v>3.4</v>
-      </c>
-      <c r="P8">
-        <v>4.18</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>2.15</v>
-      </c>
-      <c r="AB8">
-        <v>1.66</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>-1</v>
-      </c>
-      <c r="AN8">
-        <v>-1</v>
-      </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,26 +1753,26 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "72"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1935,68 +1935,68 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q10">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
         <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="U10">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
         <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="Z10">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AC10">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AD10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,37 +2009,37 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK10">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2070,22 +2070,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2098,84 +2098,84 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>1.28</v>
+        <v>2.25</v>
       </c>
       <c r="O11">
-        <v>4.15</v>
+        <v>2.87</v>
       </c>
       <c r="P11">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q11">
-        <v>1.86</v>
+        <v>3.14</v>
       </c>
       <c r="R11">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="S11">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="T11">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
       <c r="U11">
-        <v>2.75</v>
+        <v>3.68</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="Z11">
-        <v>2.92</v>
+        <v>2.32</v>
       </c>
       <c r="AA11">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="AB11">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="AC11">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF11">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>["34"]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ11">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AK11">
-        <v>3.12</v>
+        <v>1.47</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,112 +2233,112 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.25</v>
+        <v>1.28</v>
       </c>
       <c r="O12">
-        <v>2.87</v>
+        <v>4.15</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Q12">
-        <v>3.14</v>
+        <v>1.86</v>
       </c>
       <c r="R12">
-        <v>1.84</v>
+        <v>2.07</v>
       </c>
       <c r="S12">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="T12">
-        <v>2.24</v>
+        <v>2.53</v>
       </c>
       <c r="U12">
-        <v>3.68</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
+        <v>1.05</v>
+      </c>
+      <c r="X12">
         <v>1.03</v>
       </c>
-      <c r="X12">
-        <v>1.06</v>
-      </c>
       <c r="Y12">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="Z12">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="AA12">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="AB12">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="AC12">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD12">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AE12">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="AG12">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>["42", "64"]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ12">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AK12">
-        <v>1.47</v>
+        <v>3.12</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2405,130 +2405,130 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="O13">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="Q13">
-        <v>3.15</v>
+        <v>3.64</v>
       </c>
       <c r="R13">
         <v>2.08</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T13">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="U13">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
+        <v>1.43</v>
+      </c>
+      <c r="W13">
+        <v>1.09</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
+        <v>1.21</v>
+      </c>
+      <c r="Z13">
+        <v>3.58</v>
+      </c>
+      <c r="AA13">
+        <v>1.85</v>
+      </c>
+      <c r="AB13">
+        <v>1.91</v>
+      </c>
+      <c r="AC13">
+        <v>2.93</v>
+      </c>
+      <c r="AD13">
         <v>1.39</v>
       </c>
-      <c r="W13">
-        <v>1.04</v>
-      </c>
-      <c r="X13">
-        <v>1.04</v>
-      </c>
-      <c r="Y13">
-        <v>1.25</v>
-      </c>
-      <c r="Z13">
-        <v>3.28</v>
-      </c>
-      <c r="AA13">
-        <v>1.95</v>
-      </c>
-      <c r="AB13">
-        <v>1.83</v>
-      </c>
-      <c r="AC13">
-        <v>3.25</v>
-      </c>
-      <c r="AD13">
-        <v>1.29</v>
-      </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "51", "57"]</t>
         </is>
       </c>
       <c r="AJ13">
         <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2587,68 +2587,68 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="O14">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="Q14">
-        <v>3.36</v>
+        <v>2.88</v>
       </c>
       <c r="R14">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="U14">
-        <v>3.14</v>
+        <v>2.27</v>
       </c>
       <c r="V14">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>2.17</v>
+        <v>1.71</v>
       </c>
       <c r="AB14">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC14">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD14">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AG14">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,37 +2661,37 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AK14">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2743,24 +2743,24 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q15">
         <v>3.26</v>
@@ -2769,19 +2769,19 @@
         <v>2.03</v>
       </c>
       <c r="S15">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U15">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="V15">
         <v>1.41</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,34 +2793,34 @@
         <v>3.28</v>
       </c>
       <c r="AA15">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB15">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC15">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE15">
         <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AG15">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+3"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2913,68 +2913,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3069,69 +3069,69 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="O17">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P17">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="Q17">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S17">
         <v>1.32</v>
       </c>
       <c r="T17">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U17">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="V17">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA17">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB17">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC17">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD17">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE17">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF17">
         <v>1.6</v>
@@ -3141,46 +3141,46 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK17">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O18">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="P18">
-        <v>7.2</v>
+        <v>7.01</v>
       </c>
       <c r="Q18">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R18">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="S18">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V18">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="AA18">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AB18">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AC18">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="AD18">
         <v>1.63</v>
       </c>
       <c r="AE18">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF18">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AK18">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -3395,45 +3395,45 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O19">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="P19">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q19">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S19">
         <v>1.2</v>
       </c>
       <c r="T19">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V19">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W19">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3442,71 +3442,71 @@
         <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>5.95</v>
+        <v>6.4</v>
       </c>
       <c r="AA19">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AB19">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="AC19">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AD19">
         <v>1.8</v>
       </c>
       <c r="AE19">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AF19">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AJ19">
         <v>1.03</v>
       </c>
       <c r="AK19">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,26 +3546,26 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71", "75"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "35", "58"]</t>
         </is>
       </c>
       <c r="AJ20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="O23">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="P23">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="Q23">
         <v>3.58</v>
@@ -4088,13 +4088,13 @@
         <v>1.02</v>
       </c>
       <c r="X23">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y23">
         <v>1.41</v>
       </c>
       <c r="Z23">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="AA23">
         <v>2.38</v>
@@ -4115,7 +4115,7 @@
         <v>1.94</v>
       </c>
       <c r="AG23">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AK23">
         <v>1.45</v>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -4210,14 +4210,14 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+2"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
@@ -4361,13 +4361,13 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4393,59 +4393,59 @@
         <v>4.2</v>
       </c>
       <c r="Q25">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="R25">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="S25">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="T25">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="U25">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
         <v>1.06</v>
       </c>
       <c r="Y25">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z25">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="AA25">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AB25">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC25">
         <v>4.2</v>
       </c>
       <c r="AD25">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE25">
         <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG25">
         <v>1.8</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
@@ -4457,34 +4457,34 @@
         <v>1.39</v>
       </c>
       <c r="AK25">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,33 +4524,33 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O26">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
         <v>3.4</v>
@@ -4559,19 +4559,19 @@
         <v>2.38</v>
       </c>
       <c r="R26">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T26">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U26">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="V26">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
         <v>1.09</v>
@@ -4583,19 +4583,19 @@
         <v>1.16</v>
       </c>
       <c r="Z26">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA26">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB26">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="AC26">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD26">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE26">
         <v>1.15</v>
@@ -4604,50 +4604,50 @@
         <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17"]</t>
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK26">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="O27">
         <v>3.6</v>
       </c>
       <c r="P27">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="Q27">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T27">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="U27">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="V27">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z27">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="AA27">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AB27">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AC27">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE27">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>3.23</v>
+        <v>3.7</v>
       </c>
       <c r="Q28">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R28">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T28">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="U28">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z28">
-        <v>3.99</v>
+        <v>3.45</v>
       </c>
       <c r="AA28">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AB28">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC28">
-        <v>2.85</v>
+        <v>3.38</v>
       </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG28">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,46 +5039,46 @@
         <v>1.85</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="P29">
-        <v>3.9</v>
+        <v>3.53</v>
       </c>
       <c r="Q29">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="R29">
         <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U29">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="V29">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AA29">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AB29">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AC29">
         <v>3.4</v>
@@ -5087,13 +5087,13 @@
         <v>1.24</v>
       </c>
       <c r="AE29">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
         <v>1.83</v>
       </c>
       <c r="AG29">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,77 +5202,77 @@
         <v>1.73</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q30">
-        <v>2.44</v>
+        <v>2.61</v>
       </c>
       <c r="R30">
+        <v>1.86</v>
+      </c>
+      <c r="S30">
+        <v>1.45</v>
+      </c>
+      <c r="T30">
+        <v>2.31</v>
+      </c>
+      <c r="U30">
+        <v>3.34</v>
+      </c>
+      <c r="V30">
+        <v>1.23</v>
+      </c>
+      <c r="W30">
+        <v>1.05</v>
+      </c>
+      <c r="X30">
+        <v>1.04</v>
+      </c>
+      <c r="Y30">
+        <v>1.46</v>
+      </c>
+      <c r="Z30">
+        <v>2.47</v>
+      </c>
+      <c r="AA30">
+        <v>2.5</v>
+      </c>
+      <c r="AB30">
+        <v>1.57</v>
+      </c>
+      <c r="AC30">
+        <v>4.5</v>
+      </c>
+      <c r="AD30">
+        <v>1.18</v>
+      </c>
+      <c r="AE30">
+        <v>1</v>
+      </c>
+      <c r="AF30">
+        <v>2</v>
+      </c>
+      <c r="AG30">
+        <v>1.61</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.2</v>
+      </c>
+      <c r="AK30">
         <v>1.85</v>
-      </c>
-      <c r="S30">
-        <v>1.5</v>
-      </c>
-      <c r="T30">
-        <v>2.24</v>
-      </c>
-      <c r="U30">
-        <v>3.68</v>
-      </c>
-      <c r="V30">
-        <v>1.2</v>
-      </c>
-      <c r="W30">
-        <v>1.03</v>
-      </c>
-      <c r="X30">
-        <v>1.06</v>
-      </c>
-      <c r="Y30">
-        <v>1.51</v>
-      </c>
-      <c r="Z30">
-        <v>2.41</v>
-      </c>
-      <c r="AA30">
-        <v>2.44</v>
-      </c>
-      <c r="AB30">
-        <v>1.42</v>
-      </c>
-      <c r="AC30">
-        <v>5.25</v>
-      </c>
-      <c r="AD30">
-        <v>1.14</v>
-      </c>
-      <c r="AE30">
-        <v>1.02</v>
-      </c>
-      <c r="AF30">
-        <v>2.25</v>
-      </c>
-      <c r="AG30">
-        <v>1.52</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.09</v>
-      </c>
-      <c r="AK30">
-        <v>2.05</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.94</v>
+        <v>4.19</v>
       </c>
       <c r="O31">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="P31">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q31">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="R31">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S31">
         <v>1.51</v>
       </c>
       <c r="T31">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="U31">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="V31">
         <v>1.27</v>
@@ -5392,34 +5392,34 @@
         <v>1.01</v>
       </c>
       <c r="X31">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z31">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AA31">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AB31">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC31">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AD31">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE31">
         <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG31">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AK31">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,46 +5528,46 @@
         <v>2.1</v>
       </c>
       <c r="O32">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q32">
+        <v>2.75</v>
+      </c>
+      <c r="R32">
+        <v>1.99</v>
+      </c>
+      <c r="S32">
+        <v>1.43</v>
+      </c>
+      <c r="T32">
+        <v>2.57</v>
+      </c>
+      <c r="U32">
         <v>2.8</v>
       </c>
-      <c r="R32">
-        <v>2.01</v>
-      </c>
-      <c r="S32">
-        <v>1.42</v>
-      </c>
-      <c r="T32">
-        <v>2.59</v>
-      </c>
-      <c r="U32">
-        <v>3.07</v>
-      </c>
       <c r="V32">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W32">
         <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z32">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA32">
         <v>1.97</v>
       </c>
       <c r="AB32">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC32">
         <v>3.6</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q33">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="R33">
-        <v>2.78</v>
+        <v>3.55</v>
       </c>
       <c r="S33">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="T33">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="U33">
-        <v>2.28</v>
+        <v>1.76</v>
       </c>
       <c r="V33">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="W33">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Z33">
-        <v>4.35</v>
+        <v>7.5</v>
       </c>
       <c r="AA33">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AB33">
-        <v>2.38</v>
+        <v>3.58</v>
       </c>
       <c r="AC33">
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="AD33">
-        <v>1.48</v>
+        <v>2.13</v>
       </c>
       <c r="AE33">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="AF33">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="AG33">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK33">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,43 +5851,43 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="O34">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P34">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q34">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="R34">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S34">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="T34">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="U34">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="V34">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W34">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X34">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Y34">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="Z34">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="AA34">
         <v>3.2</v>
@@ -5896,19 +5896,19 @@
         <v>1.36</v>
       </c>
       <c r="AC34">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AD34">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE34">
         <v>1.01</v>
       </c>
       <c r="AF34">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AG34">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AK34">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6020,13 +6020,13 @@
         <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="Q35">
         <v>2.62</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
         <v>1.33</v>
@@ -6035,7 +6035,7 @@
         <v>3.31</v>
       </c>
       <c r="U35">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V35">
         <v>1.45</v>
@@ -6050,13 +6050,13 @@
         <v>1.21</v>
       </c>
       <c r="Z35">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AA35">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB35">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC35">
         <v>2.72</v>
@@ -6065,13 +6065,13 @@
         <v>1.36</v>
       </c>
       <c r="AE35">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
         <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
+        <v>4.65</v>
+      </c>
+      <c r="O36">
         <v>4.1</v>
       </c>
-      <c r="O36">
-        <v>3.88</v>
-      </c>
       <c r="P36">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q36">
-        <v>4.19</v>
+        <v>5.3</v>
       </c>
       <c r="R36">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U36">
         <v>2.56</v>
       </c>
       <c r="V36">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
         <v>1.1</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="AA36">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB36">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AC36">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="AD36">
         <v>1.4</v>
       </c>
       <c r="AE36">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6343,61 +6343,61 @@
         <v>1.67</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q37">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R37">
         <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U37">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="V37">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z37">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AA37">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AB37">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="AC37">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD37">
         <v>1.58</v>
       </c>
       <c r="AE37">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF37">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
         <v>2.05</v>
@@ -6480,42 +6480,42 @@
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O38">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
         <v>1.67</v>
       </c>
       <c r="Q38">
-        <v>4.5</v>
+        <v>4.78</v>
       </c>
       <c r="R38">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S38">
         <v>1.28</v>
@@ -6524,86 +6524,86 @@
         <v>3.18</v>
       </c>
       <c r="U38">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V38">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA38">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB38">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC38">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AE38">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20"]</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "90+2"]</t>
         </is>
       </c>
       <c r="AJ38">
         <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -6655,54 +6655,54 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q39">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S39">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U39">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V39">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z39">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA39">
         <v>1.98</v>
@@ -6711,32 +6711,32 @@
         <v>1.74</v>
       </c>
       <c r="AC39">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AD39">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE39">
         <v>1.04</v>
       </c>
       <c r="AF39">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AG39">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
+          <t>["52"]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ39">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK39">
         <v>1.87</v>
@@ -6745,28 +6745,28 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -6818,118 +6818,118 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="O40">
-        <v>4.05</v>
+        <v>4.95</v>
       </c>
       <c r="P40">
-        <v>6.5</v>
+        <v>6.79</v>
       </c>
       <c r="Q40">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="R40">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T40">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="U40">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="V40">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>3.84</v>
+        <v>4.33</v>
       </c>
       <c r="AA40">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB40">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AC40">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="AD40">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF40">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG40">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
+          <t>["86", "86", "90+2", "90+3"]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ40">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK40">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AL40">
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -6981,14 +6981,14 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72", "86"]</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63", "74"]</t>
         </is>
       </c>
       <c r="AJ41">
@@ -7071,28 +7071,28 @@
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7132,26 +7132,26 @@
         </is>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "49", "57", "74"]</t>
         </is>
       </c>
       <c r="AJ42">
@@ -7234,28 +7234,28 @@
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P44">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q44">
         <v>5.5</v>
@@ -7499,7 +7499,7 @@
         <v>1.32</v>
       </c>
       <c r="T44">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U44">
         <v>2.5</v>
@@ -7511,13 +7511,13 @@
         <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
         <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA44">
         <v>1.7</v>
@@ -7532,13 +7532,13 @@
         <v>1.38</v>
       </c>
       <c r="AE44">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AG44">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AK44">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7680,7 +7680,7 @@
         <v>1.17</v>
       </c>
       <c r="Z45">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AA45">
         <v>1.62</v>
@@ -7689,13 +7689,13 @@
         <v>2.02</v>
       </c>
       <c r="AC45">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="AD45">
         <v>1.36</v>
       </c>
       <c r="AE45">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF45">
         <v>1.73</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O46">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P46">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="Q46">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="R46">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="S46">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T46">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="U46">
         <v>2.25</v>
       </c>
       <c r="V46">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W46">
         <v>1.14</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA46">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB46">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AC46">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="AD46">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AE46">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF46">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG46">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.3</v>
       </c>
       <c r="AK46">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7973,49 +7973,49 @@
         <v>1.53</v>
       </c>
       <c r="O47">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="P47">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="Q47">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="R47">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U47">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="V47">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W47">
         <v>1.12</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z47">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AA47">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB47">
         <v>2.26</v>
       </c>
       <c r="AC47">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AD47">
         <v>1.42</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK47">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,31 +8133,31 @@
         </is>
       </c>
       <c r="N48">
+        <v>2.53</v>
+      </c>
+      <c r="O48">
+        <v>2.92</v>
+      </c>
+      <c r="P48">
         <v>2.5</v>
       </c>
-      <c r="O48">
-        <v>3.1</v>
-      </c>
-      <c r="P48">
-        <v>3</v>
-      </c>
       <c r="Q48">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="R48">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="S48">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T48">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="U48">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="V48">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W48">
         <v>1.02</v>
@@ -8166,31 +8166,31 @@
         <v>1.05</v>
       </c>
       <c r="Y48">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z48">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AA48">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB48">
         <v>1.57</v>
       </c>
       <c r="AC48">
-        <v>4.25</v>
+        <v>4.65</v>
       </c>
       <c r="AD48">
         <v>1.18</v>
       </c>
       <c r="AE48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF48">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG48">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>8.18</v>
       </c>
       <c r="Q50">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="R50">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="S50">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="T50">
-        <v>4.75</v>
+        <v>3.42</v>
       </c>
       <c r="U50">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="V50">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="W50">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
+        <v>1.12</v>
+      </c>
+      <c r="Z50">
+        <v>5.3</v>
+      </c>
+      <c r="AA50">
+        <v>1.42</v>
+      </c>
+      <c r="AB50">
+        <v>2.59</v>
+      </c>
+      <c r="AC50">
+        <v>2.02</v>
+      </c>
+      <c r="AD50">
+        <v>1.68</v>
+      </c>
+      <c r="AE50">
+        <v>1.28</v>
+      </c>
+      <c r="AF50">
+        <v>2.04</v>
+      </c>
+      <c r="AG50">
+        <v>1.7</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.05</v>
       </c>
-      <c r="Z50">
-        <v>6.6</v>
-      </c>
-      <c r="AA50">
-        <v>1.3</v>
-      </c>
-      <c r="AB50">
-        <v>2.97</v>
-      </c>
-      <c r="AC50">
-        <v>1.89</v>
-      </c>
-      <c r="AD50">
-        <v>1.85</v>
-      </c>
-      <c r="AE50">
-        <v>1.32</v>
-      </c>
-      <c r="AF50">
-        <v>1.78</v>
-      </c>
-      <c r="AG50">
-        <v>1.89</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.06</v>
-      </c>
       <c r="AK50">
-        <v>4.7</v>
+        <v>4.32</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,28 +8622,28 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q51">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="R51">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S51">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T51">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="U51">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="V51">
         <v>1.32</v>
@@ -8652,31 +8652,31 @@
         <v>1.03</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z51">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="AA51">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AB51">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC51">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD51">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE51">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF51">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
         <v>1.65</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK51">
         <v>1.49</v>
@@ -9111,80 +9111,80 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="O54">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P54">
-        <v>4.6</v>
+        <v>5.69</v>
       </c>
       <c r="Q54">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R54">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="S54">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="U54">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="V54">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y54">
+        <v>1.21</v>
+      </c>
+      <c r="Z54">
+        <v>3.62</v>
+      </c>
+      <c r="AA54">
+        <v>1.77</v>
+      </c>
+      <c r="AB54">
+        <v>2.01</v>
+      </c>
+      <c r="AC54">
+        <v>2.72</v>
+      </c>
+      <c r="AD54">
+        <v>1.36</v>
+      </c>
+      <c r="AE54">
+        <v>1.11</v>
+      </c>
+      <c r="AF54">
+        <v>1.77</v>
+      </c>
+      <c r="AG54">
+        <v>1.94</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
         <v>1.24</v>
       </c>
-      <c r="Z54">
-        <v>3.38</v>
-      </c>
-      <c r="AA54">
-        <v>1.87</v>
-      </c>
-      <c r="AB54">
-        <v>1.9</v>
-      </c>
-      <c r="AC54">
-        <v>2.94</v>
-      </c>
-      <c r="AD54">
-        <v>1.3</v>
-      </c>
-      <c r="AE54">
-        <v>1.07</v>
-      </c>
-      <c r="AF54">
-        <v>1.8</v>
-      </c>
-      <c r="AG54">
-        <v>1.9</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54">
-        <v>1.26</v>
-      </c>
       <c r="AK54">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,49 +9274,49 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="O55">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="P55">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q55">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="R55">
         <v>2.05</v>
       </c>
       <c r="S55">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T55">
         <v>2.59</v>
       </c>
       <c r="U55">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="V55">
         <v>1.38</v>
       </c>
       <c r="W55">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X55">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y55">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z55">
         <v>3.24</v>
       </c>
       <c r="AA55">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AB55">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC55">
         <v>3.8</v>
@@ -9328,10 +9328,10 @@
         <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG55">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="O56">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="P56">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="Q56">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="R56">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S56">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T56">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V56">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>4.08</v>
+        <v>3.84</v>
       </c>
       <c r="AA56">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB56">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC56">
         <v>2.8</v>
       </c>
       <c r="AD56">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE56">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF56">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG56">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.24</v>
       </c>
       <c r="AK56">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9603,16 +9603,16 @@
         <v>1.53</v>
       </c>
       <c r="O57">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P57">
         <v>5.18</v>
       </c>
       <c r="Q57">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="R57">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S57">
         <v>1.42</v>
@@ -9621,7 +9621,7 @@
         <v>2.88</v>
       </c>
       <c r="U57">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="V57">
         <v>1.35</v>
@@ -9630,19 +9630,19 @@
         <v>1.02</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y57">
         <v>1.34</v>
       </c>
       <c r="Z57">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AA57">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB57">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC57">
         <v>3.5</v>
@@ -9651,10 +9651,10 @@
         <v>1.25</v>
       </c>
       <c r="AE57">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF57">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AG57">
         <v>1.67</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK57">
         <v>2.27</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="O59">
         <v>3</v>
@@ -9935,55 +9935,55 @@
         <v>2.75</v>
       </c>
       <c r="Q59">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R59">
         <v>1.92</v>
       </c>
       <c r="S59">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T59">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="U59">
         <v>3.3</v>
       </c>
       <c r="V59">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W59">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X59">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y59">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z59">
-        <v>2.73</v>
+        <v>3.16</v>
       </c>
       <c r="AA59">
-        <v>2.41</v>
+        <v>2.26</v>
       </c>
       <c r="AB59">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC59">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AD59">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE59">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF59">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG59">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>3.02</v>
       </c>
       <c r="Q61">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="R61">
         <v>1.91</v>
@@ -10273,7 +10273,7 @@
         <v>2.63</v>
       </c>
       <c r="U61">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V61">
         <v>1.28</v>
@@ -10282,31 +10282,31 @@
         <v>1.02</v>
       </c>
       <c r="X61">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y61">
         <v>1.4</v>
       </c>
       <c r="Z61">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AA61">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AB61">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC61">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="AD61">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE61">
         <v>1.06</v>
       </c>
       <c r="AF61">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG61">
         <v>1.75</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,80 +10578,80 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O63">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P63">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="Q63">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R63">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="T63">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="U63">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="V63">
+        <v>1.29</v>
+      </c>
+      <c r="W63">
+        <v>1.03</v>
+      </c>
+      <c r="X63">
+        <v>1.03</v>
+      </c>
+      <c r="Y63">
+        <v>1.4</v>
+      </c>
+      <c r="Z63">
+        <v>2.75</v>
+      </c>
+      <c r="AA63">
+        <v>2.17</v>
+      </c>
+      <c r="AB63">
+        <v>1.59</v>
+      </c>
+      <c r="AC63">
+        <v>4.1</v>
+      </c>
+      <c r="AD63">
+        <v>1.17</v>
+      </c>
+      <c r="AE63">
+        <v>1.05</v>
+      </c>
+      <c r="AF63">
+        <v>1.9</v>
+      </c>
+      <c r="AG63">
+        <v>1.78</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
         <v>1.22</v>
       </c>
-      <c r="W63">
-        <v>1.04</v>
-      </c>
-      <c r="X63">
-        <v>1.1</v>
-      </c>
-      <c r="Y63">
-        <v>1.51</v>
-      </c>
-      <c r="Z63">
-        <v>2.36</v>
-      </c>
-      <c r="AA63">
-        <v>2.62</v>
-      </c>
-      <c r="AB63">
-        <v>1.44</v>
-      </c>
-      <c r="AC63">
-        <v>5.05</v>
-      </c>
-      <c r="AD63">
-        <v>1.14</v>
-      </c>
-      <c r="AE63">
-        <v>1.03</v>
-      </c>
-      <c r="AF63">
-        <v>2.15</v>
-      </c>
-      <c r="AG63">
-        <v>1.62</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.33</v>
-      </c>
       <c r="AK63">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,55 +10741,55 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="O64">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P64">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q64">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="R64">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S64">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T64">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="U64">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V64">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W64">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z64">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AA64">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AB64">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AC64">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD64">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE64">
         <v>1.03</v>
@@ -10798,7 +10798,7 @@
         <v>1.9</v>
       </c>
       <c r="AG64">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK64">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="O65">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P65">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="Q65">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="R65">
+        <v>2</v>
+      </c>
+      <c r="S65">
+        <v>1.43</v>
+      </c>
+      <c r="T65">
+        <v>2.5</v>
+      </c>
+      <c r="U65">
+        <v>3</v>
+      </c>
+      <c r="V65">
+        <v>1.33</v>
+      </c>
+      <c r="W65">
+        <v>1.03</v>
+      </c>
+      <c r="X65">
+        <v>1.03</v>
+      </c>
+      <c r="Y65">
+        <v>1.33</v>
+      </c>
+      <c r="Z65">
+        <v>2.81</v>
+      </c>
+      <c r="AA65">
         <v>2.1</v>
-      </c>
-      <c r="S65">
-        <v>1.45</v>
-      </c>
-      <c r="T65">
-        <v>2.62</v>
-      </c>
-      <c r="U65">
-        <v>3.2</v>
-      </c>
-      <c r="V65">
-        <v>1.32</v>
-      </c>
-      <c r="W65">
-        <v>1.04</v>
-      </c>
-      <c r="X65">
-        <v>1.04</v>
-      </c>
-      <c r="Y65">
-        <v>1.36</v>
-      </c>
-      <c r="Z65">
-        <v>2.9</v>
-      </c>
-      <c r="AA65">
-        <v>2.14</v>
       </c>
       <c r="AB65">
         <v>1.66</v>
       </c>
       <c r="AC65">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AD65">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE65">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF65">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG65">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK65">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="O66">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P66">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q66">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R66">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="S66">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="T66">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="U66">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V66">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W66">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X66">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y66">
+        <v>1.52</v>
+      </c>
+      <c r="Z66">
+        <v>2.34</v>
+      </c>
+      <c r="AA66">
+        <v>2.55</v>
+      </c>
+      <c r="AB66">
+        <v>1.45</v>
+      </c>
+      <c r="AC66">
+        <v>5.1</v>
+      </c>
+      <c r="AD66">
+        <v>1.14</v>
+      </c>
+      <c r="AE66">
+        <v>1.04</v>
+      </c>
+      <c r="AF66">
+        <v>2.15</v>
+      </c>
+      <c r="AG66">
+        <v>1.61</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>1.2</v>
+      </c>
+      <c r="AK66">
         <v>1.47</v>
-      </c>
-      <c r="Z66">
-        <v>2.44</v>
-      </c>
-      <c r="AA66">
-        <v>2.45</v>
-      </c>
-      <c r="AB66">
-        <v>1.52</v>
-      </c>
-      <c r="AC66">
-        <v>5</v>
-      </c>
-      <c r="AD66">
-        <v>1.17</v>
-      </c>
-      <c r="AE66">
-        <v>1.02</v>
-      </c>
-      <c r="AF66">
-        <v>2.05</v>
-      </c>
-      <c r="AG66">
-        <v>1.67</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.29</v>
-      </c>
-      <c r="AK66">
-        <v>1.57</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,61 +11230,61 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O67">
         <v>3.4</v>
       </c>
       <c r="P67">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="Q67">
-        <v>2.92</v>
+        <v>3.02</v>
       </c>
       <c r="R67">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="S67">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U67">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="V67">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W67">
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z67">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA67">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB67">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC67">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD67">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE67">
         <v>1.07</v>
       </c>
       <c r="AF67">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG67">
         <v>2.08</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK67">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.71</v>
+        <v>3.5</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P68">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -11408,49 +11408,49 @@
         <v>2.25</v>
       </c>
       <c r="S68">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T68">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="U68">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V68">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W68">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X68">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
         <v>1.22</v>
       </c>
       <c r="Z68">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AA68">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AB68">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC68">
         <v>2.77</v>
       </c>
       <c r="AD68">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE68">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF68">
         <v>1.6</v>
       </c>
       <c r="AG68">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK68">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12045,31 +12045,31 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="O72">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="P72">
-        <v>4.08</v>
+        <v>4.85</v>
       </c>
       <c r="Q72">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="R72">
         <v>2.4</v>
       </c>
       <c r="S72">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T72">
         <v>3.5</v>
       </c>
       <c r="U72">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V72">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W72">
         <v>1.14</v>
@@ -12078,47 +12078,47 @@
         <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z72">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA72">
+        <v>1.51</v>
+      </c>
+      <c r="AB72">
+        <v>2.52</v>
+      </c>
+      <c r="AC72">
+        <v>2.25</v>
+      </c>
+      <c r="AD72">
         <v>1.55</v>
       </c>
-      <c r="AB72">
-        <v>2.35</v>
-      </c>
-      <c r="AC72">
-        <v>2.3</v>
-      </c>
-      <c r="AD72">
-        <v>1.53</v>
-      </c>
       <c r="AE72">
+        <v>1.24</v>
+      </c>
+      <c r="AF72">
+        <v>1.55</v>
+      </c>
+      <c r="AG72">
+        <v>2.25</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
         <v>1.17</v>
       </c>
-      <c r="AF72">
-        <v>1.53</v>
-      </c>
-      <c r="AG72">
-        <v>2.3</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.18</v>
-      </c>
       <c r="AK72">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,28 +12208,28 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="O73">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P73">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="Q73">
-        <v>2.42</v>
+        <v>2.01</v>
       </c>
       <c r="R73">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S73">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T73">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="U73">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="V73">
         <v>1.36</v>
@@ -12238,34 +12238,34 @@
         <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y73">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z73">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AA73">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB73">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AC73">
-        <v>3.59</v>
+        <v>3.42</v>
       </c>
       <c r="AD73">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE73">
         <v>1.04</v>
       </c>
       <c r="AF73">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="AG73">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>1.81</v>
+        <v>2.46</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,65 +12371,65 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="O74">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P74">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q74">
-        <v>2.01</v>
+        <v>2.57</v>
       </c>
       <c r="R74">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S74">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="T74">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="U74">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="V74">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W74">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="Z74">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="AA74">
+        <v>2.27</v>
+      </c>
+      <c r="AB74">
+        <v>1.61</v>
+      </c>
+      <c r="AC74">
+        <v>3.6</v>
+      </c>
+      <c r="AD74">
+        <v>1.19</v>
+      </c>
+      <c r="AE74">
+        <v>1.02</v>
+      </c>
+      <c r="AF74">
+        <v>1.91</v>
+      </c>
+      <c r="AG74">
         <v>1.75</v>
       </c>
-      <c r="AB74">
-        <v>1.59</v>
-      </c>
-      <c r="AC74">
-        <v>3.42</v>
-      </c>
-      <c r="AD74">
-        <v>1.23</v>
-      </c>
-      <c r="AE74">
-        <v>1.04</v>
-      </c>
-      <c r="AF74">
-        <v>2.09</v>
-      </c>
-      <c r="AG74">
-        <v>1.5</v>
-      </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK74">
-        <v>2.46</v>
+        <v>1.77</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="O75">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="Q75">
-        <v>2.57</v>
+        <v>2.42</v>
       </c>
       <c r="R75">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S75">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T75">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="U75">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="V75">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W75">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X75">
         <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AA75">
-        <v>2.27</v>
+        <v>1.78</v>
       </c>
       <c r="AB75">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC75">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="AD75">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE75">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF75">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AG75">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK75">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-09-07.xlsx
+++ b/jogos_2026-09-07.xlsx
@@ -3211,19 +3211,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -3232,118 +3232,118 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="O18">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="P18">
-        <v>7.01</v>
+        <v>9.5</v>
       </c>
       <c r="Q18">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="R18">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="U18">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="V18">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z18">
-        <v>5.15</v>
+        <v>6.4</v>
       </c>
       <c r="AA18">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AB18">
-        <v>2.57</v>
+        <v>2.97</v>
       </c>
       <c r="AC18">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="AD18">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AE18">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AF18">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AJ18">
         <v>1.03</v>
       </c>
       <c r="AK18">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3374,19 +3374,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -3395,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -3406,107 +3406,107 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="O19">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="P19">
-        <v>9.5</v>
+        <v>7.01</v>
       </c>
       <c r="Q19">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="R19">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="S19">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="V19">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="W19">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>6.4</v>
+        <v>5.15</v>
       </c>
       <c r="AA19">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AB19">
-        <v>2.97</v>
+        <v>2.57</v>
       </c>
       <c r="AC19">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="AD19">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AE19">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>["72"]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>["54"]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ19">
         <v>1.03</v>
       </c>
       <c r="AK19">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AN19">
         <v>1</v>
       </c>
       <c r="AO19">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AP19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AQ19">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AR19">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="AS19">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="AT19">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4050,11 +4050,11 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4687,26 +4687,26 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "66", "87"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4850,26 +4850,26 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "90+3"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "10", "34", "45+1"]</t>
         </is>
       </c>
       <c r="AJ28">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5028,11 +5028,11 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5176,26 +5176,26 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "31", "48"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5339,26 +5339,26 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "56"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55"]</t>
         </is>
       </c>
       <c r="AJ31">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,26 +5502,26 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "87"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,26 +5665,26 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "90+13"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
@@ -5767,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5828,13 +5828,13 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -5843,11 +5843,11 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57"]</t>
         </is>
       </c>
       <c r="AJ34">
@@ -5930,28 +5930,28 @@
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5982,19 +5982,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -6006,72 +6006,72 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.25</v>
+        <v>4.65</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P35">
-        <v>2.93</v>
+        <v>1.5</v>
       </c>
       <c r="Q35">
-        <v>2.62</v>
+        <v>5.3</v>
       </c>
       <c r="R35">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="U35">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="AA35">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AC35">
-        <v>2.72</v>
+        <v>2.51</v>
       </c>
       <c r="AD35">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE35">
         <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6080,41 +6080,41 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G36">
@@ -6173,111 +6173,111 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
-        <v>4.65</v>
+        <v>1.67</v>
       </c>
       <c r="O36">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q36">
-        <v>5.3</v>
+        <v>2.24</v>
       </c>
       <c r="R36">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T36">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U36">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W36">
         <v>1.1</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>4.05</v>
+        <v>4.45</v>
       </c>
       <c r="AA36">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AB36">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AC36">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AD36">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AE36">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF36">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG36">
+        <v>2.2</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.2</v>
+      </c>
+      <c r="AK36">
         <v>2.05</v>
       </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.22</v>
-      </c>
-      <c r="AK36">
-        <v>1.16</v>
-      </c>
       <c r="AL36">
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6308,19 +6308,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -6329,118 +6329,118 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P37">
-        <v>4.4</v>
+        <v>2.93</v>
       </c>
       <c r="Q37">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="U37">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="V37">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W37">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z37">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="AA37">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AB37">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AC37">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="AD37">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AE37">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF37">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG37">
         <v>2.2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "63", "75", "79"]</t>
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -7310,66 +7310,66 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="O43">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="P43">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="Q43">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="R43">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T43">
         <v>2.9</v>
       </c>
       <c r="U43">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="V43">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W43">
         <v>1.07</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
         <v>1.28</v>
       </c>
       <c r="Z43">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA43">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB43">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AC43">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AD43">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE43">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
         <v>1.55</v>
@@ -7384,41 +7384,41 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AJ43">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL43">
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -7473,11 +7473,11 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AJ44">
@@ -7560,28 +7560,28 @@
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7621,26 +7621,26 @@
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "30", "46"]</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "45+1"]</t>
         </is>
       </c>
       <c r="AJ45">
@@ -7723,28 +7723,28 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7784,26 +7784,26 @@
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "35", "67", "79"]</t>
         </is>
       </c>
       <c r="AJ46">
@@ -7886,28 +7886,28 @@
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -7959,14 +7959,14 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "52", "55", "77"]</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
@@ -8049,28 +8049,28 @@
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -8125,11 +8125,11 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N48">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AJ48">
@@ -8212,28 +8212,28 @@
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN48">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO48">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP48">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ48">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS48">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -8273,26 +8273,26 @@
         </is>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>0</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49">
         <v>0</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N49">
@@ -8357,12 +8357,12 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55", "82"]</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30"]</t>
         </is>
       </c>
       <c r="AJ49">
@@ -8375,28 +8375,28 @@
         <v>0</v>
       </c>
       <c r="AM49">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN49">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO49">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP49">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS49">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT49">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
@@ -8439,13 +8439,13 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N50">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "45"]</t>
         </is>
       </c>
       <c r="AJ50">
@@ -8538,28 +8538,28 @@
         <v>0</v>
       </c>
       <c r="AM50">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN50">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO50">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP50">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ50">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR50">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS50">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT50">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
@@ -8599,13 +8599,13 @@
         </is>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -8614,11 +8614,11 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N51">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32"]</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AJ51">
@@ -8701,28 +8701,28 @@
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN51">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO51">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP51">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AR51">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS51">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT51">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N52">
@@ -8864,28 +8864,28 @@
         <v>0</v>
       </c>
       <c r="AM52">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN52">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO52">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP52">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS52">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT52">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -8937,14 +8937,14 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N53">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "52", "53"]</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70"]</t>
         </is>
       </c>
       <c r="AJ53">
@@ -9027,28 +9027,28 @@
         <v>0</v>
       </c>
       <c r="AM53">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN53">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO53">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP53">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ53">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR53">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS53">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT53">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
@@ -9088,26 +9088,26 @@
         </is>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N54">
@@ -9172,12 +9172,12 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "33", "90+4"]</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AJ54">
@@ -9190,28 +9190,28 @@
         <v>0</v>
       </c>
       <c r="AM54">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN54">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO54">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP54">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ54">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR54">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS54">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT54">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
@@ -9251,26 +9251,26 @@
         </is>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N55">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "11", "89"]</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "76"]</t>
         </is>
       </c>
       <c r="AJ55">
@@ -9353,28 +9353,28 @@
         <v>0</v>
       </c>
       <c r="AM55">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN55">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO55">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP55">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ55">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AR55">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS55">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT55">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
@@ -9414,10 +9414,10 @@
         </is>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -9426,14 +9426,14 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N56">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60"]</t>
         </is>
       </c>
       <c r="AJ56">
@@ -9516,28 +9516,28 @@
         <v>0</v>
       </c>
       <c r="AM56">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN56">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO56">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP56">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ56">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AR56">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS56">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT56">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
@@ -9577,26 +9577,26 @@
         </is>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H57">
         <v>0</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L57">
         <v>0</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N57">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "54", "61", "85"]</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
@@ -9679,28 +9679,28 @@
         <v>0</v>
       </c>
       <c r="AM57">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN57">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO57">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP57">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ57">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR57">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS57">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT57">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         </is>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -9752,39 +9752,39 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58">
         <v>0</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N58">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="O58">
         <v>3.3</v>
       </c>
       <c r="P58">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="Q58">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R58">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S58">
         <v>1.37</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="U58">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="V58">
         <v>1.41</v>
@@ -9796,25 +9796,25 @@
         <v>1</v>
       </c>
       <c r="Y58">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z58">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA58">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB58">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AC58">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="AD58">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE58">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF58">
         <v>1.73</v>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46"]</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
@@ -9836,34 +9836,34 @@
         <v>1.27</v>
       </c>
       <c r="AK58">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL58">
         <v>0</v>
       </c>
       <c r="AM58">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN58">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO58">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP58">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ58">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR58">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AS58">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT58">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
@@ -9903,10 +9903,10 @@
         </is>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -9915,14 +9915,14 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N59">
@@ -9987,12 +9987,12 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49"]</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75", "88"]</t>
         </is>
       </c>
       <c r="AJ59">
@@ -10005,28 +10005,28 @@
         <v>0</v>
       </c>
       <c r="AM59">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN59">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO59">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP59">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR59">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AS59">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT59">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
@@ -10066,10 +10066,10 @@
         </is>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -10078,45 +10078,45 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q60">
-        <v>4.7</v>
+        <v>4.87</v>
       </c>
       <c r="R60">
         <v>2.18</v>
       </c>
       <c r="S60">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T60">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U60">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V60">
         <v>1.43</v>
       </c>
       <c r="W60">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10125,71 +10125,71 @@
         <v>1.18</v>
       </c>
       <c r="Z60">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="AA60">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB60">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC60">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD60">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE60">
+        <v>1.11</v>
+      </c>
+      <c r="AF60">
+        <v>1.66</v>
+      </c>
+      <c r="AG60">
+        <v>2.05</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>["87"]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>["48", "64", "75"]</t>
+        </is>
+      </c>
+      <c r="AJ60">
+        <v>1.19</v>
+      </c>
+      <c r="AK60">
+        <v>1.14</v>
+      </c>
+      <c r="AL60">
+        <v>0</v>
+      </c>
+      <c r="AM60">
+        <v>4</v>
+      </c>
+      <c r="AN60">
+        <v>5</v>
+      </c>
+      <c r="AO60">
+        <v>13</v>
+      </c>
+      <c r="AP60">
+        <v>9</v>
+      </c>
+      <c r="AQ60">
+        <v>1.29</v>
+      </c>
+      <c r="AR60">
         <v>1.1</v>
       </c>
-      <c r="AF60">
-        <v>1.65</v>
-      </c>
-      <c r="AG60">
-        <v>2.03</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>2</v>
-      </c>
-      <c r="AK60">
-        <v>1.18</v>
-      </c>
-      <c r="AL60">
-        <v>0</v>
-      </c>
-      <c r="AM60">
-        <v>-1</v>
-      </c>
-      <c r="AN60">
-        <v>-1</v>
-      </c>
-      <c r="AO60">
-        <v>-1</v>
-      </c>
-      <c r="AP60">
-        <v>-1</v>
-      </c>
-      <c r="AQ60">
-        <v>0</v>
-      </c>
-      <c r="AR60">
-        <v>0</v>
-      </c>
       <c r="AS60">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT60">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
@@ -10229,26 +10229,26 @@
         </is>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N61">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "40", "81", "90+5"]</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AJ61">
@@ -10331,28 +10331,28 @@
         <v>0</v>
       </c>
       <c r="AM61">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN61">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO61">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP61">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ61">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR61">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS61">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT61">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
@@ -10395,39 +10395,39 @@
         <v>0</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I62">
         <v>0</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N62">
         <v>2.45</v>
       </c>
       <c r="O62">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P62">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q62">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="R62">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S62">
         <v>1.36</v>
@@ -10448,28 +10448,28 @@
         <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z62">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="AA62">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB62">
         <v>1.8</v>
       </c>
       <c r="AC62">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AD62">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE62">
         <v>1.04</v>
       </c>
       <c r="AF62">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG62">
         <v>1.97</v>
@@ -10481,41 +10481,41 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "67"]</t>
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AK62">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AL62">
         <v>0</v>
       </c>
       <c r="AM62">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN62">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO62">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP62">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ62">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR62">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS62">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT62">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
@@ -10555,10 +10555,10 @@
         </is>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -10567,14 +10567,14 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N63">
@@ -10639,12 +10639,12 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+4"]</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55", "69"]</t>
         </is>
       </c>
       <c r="AJ63">
@@ -10657,28 +10657,28 @@
         <v>0</v>
       </c>
       <c r="AM63">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN63">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO63">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP63">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ63">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR63">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS63">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT63">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
@@ -10709,22 +10709,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64">
         <v>0</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -10737,111 +10737,111 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N64">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="O64">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P64">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q64">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="R64">
+        <v>2</v>
+      </c>
+      <c r="S64">
+        <v>1.43</v>
+      </c>
+      <c r="T64">
+        <v>2.5</v>
+      </c>
+      <c r="U64">
+        <v>3</v>
+      </c>
+      <c r="V64">
+        <v>1.33</v>
+      </c>
+      <c r="W64">
+        <v>1.03</v>
+      </c>
+      <c r="X64">
+        <v>1.03</v>
+      </c>
+      <c r="Y64">
+        <v>1.33</v>
+      </c>
+      <c r="Z64">
+        <v>2.81</v>
+      </c>
+      <c r="AA64">
         <v>2.1</v>
       </c>
-      <c r="S64">
-        <v>1.45</v>
-      </c>
-      <c r="T64">
-        <v>2.62</v>
-      </c>
-      <c r="U64">
-        <v>3.2</v>
-      </c>
-      <c r="V64">
-        <v>1.32</v>
-      </c>
-      <c r="W64">
-        <v>1.04</v>
-      </c>
-      <c r="X64">
-        <v>1.04</v>
-      </c>
-      <c r="Y64">
-        <v>1.36</v>
-      </c>
-      <c r="Z64">
-        <v>2.9</v>
-      </c>
-      <c r="AA64">
-        <v>2.19</v>
-      </c>
       <c r="AB64">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC64">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD64">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE64">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF64">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG64">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
+          <t>["8"]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ64">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK64">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AL64">
         <v>0</v>
       </c>
       <c r="AM64">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN64">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO64">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP64">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ64">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR64">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS64">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT64">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
@@ -10872,16 +10872,16 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -10893,118 +10893,118 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65">
         <v>0</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N65">
+        <v>1.93</v>
+      </c>
+      <c r="O65">
+        <v>3.1</v>
+      </c>
+      <c r="P65">
+        <v>3.6</v>
+      </c>
+      <c r="Q65">
+        <v>2.61</v>
+      </c>
+      <c r="R65">
         <v>2.1</v>
       </c>
-      <c r="O65">
-        <v>3</v>
-      </c>
-      <c r="P65">
-        <v>3.35</v>
-      </c>
-      <c r="Q65">
-        <v>2.77</v>
-      </c>
-      <c r="R65">
+      <c r="S65">
+        <v>1.45</v>
+      </c>
+      <c r="T65">
+        <v>2.62</v>
+      </c>
+      <c r="U65">
+        <v>3.2</v>
+      </c>
+      <c r="V65">
+        <v>1.32</v>
+      </c>
+      <c r="W65">
+        <v>1.04</v>
+      </c>
+      <c r="X65">
+        <v>1.04</v>
+      </c>
+      <c r="Y65">
+        <v>1.36</v>
+      </c>
+      <c r="Z65">
+        <v>2.9</v>
+      </c>
+      <c r="AA65">
+        <v>2.19</v>
+      </c>
+      <c r="AB65">
+        <v>1.62</v>
+      </c>
+      <c r="AC65">
+        <v>4.1</v>
+      </c>
+      <c r="AD65">
+        <v>1.19</v>
+      </c>
+      <c r="AE65">
+        <v>1.03</v>
+      </c>
+      <c r="AF65">
+        <v>1.9</v>
+      </c>
+      <c r="AG65">
+        <v>1.75</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>["90+5"]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>1.28</v>
+      </c>
+      <c r="AK65">
+        <v>1.93</v>
+      </c>
+      <c r="AL65">
+        <v>0</v>
+      </c>
+      <c r="AM65">
         <v>2</v>
       </c>
-      <c r="S65">
-        <v>1.43</v>
-      </c>
-      <c r="T65">
-        <v>2.5</v>
-      </c>
-      <c r="U65">
-        <v>3</v>
-      </c>
-      <c r="V65">
-        <v>1.33</v>
-      </c>
-      <c r="W65">
-        <v>1.03</v>
-      </c>
-      <c r="X65">
-        <v>1.03</v>
-      </c>
-      <c r="Y65">
-        <v>1.33</v>
-      </c>
-      <c r="Z65">
-        <v>2.81</v>
-      </c>
-      <c r="AA65">
-        <v>2.1</v>
-      </c>
-      <c r="AB65">
-        <v>1.66</v>
-      </c>
-      <c r="AC65">
-        <v>3.9</v>
-      </c>
-      <c r="AD65">
+      <c r="AN65">
+        <v>4</v>
+      </c>
+      <c r="AO65">
+        <v>12</v>
+      </c>
+      <c r="AP65">
+        <v>10</v>
+      </c>
+      <c r="AQ65">
+        <v>1.34</v>
+      </c>
+      <c r="AR65">
         <v>1.22</v>
       </c>
-      <c r="AE65">
-        <v>1.05</v>
-      </c>
-      <c r="AF65">
-        <v>1.87</v>
-      </c>
-      <c r="AG65">
-        <v>1.85</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.27</v>
-      </c>
-      <c r="AK65">
-        <v>1.58</v>
-      </c>
-      <c r="AL65">
-        <v>0</v>
-      </c>
-      <c r="AM65">
-        <v>-1</v>
-      </c>
-      <c r="AN65">
-        <v>-1</v>
-      </c>
-      <c r="AO65">
-        <v>-1</v>
-      </c>
-      <c r="AP65">
-        <v>-1</v>
-      </c>
-      <c r="AQ65">
-        <v>0</v>
-      </c>
-      <c r="AR65">
-        <v>0</v>
-      </c>
       <c r="AS65">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT65">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
@@ -11044,10 +11044,10 @@
         </is>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -11056,14 +11056,14 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N66">
@@ -11128,12 +11128,12 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46"]</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AJ66">
@@ -11146,28 +11146,28 @@
         <v>0</v>
       </c>
       <c r="AM66">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN66">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO66">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP66">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ66">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR66">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS66">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT66">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
@@ -11226,68 +11226,68 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N67">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="O67">
         <v>3.4</v>
       </c>
       <c r="P67">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="Q67">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="R67">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S67">
         <v>1.3</v>
       </c>
       <c r="T67">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="U67">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="V67">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z67">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA67">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB67">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AC67">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD67">
         <v>1.33</v>
       </c>
       <c r="AE67">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF67">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,37 +11300,37 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK67">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AL67">
         <v>0</v>
       </c>
       <c r="AM67">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN67">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO67">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP67">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ67">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AR67">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS67">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT67">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
@@ -11370,36 +11370,36 @@
         </is>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I68">
         <v>0</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N68">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O68">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="P68">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -11408,92 +11408,92 @@
         <v>2.25</v>
       </c>
       <c r="S68">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T68">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="U68">
         <v>2.55</v>
       </c>
       <c r="V68">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W68">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z68">
         <v>3.8</v>
       </c>
       <c r="AA68">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB68">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AD68">
         <v>1.4</v>
       </c>
       <c r="AE68">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF68">
         <v>1.6</v>
       </c>
       <c r="AG68">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67", "74"]</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "31", "90"]</t>
         </is>
       </c>
       <c r="AJ68">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL68">
         <v>0</v>
       </c>
       <c r="AM68">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN68">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO68">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP68">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ68">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AR68">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS68">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT68">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
@@ -11556,52 +11556,52 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="O69">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P69">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="Q69">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R69">
         <v>1.91</v>
       </c>
       <c r="S69">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="T69">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="U69">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="V69">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W69">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X69">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y69">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Z69">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AA69">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="AB69">
         <v>1.39</v>
       </c>
       <c r="AC69">
-        <v>5.52</v>
+        <v>5.79</v>
       </c>
       <c r="AD69">
         <v>1.09</v>
@@ -11610,7 +11610,7 @@
         <v>1.01</v>
       </c>
       <c r="AF69">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG69">
         <v>1.62</v>
@@ -11629,7 +11629,7 @@
         <v>1.36</v>
       </c>
       <c r="AK69">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="O70">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P70">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q70">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R70">
         <v>2.15</v>
       </c>
       <c r="S70">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T70">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="U70">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V70">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W70">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y70">
         <v>1.29</v>
       </c>
       <c r="Z70">
+        <v>3.34</v>
+      </c>
+      <c r="AA70">
+        <v>1.95</v>
+      </c>
+      <c r="AB70">
+        <v>1.83</v>
+      </c>
+      <c r="AC70">
         <v>3.4</v>
-      </c>
-      <c r="AA70">
-        <v>1.87</v>
-      </c>
-      <c r="AB70">
-        <v>1.85</v>
-      </c>
-      <c r="AC70">
-        <v>3.3</v>
       </c>
       <c r="AD70">
         <v>1.29</v>
       </c>
       <c r="AE70">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AG70">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11885,49 +11885,49 @@
         <v>2.15</v>
       </c>
       <c r="O71">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P71">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="Q71">
         <v>2.7</v>
       </c>
       <c r="R71">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S71">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T71">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="U71">
-        <v>3.04</v>
+        <v>3.19</v>
       </c>
       <c r="V71">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W71">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
         <v>1.06</v>
       </c>
       <c r="Y71">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z71">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AA71">
         <v>2.1</v>
       </c>
       <c r="AB71">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC71">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="AD71">
         <v>1.21</v>
@@ -11936,7 +11936,7 @@
         <v>1.04</v>
       </c>
       <c r="AF71">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG71">
         <v>1.84</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK71">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,25 +12045,25 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="O72">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P72">
-        <v>4.85</v>
+        <v>4.98</v>
       </c>
       <c r="Q72">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="R72">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="S72">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T72">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U72">
         <v>2.2</v>
@@ -12072,53 +12072,53 @@
         <v>1.6</v>
       </c>
       <c r="W72">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X72">
         <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z72">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AA72">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB72">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AC72">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AD72">
         <v>1.55</v>
       </c>
       <c r="AE72">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF72">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG72">
+        <v>2.26</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
+        <v>1.15</v>
+      </c>
+      <c r="AK72">
         <v>2.25</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.17</v>
-      </c>
-      <c r="AK72">
-        <v>2.2</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="O73">
-        <v>3.9</v>
+        <v>3.62</v>
       </c>
       <c r="P73">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q73">
+        <v>2.16</v>
+      </c>
+      <c r="R73">
+        <v>2</v>
+      </c>
+      <c r="S73">
+        <v>1.38</v>
+      </c>
+      <c r="T73">
+        <v>2.7</v>
+      </c>
+      <c r="U73">
+        <v>3</v>
+      </c>
+      <c r="V73">
+        <v>1.4</v>
+      </c>
+      <c r="W73">
+        <v>1.06</v>
+      </c>
+      <c r="X73">
+        <v>1.05</v>
+      </c>
+      <c r="Y73">
+        <v>1.25</v>
+      </c>
+      <c r="Z73">
+        <v>2.5</v>
+      </c>
+      <c r="AA73">
         <v>2.01</v>
       </c>
-      <c r="R73">
-        <v>2.15</v>
-      </c>
-      <c r="S73">
-        <v>1.39</v>
-      </c>
-      <c r="T73">
-        <v>2.66</v>
-      </c>
-      <c r="U73">
-        <v>3.04</v>
-      </c>
-      <c r="V73">
-        <v>1.36</v>
-      </c>
-      <c r="W73">
-        <v>1.05</v>
-      </c>
-      <c r="X73">
-        <v>1</v>
-      </c>
-      <c r="Y73">
-        <v>1.22</v>
-      </c>
-      <c r="Z73">
-        <v>2.6</v>
-      </c>
-      <c r="AA73">
-        <v>1.75</v>
-      </c>
       <c r="AB73">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AC73">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="AD73">
         <v>1.23</v>
       </c>
       <c r="AE73">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF73">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AG73">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK73">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,55 +12371,55 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O74">
         <v>3.1</v>
       </c>
       <c r="P74">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q74">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="R74">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="S74">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T74">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="U74">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="V74">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W74">
         <v>1.06</v>
       </c>
       <c r="X74">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z74">
-        <v>2.74</v>
+        <v>2.89</v>
       </c>
       <c r="AA74">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="AB74">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC74">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD74">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE74">
         <v>1.02</v>
@@ -12428,7 +12428,7 @@
         <v>1.91</v>
       </c>
       <c r="AG74">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="O75">
+        <v>3.1</v>
+      </c>
+      <c r="P75">
         <v>3.4</v>
       </c>
-      <c r="P75">
-        <v>3.45</v>
-      </c>
       <c r="Q75">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R75">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S75">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T75">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="U75">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V75">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W75">
         <v>1.05</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y75">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z75">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA75">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="AB75">
         <v>1.72</v>
       </c>
       <c r="AC75">
-        <v>3.59</v>
+        <v>3.8</v>
       </c>
       <c r="AD75">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE75">
         <v>1.04</v>
       </c>
       <c r="AF75">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG75">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK75">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AL75">
         <v>0</v>
